--- a/Relatorio/APIS_detalhe_Campos_v23_06.xlsx
+++ b/Relatorio/APIS_detalhe_Campos_v23_06.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulo\Desktop\Relatório_PI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ESTG 25_26\2S\ProjetoInformatico\Prototipo\Versoes\weatherSense\Relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBEF48AD-AE3A-414A-94D1-B430EF9F8673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B33971D-2925-49C5-86AE-D2A95760CE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="14" xr2:uid="{E6E5DD2F-D0B6-44E9-B2EB-37380A5D374B}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3340" uniqueCount="1526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3361" uniqueCount="1534">
   <si>
     <t>Foreca</t>
   </si>
@@ -5643,9 +5643,6 @@
     <t>/data/observations/records</t>
   </si>
   <si>
-    <t>lat, lon, page, page_size, search</t>
-  </si>
-  <si>
     <t>lat, lon, variable, range</t>
   </si>
   <si>
@@ -5658,9 +5655,6 @@
     <t>/data/observations/current?lat=39.7436&amp;lon=-8.8071</t>
   </si>
   <si>
-    <t>/data/observations/records?lat=39.735122&amp;lon=-8.821217&amp;page=1&amp;page_size=10</t>
-  </si>
-  <si>
     <t>Exemplo de pedido</t>
   </si>
   <si>
@@ -5718,7 +5712,37 @@
     <t>/data/forecast/terrestrial/history?lat=39.735122&amp;lon=-8.821217&amp;variable=temperature&amp;range=24h</t>
   </si>
   <si>
-    <t>/data/forecast/terrestrial/records?lat=39.735122&amp;lon=-8.821217&amp;page=1&amp;page_size=10</t>
+    <t>lat, lon, page, page_size, search,variable</t>
+  </si>
+  <si>
+    <t>/data/observations/records?lat=39.735122&amp;lon=-8.821217&amp;page=1&amp;page_size=10&amp;variable=temperature</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/records?lat=39.735122&amp;lon=-8.821217&amp;page=1&amp;page_size=10&amp;variable=temperature</t>
+  </si>
+  <si>
+    <t>PREV MARINE</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/current</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/timeline</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/history</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/records</t>
+  </si>
+  <si>
+    <t>Previsão marítima mais próxima do momento atual por fonte</t>
+  </si>
+  <si>
+    <t>Previsões marítimas futuras organizadas cronologicamente por fonte</t>
+  </si>
+  <si>
+    <t>Registos históricos paginados das previsões marítimas</t>
   </si>
 </sst>
 </file>
@@ -6675,7 +6699,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="334">
+  <cellXfs count="333">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7377,6 +7401,192 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7404,175 +7614,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7599,38 +7647,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8299,7 +8320,7 @@
       </c>
     </row>
     <row r="5" spans="3:12" ht="15.75">
-      <c r="C5" s="265" t="s">
+      <c r="C5" s="257" t="s">
         <v>746</v>
       </c>
       <c r="D5" s="93" t="s">
@@ -8314,21 +8335,21 @@
       <c r="G5" s="93" t="s">
         <v>1033</v>
       </c>
-      <c r="H5" s="266" t="s">
+      <c r="H5" s="256" t="s">
         <v>1034</v>
       </c>
-      <c r="I5" s="267" t="s">
+      <c r="I5" s="258" t="s">
         <v>1035</v>
       </c>
-      <c r="J5" s="267" t="s">
+      <c r="J5" s="258" t="s">
         <v>1036</v>
       </c>
-      <c r="K5" s="268" t="s">
+      <c r="K5" s="254" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="6" spans="3:12" ht="15.75">
-      <c r="C6" s="265"/>
+      <c r="C6" s="257"/>
       <c r="D6" s="93" t="s">
         <v>1038</v>
       </c>
@@ -8341,13 +8362,13 @@
       <c r="G6" s="93" t="s">
         <v>1041</v>
       </c>
-      <c r="H6" s="266"/>
-      <c r="I6" s="267"/>
-      <c r="J6" s="267"/>
-      <c r="K6" s="269"/>
+      <c r="H6" s="256"/>
+      <c r="I6" s="258"/>
+      <c r="J6" s="258"/>
+      <c r="K6" s="259"/>
     </row>
     <row r="7" spans="3:12" ht="15.75">
-      <c r="C7" s="265"/>
+      <c r="C7" s="257"/>
       <c r="D7" s="93" t="s">
         <v>860</v>
       </c>
@@ -8360,94 +8381,94 @@
       <c r="G7" s="93" t="s">
         <v>1043</v>
       </c>
-      <c r="H7" s="266"/>
-      <c r="I7" s="267"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="270"/>
+      <c r="H7" s="256"/>
+      <c r="I7" s="258"/>
+      <c r="J7" s="258"/>
+      <c r="K7" s="255"/>
     </row>
     <row r="8" spans="3:12" ht="15.75">
-      <c r="C8" s="265" t="s">
+      <c r="C8" s="257" t="s">
         <v>1044</v>
       </c>
       <c r="D8" s="93" t="s">
         <v>1045</v>
       </c>
-      <c r="E8" s="266" t="s">
+      <c r="E8" s="256" t="s">
         <v>1046</v>
       </c>
-      <c r="F8" s="266" t="s">
+      <c r="F8" s="256" t="s">
         <v>1047</v>
       </c>
-      <c r="G8" s="266" t="s">
+      <c r="G8" s="256" t="s">
         <v>1048</v>
       </c>
-      <c r="H8" s="266" t="s">
+      <c r="H8" s="256" t="s">
         <v>1049</v>
       </c>
-      <c r="I8" s="266" t="s">
+      <c r="I8" s="256" t="s">
         <v>1050</v>
       </c>
-      <c r="J8" s="266" t="s">
+      <c r="J8" s="256" t="s">
         <v>1051</v>
       </c>
-      <c r="K8" s="268" t="s">
+      <c r="K8" s="254" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="9" spans="3:12" ht="15.75">
-      <c r="C9" s="265"/>
+      <c r="C9" s="257"/>
       <c r="D9" s="93" t="s">
         <v>1052</v>
       </c>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="270"/>
+      <c r="E9" s="256"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="256"/>
+      <c r="H9" s="256"/>
+      <c r="I9" s="256"/>
+      <c r="J9" s="256"/>
+      <c r="K9" s="255"/>
     </row>
     <row r="10" spans="3:12" ht="15.75">
-      <c r="C10" s="265" t="s">
+      <c r="C10" s="257" t="s">
         <v>455</v>
       </c>
       <c r="D10" s="93" t="s">
         <v>1053</v>
       </c>
-      <c r="E10" s="266" t="s">
+      <c r="E10" s="256" t="s">
         <v>1054</v>
       </c>
-      <c r="F10" s="266" t="s">
+      <c r="F10" s="256" t="s">
         <v>1055</v>
       </c>
-      <c r="G10" s="266" t="s">
+      <c r="G10" s="256" t="s">
         <v>1048</v>
       </c>
-      <c r="H10" s="266" t="s">
+      <c r="H10" s="256" t="s">
         <v>1034</v>
       </c>
-      <c r="I10" s="266" t="s">
+      <c r="I10" s="256" t="s">
         <v>1056</v>
       </c>
-      <c r="J10" s="266" t="s">
+      <c r="J10" s="256" t="s">
         <v>1048</v>
       </c>
-      <c r="K10" s="268" t="s">
+      <c r="K10" s="254" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="11" spans="3:12" ht="15.75">
-      <c r="C11" s="265"/>
+      <c r="C11" s="257"/>
       <c r="D11" s="93" t="s">
         <v>1058</v>
       </c>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="270"/>
+      <c r="E11" s="256"/>
+      <c r="F11" s="256"/>
+      <c r="G11" s="256"/>
+      <c r="H11" s="256"/>
+      <c r="I11" s="256"/>
+      <c r="J11" s="256"/>
+      <c r="K11" s="255"/>
     </row>
     <row r="12" spans="3:12" ht="15.75">
       <c r="C12" s="92" t="s">
@@ -8594,6 +8615,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="K5:K7"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="J8:J9"/>
@@ -8610,11 +8636,6 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="H8:H9"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="K5:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8901,7 +8922,7 @@
       <c r="G19" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="278" t="s">
+      <c r="H19" s="268" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -8927,7 +8948,7 @@
       <c r="G20" s="148" t="s">
         <v>87</v>
       </c>
-      <c r="H20" s="278"/>
+      <c r="H20" s="268"/>
     </row>
     <row r="21" spans="1:8" ht="21" customHeight="1">
       <c r="A21" s="133" t="s">
@@ -8951,7 +8972,7 @@
       <c r="G21" s="148" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="278"/>
+      <c r="H21" s="268"/>
     </row>
     <row r="22" spans="1:8" ht="21.75" customHeight="1">
       <c r="A22" s="133" t="s">
@@ -8975,7 +8996,7 @@
       <c r="G22" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="278" t="s">
+      <c r="H22" s="268" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -9001,7 +9022,7 @@
       <c r="G23" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="278"/>
+      <c r="H23" s="268"/>
     </row>
     <row r="24" spans="1:8" ht="21.75" customHeight="1">
       <c r="A24" s="133" t="s">
@@ -9025,7 +9046,7 @@
       <c r="G24" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="278"/>
+      <c r="H24" s="268"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1">
       <c r="A25" s="133" t="s">
@@ -9049,7 +9070,7 @@
       <c r="G25" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="278"/>
+      <c r="H25" s="268"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1">
       <c r="A26" s="133" t="s">
@@ -9073,7 +9094,7 @@
       <c r="G26" s="148" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="278"/>
+      <c r="H26" s="268"/>
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1">
       <c r="A27" s="133" t="s">
@@ -9095,7 +9116,7 @@
         <v>1106</v>
       </c>
       <c r="G27" s="148"/>
-      <c r="H27" s="278"/>
+      <c r="H27" s="268"/>
     </row>
     <row r="28" spans="1:8" ht="20.25" customHeight="1">
       <c r="A28" s="133" t="s">
@@ -9119,7 +9140,7 @@
       <c r="G28" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="278"/>
+      <c r="H28" s="268"/>
     </row>
     <row r="29" spans="1:8" ht="21" customHeight="1">
       <c r="A29" s="133" t="s">
@@ -9143,7 +9164,7 @@
       <c r="G29" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="278"/>
+      <c r="H29" s="268"/>
     </row>
     <row r="30" spans="1:8" ht="20.25" customHeight="1">
       <c r="A30" s="133" t="s">
@@ -9167,7 +9188,7 @@
       <c r="G30" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="278"/>
+      <c r="H30" s="268"/>
     </row>
     <row r="31" spans="1:8" ht="20.25" customHeight="1">
       <c r="A31" s="133" t="s">
@@ -9191,7 +9212,7 @@
       <c r="G31" s="148" t="s">
         <v>63</v>
       </c>
-      <c r="H31" s="278"/>
+      <c r="H31" s="268"/>
     </row>
     <row r="32" spans="1:8" ht="23.25" customHeight="1">
       <c r="A32" s="133" t="s">
@@ -9215,7 +9236,7 @@
       <c r="G32" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="278"/>
+      <c r="H32" s="268"/>
     </row>
     <row r="33" spans="1:8" ht="21" customHeight="1">
       <c r="A33" s="133" t="s">
@@ -9237,7 +9258,7 @@
         <v>1106</v>
       </c>
       <c r="G33" s="148"/>
-      <c r="H33" s="278"/>
+      <c r="H33" s="268"/>
     </row>
     <row r="34" spans="1:8" ht="20.25" customHeight="1">
       <c r="A34" s="133" t="s">
@@ -9261,7 +9282,7 @@
       <c r="G34" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="278"/>
+      <c r="H34" s="268"/>
     </row>
     <row r="35" spans="1:8" ht="21" customHeight="1">
       <c r="A35" s="133" t="s">
@@ -9283,7 +9304,7 @@
         <v>1106</v>
       </c>
       <c r="G35" s="148"/>
-      <c r="H35" s="278"/>
+      <c r="H35" s="268"/>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1">
       <c r="A36" s="133" t="s">
@@ -9305,7 +9326,7 @@
         <v>1106</v>
       </c>
       <c r="G36" s="148"/>
-      <c r="H36" s="278"/>
+      <c r="H36" s="268"/>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1">
       <c r="A37" s="133" t="s">
@@ -9329,7 +9350,7 @@
       <c r="G37" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="278"/>
+      <c r="H37" s="268"/>
     </row>
     <row r="38" spans="1:8" ht="20.25" customHeight="1">
       <c r="A38" s="133" t="s">
@@ -9353,7 +9374,7 @@
       <c r="G38" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="H38" s="278" t="s">
+      <c r="H38" s="268" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -9379,7 +9400,7 @@
       <c r="G39" s="155" t="s">
         <v>114</v>
       </c>
-      <c r="H39" s="278"/>
+      <c r="H39" s="268"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="42" spans="1:8" ht="21" customHeight="1" thickBot="1">
@@ -9800,10 +9821,10 @@
   <sheetData>
     <row r="3" spans="2:14" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:14" ht="15.75" thickBot="1">
-      <c r="K4" s="262" t="s">
+      <c r="K4" s="304" t="s">
         <v>1192</v>
       </c>
-      <c r="L4" s="264"/>
+      <c r="L4" s="305"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
@@ -9817,13 +9838,13 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B6" s="306" t="s">
+      <c r="B6" s="292" t="s">
         <v>1437</v>
       </c>
-      <c r="C6" s="307"/>
-      <c r="D6" s="307"/>
-      <c r="E6" s="307"/>
-      <c r="F6" s="308"/>
+      <c r="C6" s="293"/>
+      <c r="D6" s="293"/>
+      <c r="E6" s="293"/>
+      <c r="F6" s="294"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="K6" s="161" t="s">
@@ -9857,7 +9878,7 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="309"/>
+      <c r="B8" s="295"/>
       <c r="C8" s="14" t="s">
         <v>1335</v>
       </c>
@@ -9878,7 +9899,7 @@
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="310"/>
+      <c r="B9" s="296"/>
       <c r="C9" s="14" t="s">
         <v>1336</v>
       </c>
@@ -9899,12 +9920,12 @@
       </c>
     </row>
     <row r="10" spans="2:14">
-      <c r="B10" s="310"/>
-      <c r="C10" s="312"/>
+      <c r="B10" s="296"/>
+      <c r="C10" s="298"/>
       <c r="D10" s="156" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="312"/>
+      <c r="E10" s="298"/>
       <c r="F10" s="15" t="s">
         <v>1339</v>
       </c>
@@ -9916,12 +9937,12 @@
       </c>
     </row>
     <row r="11" spans="2:14">
-      <c r="B11" s="310"/>
-      <c r="C11" s="313"/>
+      <c r="B11" s="296"/>
+      <c r="C11" s="299"/>
       <c r="D11" s="156" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="313"/>
+      <c r="E11" s="299"/>
       <c r="F11" s="15" t="s">
         <v>1340</v>
       </c>
@@ -9933,12 +9954,12 @@
       </c>
     </row>
     <row r="12" spans="2:14">
-      <c r="B12" s="310"/>
-      <c r="C12" s="313"/>
+      <c r="B12" s="296"/>
+      <c r="C12" s="299"/>
       <c r="D12" s="156" t="s">
         <v>1164</v>
       </c>
-      <c r="E12" s="313"/>
+      <c r="E12" s="299"/>
       <c r="F12" s="15" t="s">
         <v>1341</v>
       </c>
@@ -9950,10 +9971,10 @@
       </c>
     </row>
     <row r="13" spans="2:14">
-      <c r="B13" s="310"/>
-      <c r="C13" s="313"/>
-      <c r="D13" s="312"/>
-      <c r="E13" s="313"/>
+      <c r="B13" s="296"/>
+      <c r="C13" s="299"/>
+      <c r="D13" s="298"/>
+      <c r="E13" s="299"/>
       <c r="F13" s="15" t="s">
         <v>1342</v>
       </c>
@@ -9965,10 +9986,10 @@
       </c>
     </row>
     <row r="14" spans="2:14">
-      <c r="B14" s="310"/>
-      <c r="C14" s="313"/>
-      <c r="D14" s="313"/>
-      <c r="E14" s="313"/>
+      <c r="B14" s="296"/>
+      <c r="C14" s="299"/>
+      <c r="D14" s="299"/>
+      <c r="E14" s="299"/>
       <c r="F14" s="15" t="s">
         <v>1343</v>
       </c>
@@ -9980,10 +10001,10 @@
       </c>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="310"/>
-      <c r="C15" s="313"/>
-      <c r="D15" s="313"/>
-      <c r="E15" s="313"/>
+      <c r="B15" s="296"/>
+      <c r="C15" s="299"/>
+      <c r="D15" s="299"/>
+      <c r="E15" s="299"/>
       <c r="F15" s="15" t="s">
         <v>1344</v>
       </c>
@@ -9995,10 +10016,10 @@
       </c>
     </row>
     <row r="16" spans="2:14">
-      <c r="B16" s="310"/>
-      <c r="C16" s="313"/>
-      <c r="D16" s="313"/>
-      <c r="E16" s="313"/>
+      <c r="B16" s="296"/>
+      <c r="C16" s="299"/>
+      <c r="D16" s="299"/>
+      <c r="E16" s="299"/>
       <c r="F16" s="15" t="s">
         <v>1345</v>
       </c>
@@ -10010,10 +10031,10 @@
       </c>
     </row>
     <row r="17" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B17" s="311"/>
-      <c r="C17" s="314"/>
-      <c r="D17" s="314"/>
-      <c r="E17" s="314"/>
+      <c r="B17" s="297"/>
+      <c r="C17" s="300"/>
+      <c r="D17" s="300"/>
+      <c r="E17" s="300"/>
       <c r="F17" s="23" t="s">
         <v>1346</v>
       </c>
@@ -10066,11 +10087,11 @@
       <c r="H24" s="224" t="s">
         <v>1189</v>
       </c>
-      <c r="K24" s="305" t="s">
+      <c r="K24" s="306" t="s">
         <v>1194</v>
       </c>
-      <c r="L24" s="305"/>
-      <c r="M24" s="305"/>
+      <c r="L24" s="306"/>
+      <c r="M24" s="306"/>
       <c r="N24" s="174"/>
     </row>
     <row r="25" spans="2:14" ht="15.75" thickBot="1">
@@ -10111,7 +10132,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="15"/>
-      <c r="K26" s="302" t="s">
+      <c r="K26" s="301" t="s">
         <v>0</v>
       </c>
       <c r="L26" s="167" t="s">
@@ -10135,7 +10156,7 @@
         <v>20</v>
       </c>
       <c r="H27" s="26"/>
-      <c r="K27" s="303"/>
+      <c r="K27" s="302"/>
       <c r="L27" s="166" t="s">
         <v>1186</v>
       </c>
@@ -10157,7 +10178,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="169"/>
-      <c r="K28" s="303"/>
+      <c r="K28" s="302"/>
       <c r="L28" s="166" t="s">
         <v>1183</v>
       </c>
@@ -10181,7 +10202,7 @@
       <c r="H29" s="169" t="s">
         <v>1441</v>
       </c>
-      <c r="K29" s="304"/>
+      <c r="K29" s="303"/>
       <c r="L29" s="22" t="s">
         <v>1184</v>
       </c>
@@ -10203,7 +10224,7 @@
         <v>242</v>
       </c>
       <c r="H30" s="15"/>
-      <c r="K30" s="302" t="s">
+      <c r="K30" s="301" t="s">
         <v>455</v>
       </c>
       <c r="L30" s="167" t="s">
@@ -10227,7 +10248,7 @@
         <v>242</v>
       </c>
       <c r="H31" s="15"/>
-      <c r="K31" s="303"/>
+      <c r="K31" s="302"/>
       <c r="L31" s="14" t="s">
         <v>1182</v>
       </c>
@@ -10252,7 +10273,7 @@
       <c r="I32" s="182" t="s">
         <v>1190</v>
       </c>
-      <c r="K32" s="304"/>
+      <c r="K32" s="303"/>
       <c r="L32" s="22" t="s">
         <v>1184</v>
       </c>
@@ -10314,7 +10335,7 @@
         <v>25</v>
       </c>
       <c r="H35" s="15"/>
-      <c r="K35" s="302" t="s">
+      <c r="K35" s="301" t="s">
         <v>1202</v>
       </c>
       <c r="L35" s="175" t="s">
@@ -10337,7 +10358,7 @@
       <c r="H36" s="15" t="s">
         <v>1445</v>
       </c>
-      <c r="K36" s="303"/>
+      <c r="K36" s="302"/>
       <c r="L36" s="158" t="s">
         <v>1209</v>
       </c>
@@ -10356,7 +10377,7 @@
         <v>242</v>
       </c>
       <c r="H37" s="169"/>
-      <c r="K37" s="303"/>
+      <c r="K37" s="302"/>
       <c r="L37" s="158" t="s">
         <v>1210</v>
       </c>
@@ -10377,7 +10398,7 @@
       <c r="H38" s="169" t="s">
         <v>1447</v>
       </c>
-      <c r="K38" s="303"/>
+      <c r="K38" s="302"/>
       <c r="L38" s="158" t="s">
         <v>1211</v>
       </c>
@@ -10398,7 +10419,7 @@
       <c r="H39" s="169" t="s">
         <v>1191</v>
       </c>
-      <c r="K39" s="304"/>
+      <c r="K39" s="303"/>
       <c r="L39" s="159" t="s">
         <v>1212</v>
       </c>
@@ -10419,7 +10440,7 @@
       <c r="H40" s="169" t="s">
         <v>1446</v>
       </c>
-      <c r="K40" s="302" t="s">
+      <c r="K40" s="301" t="s">
         <v>1203</v>
       </c>
       <c r="L40" s="176" t="s">
@@ -10442,7 +10463,7 @@
       <c r="H41" s="15" t="s">
         <v>1445</v>
       </c>
-      <c r="K41" s="303"/>
+      <c r="K41" s="302"/>
       <c r="L41" s="177" t="s">
         <v>1214</v>
       </c>
@@ -10463,7 +10484,7 @@
       <c r="H42" s="15" t="s">
         <v>1443</v>
       </c>
-      <c r="K42" s="304"/>
+      <c r="K42" s="303"/>
       <c r="L42" s="178" t="s">
         <v>1215</v>
       </c>
@@ -10514,17 +10535,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B8:B17"/>
-    <mergeCell ref="C10:C17"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="E10:E17"/>
     <mergeCell ref="K35:K39"/>
     <mergeCell ref="K40:K42"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="K26:K29"/>
     <mergeCell ref="K30:K32"/>
     <mergeCell ref="K24:M24"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B8:B17"/>
+    <mergeCell ref="C10:C17"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="E10:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" orientation="landscape" r:id="rId1"/>
@@ -10556,24 +10577,24 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:15">
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="263" t="s">
         <v>1016</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
       <c r="F3" t="s">
         <v>1253</v>
       </c>
-      <c r="H3" s="259" t="s">
+      <c r="H3" s="263" t="s">
         <v>949</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="M3" s="259" t="s">
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="M3" s="263" t="s">
         <v>1236</v>
       </c>
-      <c r="N3" s="259"/>
-      <c r="O3" s="259"/>
+      <c r="N3" s="263"/>
+      <c r="O3" s="263"/>
     </row>
     <row r="4" spans="3:15">
       <c r="C4" s="44"/>
@@ -10593,7 +10614,7 @@
       <c r="J4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="258" t="s">
+      <c r="M4" s="308" t="s">
         <v>1217</v>
       </c>
       <c r="N4" s="40" t="s">
@@ -10604,7 +10625,7 @@
       </c>
     </row>
     <row r="5" spans="3:15">
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="308" t="s">
         <v>1217</v>
       </c>
       <c r="D5" s="14" t="s">
@@ -10613,7 +10634,7 @@
       <c r="E5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="258" t="s">
+      <c r="H5" s="308" t="s">
         <v>1217</v>
       </c>
       <c r="I5" s="14" t="s">
@@ -10622,7 +10643,7 @@
       <c r="J5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="M5" s="258"/>
+      <c r="M5" s="308"/>
       <c r="N5" s="14" t="s">
         <v>871</v>
       </c>
@@ -10631,21 +10652,21 @@
       </c>
     </row>
     <row r="6" spans="3:15">
-      <c r="C6" s="258"/>
+      <c r="C6" s="308"/>
       <c r="D6" s="14" t="s">
         <v>1004</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>1219</v>
       </c>
-      <c r="H6" s="258"/>
+      <c r="H6" s="308"/>
       <c r="I6" s="14" t="s">
         <v>906</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>1227</v>
       </c>
-      <c r="M6" s="258"/>
+      <c r="M6" s="308"/>
       <c r="N6" s="14" t="s">
         <v>873</v>
       </c>
@@ -10654,21 +10675,21 @@
       </c>
     </row>
     <row r="7" spans="3:15">
-      <c r="C7" s="258"/>
+      <c r="C7" s="308"/>
       <c r="D7" s="14" t="s">
         <v>1216</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>1220</v>
       </c>
-      <c r="H7" s="258"/>
+      <c r="H7" s="308"/>
       <c r="I7" s="14" t="s">
         <v>907</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>1228</v>
       </c>
-      <c r="M7" s="258"/>
+      <c r="M7" s="308"/>
       <c r="N7" s="14" t="s">
         <v>875</v>
       </c>
@@ -10677,21 +10698,21 @@
       </c>
     </row>
     <row r="8" spans="3:15">
-      <c r="C8" s="258"/>
+      <c r="C8" s="308"/>
       <c r="D8" s="14" t="s">
         <v>1009</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>1221</v>
       </c>
-      <c r="H8" s="258"/>
+      <c r="H8" s="308"/>
       <c r="I8" s="14" t="s">
         <v>909</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>1229</v>
       </c>
-      <c r="M8" s="258"/>
+      <c r="M8" s="308"/>
       <c r="N8" s="14" t="s">
         <v>877</v>
       </c>
@@ -10700,21 +10721,21 @@
       </c>
     </row>
     <row r="9" spans="3:15">
-      <c r="C9" s="258"/>
+      <c r="C9" s="308"/>
       <c r="D9" s="14" t="s">
         <v>1011</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>1222</v>
       </c>
-      <c r="H9" s="258"/>
+      <c r="H9" s="308"/>
       <c r="I9" s="14" t="s">
         <v>919</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>1230</v>
       </c>
-      <c r="M9" s="258"/>
+      <c r="M9" s="308"/>
       <c r="N9" s="14" t="s">
         <v>879</v>
       </c>
@@ -10723,21 +10744,21 @@
       </c>
     </row>
     <row r="10" spans="3:15">
-      <c r="C10" s="258"/>
+      <c r="C10" s="308"/>
       <c r="D10" s="14" t="s">
         <v>1013</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>1223</v>
       </c>
-      <c r="H10" s="258"/>
+      <c r="H10" s="308"/>
       <c r="I10" s="14" t="s">
         <v>921</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>1231</v>
       </c>
-      <c r="M10" s="258"/>
+      <c r="M10" s="308"/>
       <c r="N10" s="14" t="s">
         <v>881</v>
       </c>
@@ -10746,7 +10767,7 @@
       </c>
     </row>
     <row r="11" spans="3:15">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="308" t="s">
         <v>1218</v>
       </c>
       <c r="D11" s="14" t="s">
@@ -10755,14 +10776,14 @@
       <c r="E11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="258"/>
+      <c r="H11" s="308"/>
       <c r="I11" s="14" t="s">
         <v>923</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>1232</v>
       </c>
-      <c r="M11" s="258"/>
+      <c r="M11" s="308"/>
       <c r="N11" s="14" t="s">
         <v>883</v>
       </c>
@@ -10771,21 +10792,21 @@
       </c>
     </row>
     <row r="12" spans="3:15">
-      <c r="C12" s="258"/>
+      <c r="C12" s="308"/>
       <c r="D12" s="182" t="s">
         <v>975</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="258"/>
+      <c r="H12" s="308"/>
       <c r="I12" s="14" t="s">
         <v>941</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="M12" s="258"/>
+      <c r="M12" s="308"/>
       <c r="N12" s="14" t="s">
         <v>886</v>
       </c>
@@ -10794,14 +10815,14 @@
       </c>
     </row>
     <row r="13" spans="3:15">
-      <c r="C13" s="258"/>
+      <c r="C13" s="308"/>
       <c r="D13" s="14" t="s">
         <v>976</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>1224</v>
       </c>
-      <c r="H13" s="260" t="s">
+      <c r="H13" s="309" t="s">
         <v>1233</v>
       </c>
       <c r="I13" s="14" t="s">
@@ -10810,7 +10831,7 @@
       <c r="J13" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="M13" s="258"/>
+      <c r="M13" s="308"/>
       <c r="N13" s="14" t="s">
         <v>888</v>
       </c>
@@ -10819,14 +10840,14 @@
       </c>
     </row>
     <row r="14" spans="3:15">
-      <c r="C14" s="258"/>
+      <c r="C14" s="308"/>
       <c r="D14" s="14" t="s">
         <v>1000</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>1225</v>
       </c>
-      <c r="H14" s="261"/>
+      <c r="H14" s="310"/>
       <c r="I14" s="14" t="s">
         <v>945</v>
       </c>
@@ -10844,15 +10865,15 @@
       <c r="D24" s="182"/>
     </row>
     <row r="25" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C25" s="262" t="s">
+      <c r="C25" s="304" t="s">
         <v>1481</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="E25" s="263"/>
-      <c r="F25" s="263"/>
-      <c r="G25" s="263"/>
-      <c r="H25" s="263"/>
-      <c r="I25" s="264"/>
+      <c r="D25" s="307"/>
+      <c r="E25" s="307"/>
+      <c r="F25" s="307"/>
+      <c r="G25" s="307"/>
+      <c r="H25" s="307"/>
+      <c r="I25" s="305"/>
       <c r="K25" s="244" t="s">
         <v>1484</v>
       </c>
@@ -10912,7 +10933,7 @@
       <c r="P26" s="15"/>
     </row>
     <row r="27" spans="3:16">
-      <c r="C27" s="252"/>
+      <c r="C27" s="314"/>
       <c r="D27" s="14" t="s">
         <v>1256</v>
       </c>
@@ -10949,7 +10970,7 @@
       <c r="P27" s="15"/>
     </row>
     <row r="28" spans="3:16">
-      <c r="C28" s="253"/>
+      <c r="C28" s="315"/>
       <c r="D28" s="14" t="s">
         <v>1358</v>
       </c>
@@ -10986,21 +11007,21 @@
       <c r="P28" s="15"/>
     </row>
     <row r="29" spans="3:16">
-      <c r="C29" s="253"/>
+      <c r="C29" s="315"/>
       <c r="D29" s="14" t="s">
         <v>1359</v>
       </c>
       <c r="E29" s="242" t="s">
         <v>1163</v>
       </c>
-      <c r="F29" s="255"/>
+      <c r="F29" s="317"/>
       <c r="G29" s="14" t="s">
         <v>1363</v>
       </c>
       <c r="H29" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="I29" s="249"/>
+      <c r="I29" s="311"/>
       <c r="K29" s="210" t="s">
         <v>1387</v>
       </c>
@@ -11019,19 +11040,19 @@
       <c r="P29" s="15"/>
     </row>
     <row r="30" spans="3:16">
-      <c r="C30" s="253"/>
+      <c r="C30" s="315"/>
       <c r="D30" s="14" t="s">
         <v>1360</v>
       </c>
-      <c r="E30" s="255"/>
-      <c r="F30" s="256"/>
+      <c r="E30" s="317"/>
+      <c r="F30" s="318"/>
       <c r="G30" s="14" t="s">
         <v>1364</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>1346</v>
       </c>
-      <c r="I30" s="250"/>
+      <c r="I30" s="312"/>
       <c r="K30" s="210" t="s">
         <v>1388</v>
       </c>
@@ -11052,15 +11073,15 @@
       </c>
     </row>
     <row r="31" spans="3:16">
-      <c r="C31" s="253"/>
-      <c r="D31" s="255"/>
-      <c r="E31" s="256"/>
-      <c r="F31" s="256"/>
+      <c r="C31" s="315"/>
+      <c r="D31" s="317"/>
+      <c r="E31" s="318"/>
+      <c r="F31" s="318"/>
       <c r="G31" s="14" t="s">
         <v>1365</v>
       </c>
-      <c r="H31" s="255"/>
-      <c r="I31" s="250"/>
+      <c r="H31" s="317"/>
+      <c r="I31" s="312"/>
       <c r="K31" s="210" t="s">
         <v>1251</v>
       </c>
@@ -11079,15 +11100,15 @@
       <c r="P31" s="15"/>
     </row>
     <row r="32" spans="3:16">
-      <c r="C32" s="253"/>
-      <c r="D32" s="256"/>
-      <c r="E32" s="256"/>
-      <c r="F32" s="256"/>
+      <c r="C32" s="315"/>
+      <c r="D32" s="318"/>
+      <c r="E32" s="318"/>
+      <c r="F32" s="318"/>
       <c r="G32" s="14" t="s">
         <v>1366</v>
       </c>
-      <c r="H32" s="256"/>
-      <c r="I32" s="250"/>
+      <c r="H32" s="318"/>
+      <c r="I32" s="312"/>
       <c r="K32" s="210" t="s">
         <v>1252</v>
       </c>
@@ -11106,15 +11127,15 @@
       <c r="P32" s="15"/>
     </row>
     <row r="33" spans="3:16">
-      <c r="C33" s="253"/>
-      <c r="D33" s="256"/>
-      <c r="E33" s="256"/>
-      <c r="F33" s="256"/>
+      <c r="C33" s="315"/>
+      <c r="D33" s="318"/>
+      <c r="E33" s="318"/>
+      <c r="F33" s="318"/>
       <c r="G33" s="14" t="s">
         <v>1367</v>
       </c>
-      <c r="H33" s="256"/>
-      <c r="I33" s="250"/>
+      <c r="H33" s="318"/>
+      <c r="I33" s="312"/>
       <c r="K33" s="247" t="s">
         <v>1347</v>
       </c>
@@ -11133,15 +11154,15 @@
       <c r="P33" s="15"/>
     </row>
     <row r="34" spans="3:16">
-      <c r="C34" s="253"/>
-      <c r="D34" s="256"/>
-      <c r="E34" s="256"/>
-      <c r="F34" s="256"/>
+      <c r="C34" s="315"/>
+      <c r="D34" s="318"/>
+      <c r="E34" s="318"/>
+      <c r="F34" s="318"/>
       <c r="G34" s="14" t="s">
         <v>1368</v>
       </c>
-      <c r="H34" s="256"/>
-      <c r="I34" s="250"/>
+      <c r="H34" s="318"/>
+      <c r="I34" s="312"/>
       <c r="K34" s="210" t="s">
         <v>1348</v>
       </c>
@@ -11162,15 +11183,15 @@
       </c>
     </row>
     <row r="35" spans="3:16">
-      <c r="C35" s="253"/>
-      <c r="D35" s="256"/>
-      <c r="E35" s="256"/>
-      <c r="F35" s="256"/>
+      <c r="C35" s="315"/>
+      <c r="D35" s="318"/>
+      <c r="E35" s="318"/>
+      <c r="F35" s="318"/>
       <c r="G35" s="14" t="s">
         <v>1369</v>
       </c>
-      <c r="H35" s="256"/>
-      <c r="I35" s="250"/>
+      <c r="H35" s="318"/>
+      <c r="I35" s="312"/>
       <c r="K35" s="247" t="s">
         <v>1389</v>
       </c>
@@ -11189,15 +11210,15 @@
       <c r="P35" s="15"/>
     </row>
     <row r="36" spans="3:16">
-      <c r="C36" s="253"/>
-      <c r="D36" s="256"/>
-      <c r="E36" s="256"/>
-      <c r="F36" s="256"/>
+      <c r="C36" s="315"/>
+      <c r="D36" s="318"/>
+      <c r="E36" s="318"/>
+      <c r="F36" s="318"/>
       <c r="G36" s="14" t="s">
         <v>1370</v>
       </c>
-      <c r="H36" s="256"/>
-      <c r="I36" s="250"/>
+      <c r="H36" s="318"/>
+      <c r="I36" s="312"/>
       <c r="K36" s="247" t="s">
         <v>1390</v>
       </c>
@@ -11216,15 +11237,15 @@
       <c r="P36" s="15"/>
     </row>
     <row r="37" spans="3:16">
-      <c r="C37" s="253"/>
-      <c r="D37" s="256"/>
-      <c r="E37" s="256"/>
-      <c r="F37" s="256"/>
+      <c r="C37" s="315"/>
+      <c r="D37" s="318"/>
+      <c r="E37" s="318"/>
+      <c r="F37" s="318"/>
       <c r="G37" s="14" t="s">
         <v>1371</v>
       </c>
-      <c r="H37" s="256"/>
-      <c r="I37" s="250"/>
+      <c r="H37" s="318"/>
+      <c r="I37" s="312"/>
       <c r="K37" s="247" t="s">
         <v>1391</v>
       </c>
@@ -11243,15 +11264,15 @@
       <c r="P37" s="15"/>
     </row>
     <row r="38" spans="3:16">
-      <c r="C38" s="253"/>
-      <c r="D38" s="256"/>
-      <c r="E38" s="256"/>
-      <c r="F38" s="256"/>
+      <c r="C38" s="315"/>
+      <c r="D38" s="318"/>
+      <c r="E38" s="318"/>
+      <c r="F38" s="318"/>
       <c r="G38" s="14" t="s">
         <v>1372</v>
       </c>
-      <c r="H38" s="256"/>
-      <c r="I38" s="250"/>
+      <c r="H38" s="318"/>
+      <c r="I38" s="312"/>
       <c r="K38" s="247" t="s">
         <v>1392</v>
       </c>
@@ -11270,15 +11291,15 @@
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="3:16">
-      <c r="C39" s="253"/>
-      <c r="D39" s="256"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
+      <c r="C39" s="315"/>
+      <c r="D39" s="318"/>
+      <c r="E39" s="318"/>
+      <c r="F39" s="318"/>
       <c r="G39" s="14" t="s">
         <v>1373</v>
       </c>
-      <c r="H39" s="256"/>
-      <c r="I39" s="250"/>
+      <c r="H39" s="318"/>
+      <c r="I39" s="312"/>
       <c r="K39" s="247" t="s">
         <v>1393</v>
       </c>
@@ -11297,15 +11318,15 @@
       <c r="P39" s="15"/>
     </row>
     <row r="40" spans="3:16">
-      <c r="C40" s="253"/>
-      <c r="D40" s="256"/>
-      <c r="E40" s="256"/>
-      <c r="F40" s="256"/>
+      <c r="C40" s="315"/>
+      <c r="D40" s="318"/>
+      <c r="E40" s="318"/>
+      <c r="F40" s="318"/>
       <c r="G40" s="14" t="s">
         <v>1374</v>
       </c>
-      <c r="H40" s="256"/>
-      <c r="I40" s="250"/>
+      <c r="H40" s="318"/>
+      <c r="I40" s="312"/>
       <c r="K40" s="247" t="s">
         <v>1394</v>
       </c>
@@ -11324,15 +11345,15 @@
       <c r="P40" s="15"/>
     </row>
     <row r="41" spans="3:16">
-      <c r="C41" s="253"/>
-      <c r="D41" s="256"/>
-      <c r="E41" s="256"/>
-      <c r="F41" s="256"/>
+      <c r="C41" s="315"/>
+      <c r="D41" s="318"/>
+      <c r="E41" s="318"/>
+      <c r="F41" s="318"/>
       <c r="G41" s="14" t="s">
         <v>1375</v>
       </c>
-      <c r="H41" s="256"/>
-      <c r="I41" s="250"/>
+      <c r="H41" s="318"/>
+      <c r="I41" s="312"/>
       <c r="K41" s="247" t="s">
         <v>1395</v>
       </c>
@@ -11353,15 +11374,15 @@
       </c>
     </row>
     <row r="42" spans="3:16">
-      <c r="C42" s="253"/>
-      <c r="D42" s="256"/>
-      <c r="E42" s="256"/>
-      <c r="F42" s="256"/>
+      <c r="C42" s="315"/>
+      <c r="D42" s="318"/>
+      <c r="E42" s="318"/>
+      <c r="F42" s="318"/>
       <c r="G42" s="14" t="s">
         <v>1376</v>
       </c>
-      <c r="H42" s="256"/>
-      <c r="I42" s="250"/>
+      <c r="H42" s="318"/>
+      <c r="I42" s="312"/>
       <c r="K42" s="247" t="s">
         <v>1396</v>
       </c>
@@ -11380,15 +11401,15 @@
       <c r="P42" s="15"/>
     </row>
     <row r="43" spans="3:16">
-      <c r="C43" s="253"/>
-      <c r="D43" s="256"/>
-      <c r="E43" s="256"/>
-      <c r="F43" s="256"/>
+      <c r="C43" s="315"/>
+      <c r="D43" s="318"/>
+      <c r="E43" s="318"/>
+      <c r="F43" s="318"/>
       <c r="G43" s="14" t="s">
         <v>1377</v>
       </c>
-      <c r="H43" s="256"/>
-      <c r="I43" s="250"/>
+      <c r="H43" s="318"/>
+      <c r="I43" s="312"/>
       <c r="K43" s="247" t="s">
         <v>1397</v>
       </c>
@@ -11407,15 +11428,15 @@
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C44" s="254"/>
-      <c r="D44" s="257"/>
-      <c r="E44" s="257"/>
-      <c r="F44" s="257"/>
+      <c r="C44" s="316"/>
+      <c r="D44" s="319"/>
+      <c r="E44" s="319"/>
+      <c r="F44" s="319"/>
       <c r="G44" s="22" t="s">
         <v>1378</v>
       </c>
-      <c r="H44" s="257"/>
-      <c r="I44" s="251"/>
+      <c r="H44" s="319"/>
+      <c r="I44" s="313"/>
       <c r="K44" s="247" t="s">
         <v>1398</v>
       </c>
@@ -11702,6 +11723,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I29:I44"/>
+    <mergeCell ref="C27:C44"/>
+    <mergeCell ref="D31:D44"/>
+    <mergeCell ref="E30:E44"/>
+    <mergeCell ref="F29:F44"/>
+    <mergeCell ref="H31:H44"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="M4:M13"/>
     <mergeCell ref="M3:O3"/>
@@ -11711,12 +11738,6 @@
     <mergeCell ref="H5:H12"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I29:I44"/>
-    <mergeCell ref="C27:C44"/>
-    <mergeCell ref="D31:D44"/>
-    <mergeCell ref="E30:E44"/>
-    <mergeCell ref="F29:F44"/>
-    <mergeCell ref="H31:H44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="41" orientation="landscape" r:id="rId1"/>
@@ -11744,21 +11765,21 @@
   <sheetData>
     <row r="2" spans="3:16" ht="15.75" thickBot="1"/>
     <row r="3" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C3" s="296" t="s">
+      <c r="C3" s="286" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="297"/>
-      <c r="E3" s="298"/>
-      <c r="I3" s="296" t="s">
+      <c r="D3" s="287"/>
+      <c r="E3" s="288"/>
+      <c r="I3" s="286" t="s">
         <v>746</v>
       </c>
-      <c r="J3" s="297"/>
-      <c r="K3" s="322"/>
-      <c r="N3" s="306" t="s">
+      <c r="J3" s="287"/>
+      <c r="K3" s="330"/>
+      <c r="N3" s="292" t="s">
         <v>455</v>
       </c>
-      <c r="O3" s="307"/>
-      <c r="P3" s="315"/>
+      <c r="O3" s="293"/>
+      <c r="P3" s="323"/>
     </row>
     <row r="4" spans="3:16" ht="15.75" thickBot="1">
       <c r="C4" s="192"/>
@@ -11784,7 +11805,7 @@
       </c>
     </row>
     <row r="5" spans="3:16">
-      <c r="C5" s="319" t="s">
+      <c r="C5" s="327" t="s">
         <v>1265</v>
       </c>
       <c r="D5" s="185" t="s">
@@ -11793,7 +11814,7 @@
       <c r="E5" s="185" t="s">
         <v>327</v>
       </c>
-      <c r="I5" s="277" t="s">
+      <c r="I5" s="267" t="s">
         <v>1265</v>
       </c>
       <c r="J5" s="194" t="s">
@@ -11802,7 +11823,7 @@
       <c r="K5" s="12" t="s">
         <v>1282</v>
       </c>
-      <c r="N5" s="319" t="s">
+      <c r="N5" s="327" t="s">
         <v>1265</v>
       </c>
       <c r="O5" s="187" t="s">
@@ -11813,21 +11834,21 @@
       </c>
     </row>
     <row r="6" spans="3:16">
-      <c r="C6" s="320"/>
+      <c r="C6" s="328"/>
       <c r="D6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>239</v>
       </c>
-      <c r="I6" s="278"/>
+      <c r="I6" s="268"/>
       <c r="J6" s="13" t="s">
         <v>1277</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>1283</v>
       </c>
-      <c r="N6" s="320"/>
+      <c r="N6" s="328"/>
       <c r="O6" s="81" t="s">
         <v>503</v>
       </c>
@@ -11836,21 +11857,21 @@
       </c>
     </row>
     <row r="7" spans="3:16">
-      <c r="C7" s="320"/>
+      <c r="C7" s="328"/>
       <c r="D7" s="183" t="s">
         <v>247</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>248</v>
       </c>
-      <c r="I7" s="278"/>
+      <c r="I7" s="268"/>
       <c r="J7" s="13" t="s">
         <v>1278</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="N7" s="320"/>
+      <c r="N7" s="328"/>
       <c r="O7" s="81" t="s">
         <v>502</v>
       </c>
@@ -11859,21 +11880,21 @@
       </c>
     </row>
     <row r="8" spans="3:16">
-      <c r="C8" s="320"/>
+      <c r="C8" s="328"/>
       <c r="D8" s="183" t="s">
         <v>276</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>277</v>
       </c>
-      <c r="I8" s="278"/>
+      <c r="I8" s="268"/>
       <c r="J8" s="13" t="s">
         <v>1279</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="N8" s="320"/>
+      <c r="N8" s="328"/>
       <c r="O8" s="81" t="s">
         <v>1287</v>
       </c>
@@ -11882,21 +11903,21 @@
       </c>
     </row>
     <row r="9" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C9" s="321"/>
+      <c r="C9" s="329"/>
       <c r="D9" s="184" t="s">
         <v>280</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="I9" s="278"/>
+      <c r="I9" s="268"/>
       <c r="J9" s="13" t="s">
         <v>1280</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="N9" s="321"/>
+      <c r="N9" s="329"/>
       <c r="O9" s="188" t="s">
         <v>1288</v>
       </c>
@@ -11905,7 +11926,7 @@
       </c>
     </row>
     <row r="10" spans="3:16">
-      <c r="C10" s="319" t="s">
+      <c r="C10" s="327" t="s">
         <v>1266</v>
       </c>
       <c r="D10" s="190" t="s">
@@ -11914,14 +11935,14 @@
       <c r="E10" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="I10" s="278"/>
+      <c r="I10" s="268"/>
       <c r="J10" s="13" t="s">
         <v>1281</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>1285</v>
       </c>
-      <c r="N10" s="316" t="s">
+      <c r="N10" s="324" t="s">
         <v>1266</v>
       </c>
       <c r="O10" s="187" t="s">
@@ -11932,21 +11953,21 @@
       </c>
     </row>
     <row r="11" spans="3:16">
-      <c r="C11" s="320"/>
+      <c r="C11" s="328"/>
       <c r="D11" s="81" t="s">
         <v>307</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>1110</v>
       </c>
-      <c r="I11" s="278"/>
+      <c r="I11" s="268"/>
       <c r="J11" s="13" t="s">
         <v>111</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="N11" s="317"/>
+      <c r="N11" s="325"/>
       <c r="O11" s="81" t="s">
         <v>1290</v>
       </c>
@@ -11955,21 +11976,21 @@
       </c>
     </row>
     <row r="12" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C12" s="320"/>
+      <c r="C12" s="328"/>
       <c r="D12" s="81" t="s">
         <v>314</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="I12" s="279"/>
+      <c r="I12" s="269"/>
       <c r="J12" s="21" t="s">
         <v>114</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="N12" s="317"/>
+      <c r="N12" s="325"/>
       <c r="O12" s="81" t="s">
         <v>1291</v>
       </c>
@@ -11978,14 +11999,14 @@
       </c>
     </row>
     <row r="13" spans="3:16">
-      <c r="C13" s="320"/>
+      <c r="C13" s="328"/>
       <c r="D13" s="81" t="s">
         <v>336</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>1267</v>
       </c>
-      <c r="I13" s="317" t="s">
+      <c r="I13" s="325" t="s">
         <v>1266</v>
       </c>
       <c r="J13" s="197" t="s">
@@ -11994,7 +12015,7 @@
       <c r="K13" s="168" t="s">
         <v>762</v>
       </c>
-      <c r="N13" s="317"/>
+      <c r="N13" s="325"/>
       <c r="O13" s="81" t="s">
         <v>1292</v>
       </c>
@@ -12003,21 +12024,21 @@
       </c>
     </row>
     <row r="14" spans="3:16">
-      <c r="C14" s="320"/>
+      <c r="C14" s="328"/>
       <c r="D14" s="81" t="s">
         <v>339</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>1268</v>
       </c>
-      <c r="I14" s="317"/>
+      <c r="I14" s="325"/>
       <c r="J14" s="24" t="s">
         <v>800</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>801</v>
       </c>
-      <c r="N14" s="317"/>
+      <c r="N14" s="325"/>
       <c r="O14" s="81" t="s">
         <v>1293</v>
       </c>
@@ -12026,21 +12047,21 @@
       </c>
     </row>
     <row r="15" spans="3:16">
-      <c r="C15" s="320"/>
+      <c r="C15" s="328"/>
       <c r="D15" s="81" t="s">
         <v>340</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>1269</v>
       </c>
-      <c r="I15" s="317"/>
+      <c r="I15" s="325"/>
       <c r="J15" s="24" t="s">
         <v>813</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="N15" s="317"/>
+      <c r="N15" s="325"/>
       <c r="O15" s="81" t="s">
         <v>1294</v>
       </c>
@@ -12049,21 +12070,21 @@
       </c>
     </row>
     <row r="16" spans="3:16">
-      <c r="C16" s="320"/>
+      <c r="C16" s="328"/>
       <c r="D16" s="81" t="s">
         <v>341</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="I16" s="317"/>
+      <c r="I16" s="325"/>
       <c r="J16" s="24" t="s">
         <v>807</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>1274</v>
       </c>
-      <c r="N16" s="317"/>
+      <c r="N16" s="325"/>
       <c r="O16" s="81" t="s">
         <v>1295</v>
       </c>
@@ -12072,21 +12093,21 @@
       </c>
     </row>
     <row r="17" spans="3:16">
-      <c r="C17" s="320"/>
+      <c r="C17" s="328"/>
       <c r="D17" s="81" t="s">
         <v>350</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>983</v>
       </c>
-      <c r="I17" s="317"/>
+      <c r="I17" s="325"/>
       <c r="J17" s="24" t="s">
         <v>769</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="N17" s="317"/>
+      <c r="N17" s="325"/>
       <c r="O17" s="81" t="s">
         <v>1299</v>
       </c>
@@ -12095,21 +12116,21 @@
       </c>
     </row>
     <row r="18" spans="3:16">
-      <c r="C18" s="320"/>
+      <c r="C18" s="328"/>
       <c r="D18" s="81" t="s">
         <v>353</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>1270</v>
       </c>
-      <c r="I18" s="317"/>
+      <c r="I18" s="325"/>
       <c r="J18" s="24" t="s">
         <v>763</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="N18" s="317"/>
+      <c r="N18" s="325"/>
       <c r="O18" s="81" t="s">
         <v>1300</v>
       </c>
@@ -12118,21 +12139,21 @@
       </c>
     </row>
     <row r="19" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C19" s="320"/>
+      <c r="C19" s="328"/>
       <c r="D19" s="81" t="s">
         <v>354</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="I19" s="317"/>
+      <c r="I19" s="325"/>
       <c r="J19" s="24" t="s">
         <v>66</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>779</v>
       </c>
-      <c r="N19" s="318"/>
+      <c r="N19" s="326"/>
       <c r="O19" s="188" t="s">
         <v>492</v>
       </c>
@@ -12141,14 +12162,14 @@
       </c>
     </row>
     <row r="20" spans="3:16">
-      <c r="C20" s="320"/>
+      <c r="C20" s="328"/>
       <c r="D20" s="81" t="s">
         <v>356</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>1273</v>
       </c>
-      <c r="I20" s="317"/>
+      <c r="I20" s="325"/>
       <c r="J20" s="24" t="s">
         <v>784</v>
       </c>
@@ -12157,14 +12178,14 @@
       </c>
     </row>
     <row r="21" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C21" s="320"/>
+      <c r="C21" s="328"/>
       <c r="D21" s="81" t="s">
         <v>359</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>1272</v>
       </c>
-      <c r="I21" s="318"/>
+      <c r="I21" s="326"/>
       <c r="J21" s="27" t="s">
         <v>786</v>
       </c>
@@ -12173,7 +12194,7 @@
       </c>
     </row>
     <row r="22" spans="3:16">
-      <c r="C22" s="320"/>
+      <c r="C22" s="328"/>
       <c r="D22" s="81" t="s">
         <v>370</v>
       </c>
@@ -12182,7 +12203,7 @@
       </c>
     </row>
     <row r="23" spans="3:16">
-      <c r="C23" s="320"/>
+      <c r="C23" s="328"/>
       <c r="D23" s="81" t="s">
         <v>372</v>
       </c>
@@ -12191,7 +12212,7 @@
       </c>
     </row>
     <row r="24" spans="3:16">
-      <c r="C24" s="320"/>
+      <c r="C24" s="328"/>
       <c r="D24" s="81" t="s">
         <v>382</v>
       </c>
@@ -12200,7 +12221,7 @@
       </c>
     </row>
     <row r="25" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C25" s="321"/>
+      <c r="C25" s="329"/>
       <c r="D25" s="188" t="s">
         <v>386</v>
       </c>
@@ -12215,16 +12236,16 @@
     </row>
     <row r="28" spans="3:16" ht="15.75" thickBot="1"/>
     <row r="29" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C29" s="296" t="s">
+      <c r="C29" s="286" t="s">
         <v>1307</v>
       </c>
-      <c r="D29" s="297"/>
-      <c r="E29" s="298"/>
-      <c r="I29" s="296" t="s">
+      <c r="D29" s="287"/>
+      <c r="E29" s="288"/>
+      <c r="I29" s="286" t="s">
         <v>1309</v>
       </c>
-      <c r="J29" s="297"/>
-      <c r="K29" s="298"/>
+      <c r="J29" s="287"/>
+      <c r="K29" s="288"/>
     </row>
     <row r="30" spans="3:16" ht="15.75" thickBot="1">
       <c r="C30" s="87"/>
@@ -12243,7 +12264,7 @@
       </c>
     </row>
     <row r="31" spans="3:16" ht="30">
-      <c r="C31" s="277" t="s">
+      <c r="C31" s="267" t="s">
         <v>1265</v>
       </c>
       <c r="D31" s="200" t="s">
@@ -12253,7 +12274,7 @@
         <v>327</v>
       </c>
       <c r="F31" s="193"/>
-      <c r="I31" s="319" t="s">
+      <c r="I31" s="327" t="s">
         <v>1265</v>
       </c>
       <c r="J31" s="209" t="s">
@@ -12264,7 +12285,7 @@
       </c>
     </row>
     <row r="32" spans="3:16" ht="45">
-      <c r="C32" s="278"/>
+      <c r="C32" s="268"/>
       <c r="D32" s="199" t="s">
         <v>698</v>
       </c>
@@ -12272,7 +12293,7 @@
         <v>248</v>
       </c>
       <c r="F32" s="193"/>
-      <c r="I32" s="320"/>
+      <c r="I32" s="328"/>
       <c r="J32" s="203" t="s">
         <v>87</v>
       </c>
@@ -12281,7 +12302,7 @@
       </c>
     </row>
     <row r="33" spans="3:11" ht="45">
-      <c r="C33" s="278"/>
+      <c r="C33" s="268"/>
       <c r="D33" s="199" t="s">
         <v>699</v>
       </c>
@@ -12289,7 +12310,7 @@
         <v>239</v>
       </c>
       <c r="F33" s="193"/>
-      <c r="I33" s="320"/>
+      <c r="I33" s="328"/>
       <c r="J33" s="203" t="s">
         <v>89</v>
       </c>
@@ -12298,7 +12319,7 @@
       </c>
     </row>
     <row r="34" spans="3:11" ht="45">
-      <c r="C34" s="278"/>
+      <c r="C34" s="268"/>
       <c r="D34" s="199" t="s">
         <v>714</v>
       </c>
@@ -12306,7 +12327,7 @@
         <v>283</v>
       </c>
       <c r="F34" s="193"/>
-      <c r="I34" s="320"/>
+      <c r="I34" s="328"/>
       <c r="J34" s="203" t="s">
         <v>73</v>
       </c>
@@ -12315,7 +12336,7 @@
       </c>
     </row>
     <row r="35" spans="3:11" ht="45">
-      <c r="C35" s="278"/>
+      <c r="C35" s="268"/>
       <c r="D35" s="199" t="s">
         <v>715</v>
       </c>
@@ -12323,7 +12344,7 @@
         <v>271</v>
       </c>
       <c r="F35" s="193"/>
-      <c r="I35" s="320"/>
+      <c r="I35" s="328"/>
       <c r="J35" s="203" t="s">
         <v>105</v>
       </c>
@@ -12332,7 +12353,7 @@
       </c>
     </row>
     <row r="36" spans="3:11" ht="45">
-      <c r="C36" s="278"/>
+      <c r="C36" s="268"/>
       <c r="D36" s="199" t="s">
         <v>659</v>
       </c>
@@ -12340,7 +12361,7 @@
         <v>250</v>
       </c>
       <c r="F36" s="193"/>
-      <c r="I36" s="320"/>
+      <c r="I36" s="328"/>
       <c r="J36" s="203" t="s">
         <v>41</v>
       </c>
@@ -12349,7 +12370,7 @@
       </c>
     </row>
     <row r="37" spans="3:11" ht="45">
-      <c r="C37" s="278"/>
+      <c r="C37" s="268"/>
       <c r="D37" s="199" t="s">
         <v>716</v>
       </c>
@@ -12357,7 +12378,7 @@
         <v>717</v>
       </c>
       <c r="F37" s="193"/>
-      <c r="I37" s="320"/>
+      <c r="I37" s="328"/>
       <c r="J37" s="203" t="s">
         <v>108</v>
       </c>
@@ -12366,7 +12387,7 @@
       </c>
     </row>
     <row r="38" spans="3:11" ht="45">
-      <c r="C38" s="278"/>
+      <c r="C38" s="268"/>
       <c r="D38" s="199" t="s">
         <v>718</v>
       </c>
@@ -12374,7 +12395,7 @@
         <v>719</v>
       </c>
       <c r="F38" s="193"/>
-      <c r="I38" s="320"/>
+      <c r="I38" s="328"/>
       <c r="J38" s="203" t="s">
         <v>51</v>
       </c>
@@ -12383,7 +12404,7 @@
       </c>
     </row>
     <row r="39" spans="3:11" ht="30">
-      <c r="C39" s="278"/>
+      <c r="C39" s="268"/>
       <c r="D39" s="199" t="s">
         <v>720</v>
       </c>
@@ -12391,7 +12412,7 @@
         <v>338</v>
       </c>
       <c r="F39" s="193"/>
-      <c r="I39" s="320"/>
+      <c r="I39" s="328"/>
       <c r="J39" s="203" t="s">
         <v>56</v>
       </c>
@@ -12400,7 +12421,7 @@
       </c>
     </row>
     <row r="40" spans="3:11" ht="30">
-      <c r="C40" s="278"/>
+      <c r="C40" s="268"/>
       <c r="D40" s="199" t="s">
         <v>721</v>
       </c>
@@ -12408,7 +12429,7 @@
         <v>292</v>
       </c>
       <c r="F40" s="193"/>
-      <c r="I40" s="320"/>
+      <c r="I40" s="328"/>
       <c r="J40" s="203" t="s">
         <v>125</v>
       </c>
@@ -12417,7 +12438,7 @@
       </c>
     </row>
     <row r="41" spans="3:11" ht="45">
-      <c r="C41" s="278"/>
+      <c r="C41" s="268"/>
       <c r="D41" s="199" t="s">
         <v>722</v>
       </c>
@@ -12425,7 +12446,7 @@
         <v>723</v>
       </c>
       <c r="F41" s="193"/>
-      <c r="I41" s="320"/>
+      <c r="I41" s="328"/>
       <c r="J41" s="203" t="s">
         <v>63</v>
       </c>
@@ -12434,7 +12455,7 @@
       </c>
     </row>
     <row r="42" spans="3:11" ht="45.75" thickBot="1">
-      <c r="C42" s="279"/>
+      <c r="C42" s="269"/>
       <c r="D42" s="201" t="s">
         <v>674</v>
       </c>
@@ -12442,7 +12463,7 @@
         <v>513</v>
       </c>
       <c r="F42" s="193"/>
-      <c r="I42" s="320"/>
+      <c r="I42" s="328"/>
       <c r="J42" s="203" t="s">
         <v>13</v>
       </c>
@@ -12451,7 +12472,7 @@
       </c>
     </row>
     <row r="43" spans="3:11" ht="30">
-      <c r="C43" s="319" t="s">
+      <c r="C43" s="327" t="s">
         <v>1266</v>
       </c>
       <c r="D43" s="187" t="s">
@@ -12460,7 +12481,7 @@
       <c r="E43" s="168" t="s">
         <v>644</v>
       </c>
-      <c r="I43" s="320"/>
+      <c r="I43" s="328"/>
       <c r="J43" s="203" t="s">
         <v>111</v>
       </c>
@@ -12469,14 +12490,14 @@
       </c>
     </row>
     <row r="44" spans="3:11" ht="30.75" thickBot="1">
-      <c r="C44" s="320"/>
+      <c r="C44" s="328"/>
       <c r="D44" s="81" t="s">
         <v>679</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>680</v>
       </c>
-      <c r="I44" s="321"/>
+      <c r="I44" s="329"/>
       <c r="J44" s="206" t="s">
         <v>114</v>
       </c>
@@ -12485,14 +12506,14 @@
       </c>
     </row>
     <row r="45" spans="3:11" ht="30">
-      <c r="C45" s="320"/>
+      <c r="C45" s="328"/>
       <c r="D45" s="81" t="s">
         <v>645</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="I45" s="320" t="s">
+      <c r="I45" s="328" t="s">
         <v>1266</v>
       </c>
       <c r="J45" s="207" t="s">
@@ -12503,14 +12524,14 @@
       </c>
     </row>
     <row r="46" spans="3:11" ht="30">
-      <c r="C46" s="320"/>
+      <c r="C46" s="328"/>
       <c r="D46" s="81" t="s">
         <v>653</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="I46" s="320"/>
+      <c r="I46" s="328"/>
       <c r="J46" s="203" t="s">
         <v>23</v>
       </c>
@@ -12519,14 +12540,14 @@
       </c>
     </row>
     <row r="47" spans="3:11" ht="30">
-      <c r="C47" s="320"/>
+      <c r="C47" s="328"/>
       <c r="D47" s="81" t="s">
         <v>656</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="I47" s="320"/>
+      <c r="I47" s="328"/>
       <c r="J47" s="203" t="s">
         <v>38</v>
       </c>
@@ -12535,14 +12556,14 @@
       </c>
     </row>
     <row r="48" spans="3:11" ht="30">
-      <c r="C48" s="320"/>
+      <c r="C48" s="328"/>
       <c r="D48" s="81" t="s">
         <v>659</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>577</v>
       </c>
-      <c r="I48" s="320"/>
+      <c r="I48" s="328"/>
       <c r="J48" s="203" t="s">
         <v>48</v>
       </c>
@@ -12551,14 +12572,14 @@
       </c>
     </row>
     <row r="49" spans="3:11" ht="30">
-      <c r="C49" s="320"/>
+      <c r="C49" s="328"/>
       <c r="D49" s="81" t="s">
         <v>664</v>
       </c>
       <c r="E49" s="15" t="s">
         <v>610</v>
       </c>
-      <c r="I49" s="320"/>
+      <c r="I49" s="328"/>
       <c r="J49" s="203" t="s">
         <v>41</v>
       </c>
@@ -12567,14 +12588,14 @@
       </c>
     </row>
     <row r="50" spans="3:11" ht="30">
-      <c r="C50" s="320"/>
+      <c r="C50" s="328"/>
       <c r="D50" s="81" t="s">
         <v>665</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="I50" s="320"/>
+      <c r="I50" s="328"/>
       <c r="J50" s="203" t="s">
         <v>32</v>
       </c>
@@ -12583,14 +12604,14 @@
       </c>
     </row>
     <row r="51" spans="3:11" ht="45">
-      <c r="C51" s="320"/>
+      <c r="C51" s="328"/>
       <c r="D51" s="81" t="s">
         <v>666</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="I51" s="320"/>
+      <c r="I51" s="328"/>
       <c r="J51" s="203" t="s">
         <v>51</v>
       </c>
@@ -12599,14 +12620,14 @@
       </c>
     </row>
     <row r="52" spans="3:11" ht="30">
-      <c r="C52" s="320"/>
+      <c r="C52" s="328"/>
       <c r="D52" s="81" t="s">
         <v>667</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="I52" s="320"/>
+      <c r="I52" s="328"/>
       <c r="J52" s="203" t="s">
         <v>73</v>
       </c>
@@ -12615,14 +12636,14 @@
       </c>
     </row>
     <row r="53" spans="3:11" ht="30">
-      <c r="C53" s="320"/>
+      <c r="C53" s="328"/>
       <c r="D53" s="81" t="s">
         <v>668</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>1308</v>
       </c>
-      <c r="I53" s="320"/>
+      <c r="I53" s="328"/>
       <c r="J53" s="203" t="s">
         <v>56</v>
       </c>
@@ -12631,14 +12652,14 @@
       </c>
     </row>
     <row r="54" spans="3:11" ht="30">
-      <c r="C54" s="320"/>
+      <c r="C54" s="328"/>
       <c r="D54" s="81" t="s">
         <v>672</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="I54" s="320"/>
+      <c r="I54" s="328"/>
       <c r="J54" s="203" t="s">
         <v>63</v>
       </c>
@@ -12647,14 +12668,14 @@
       </c>
     </row>
     <row r="55" spans="3:11" ht="15.75" thickBot="1">
-      <c r="C55" s="321"/>
+      <c r="C55" s="329"/>
       <c r="D55" s="188" t="s">
         <v>674</v>
       </c>
       <c r="E55" s="23" t="s">
         <v>513</v>
       </c>
-      <c r="I55" s="320"/>
+      <c r="I55" s="328"/>
       <c r="J55" s="203" t="s">
         <v>66</v>
       </c>
@@ -12663,7 +12684,7 @@
       </c>
     </row>
     <row r="56" spans="3:11" ht="45.75" thickBot="1">
-      <c r="I56" s="321"/>
+      <c r="I56" s="329"/>
       <c r="J56" s="206" t="s">
         <v>13</v>
       </c>
@@ -12676,16 +12697,16 @@
     </row>
     <row r="60" spans="3:11" ht="15.75" thickBot="1"/>
     <row r="61" spans="3:11" ht="15.75" thickBot="1">
-      <c r="C61" s="306" t="s">
+      <c r="C61" s="292" t="s">
         <v>1449</v>
       </c>
-      <c r="D61" s="307"/>
-      <c r="E61" s="307"/>
-      <c r="F61" s="307"/>
-      <c r="G61" s="307"/>
-      <c r="H61" s="307"/>
-      <c r="I61" s="307"/>
-      <c r="J61" s="308"/>
+      <c r="D61" s="293"/>
+      <c r="E61" s="293"/>
+      <c r="F61" s="293"/>
+      <c r="G61" s="293"/>
+      <c r="H61" s="293"/>
+      <c r="I61" s="293"/>
+      <c r="J61" s="294"/>
       <c r="K61" s="7"/>
     </row>
     <row r="62" spans="3:11">
@@ -12715,7 +12736,7 @@
       </c>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="252"/>
+      <c r="C63" s="314"/>
       <c r="D63" s="25" t="s">
         <v>1256</v>
       </c>
@@ -12739,7 +12760,7 @@
       </c>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="253"/>
+      <c r="C64" s="315"/>
       <c r="D64" s="25" t="s">
         <v>1358</v>
       </c>
@@ -12763,88 +12784,88 @@
       </c>
     </row>
     <row r="65" spans="3:10">
-      <c r="C65" s="253"/>
+      <c r="C65" s="315"/>
       <c r="D65" s="25" t="s">
         <v>1359</v>
       </c>
       <c r="E65" s="25" t="s">
         <v>1163</v>
       </c>
-      <c r="F65" s="255"/>
+      <c r="F65" s="317"/>
       <c r="G65" s="14" t="s">
         <v>1409</v>
       </c>
       <c r="H65" s="14" t="s">
         <v>1346</v>
       </c>
-      <c r="I65" s="255"/>
-      <c r="J65" s="323"/>
+      <c r="I65" s="317"/>
+      <c r="J65" s="320"/>
     </row>
     <row r="66" spans="3:10">
-      <c r="C66" s="253"/>
+      <c r="C66" s="315"/>
       <c r="D66" s="25" t="s">
         <v>1360</v>
       </c>
-      <c r="E66" s="255"/>
-      <c r="F66" s="256"/>
+      <c r="E66" s="317"/>
+      <c r="F66" s="318"/>
       <c r="G66" s="14" t="s">
         <v>1410</v>
       </c>
       <c r="H66" s="14" t="s">
         <v>1339</v>
       </c>
-      <c r="I66" s="256"/>
-      <c r="J66" s="324"/>
+      <c r="I66" s="318"/>
+      <c r="J66" s="321"/>
     </row>
     <row r="67" spans="3:10">
-      <c r="C67" s="253"/>
-      <c r="D67" s="255"/>
-      <c r="E67" s="256"/>
-      <c r="F67" s="256"/>
+      <c r="C67" s="315"/>
+      <c r="D67" s="317"/>
+      <c r="E67" s="318"/>
+      <c r="F67" s="318"/>
       <c r="G67" s="14" t="s">
         <v>1343</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="I67" s="256"/>
-      <c r="J67" s="324"/>
+      <c r="I67" s="318"/>
+      <c r="J67" s="321"/>
     </row>
     <row r="68" spans="3:10">
-      <c r="C68" s="253"/>
-      <c r="D68" s="256"/>
-      <c r="E68" s="256"/>
-      <c r="F68" s="256"/>
+      <c r="C68" s="315"/>
+      <c r="D68" s="318"/>
+      <c r="E68" s="318"/>
+      <c r="F68" s="318"/>
       <c r="G68" s="14" t="s">
         <v>1345</v>
       </c>
-      <c r="H68" s="255"/>
-      <c r="I68" s="256"/>
-      <c r="J68" s="324"/>
+      <c r="H68" s="317"/>
+      <c r="I68" s="318"/>
+      <c r="J68" s="321"/>
     </row>
     <row r="69" spans="3:10">
-      <c r="C69" s="253"/>
-      <c r="D69" s="256"/>
-      <c r="E69" s="256"/>
-      <c r="F69" s="256"/>
+      <c r="C69" s="315"/>
+      <c r="D69" s="318"/>
+      <c r="E69" s="318"/>
+      <c r="F69" s="318"/>
       <c r="G69" s="14" t="s">
         <v>1411</v>
       </c>
-      <c r="H69" s="256"/>
-      <c r="I69" s="256"/>
-      <c r="J69" s="324"/>
+      <c r="H69" s="318"/>
+      <c r="I69" s="318"/>
+      <c r="J69" s="321"/>
     </row>
     <row r="70" spans="3:10" ht="15.75" thickBot="1">
-      <c r="C70" s="254"/>
-      <c r="D70" s="257"/>
-      <c r="E70" s="257"/>
-      <c r="F70" s="257"/>
+      <c r="C70" s="316"/>
+      <c r="D70" s="319"/>
+      <c r="E70" s="319"/>
+      <c r="F70" s="319"/>
       <c r="G70" s="22" t="s">
         <v>1344</v>
       </c>
-      <c r="H70" s="257"/>
-      <c r="I70" s="257"/>
-      <c r="J70" s="325"/>
+      <c r="H70" s="319"/>
+      <c r="I70" s="319"/>
+      <c r="J70" s="322"/>
     </row>
     <row r="71" spans="3:10">
       <c r="E71" s="189"/>
@@ -13405,13 +13426,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="I65:I70"/>
-    <mergeCell ref="J65:J70"/>
-    <mergeCell ref="C63:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F65:F70"/>
-    <mergeCell ref="H68:H70"/>
     <mergeCell ref="C61:J61"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="N10:N19"/>
@@ -13428,6 +13442,13 @@
     <mergeCell ref="I45:I56"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C31:C42"/>
+    <mergeCell ref="I65:I70"/>
+    <mergeCell ref="J65:J70"/>
+    <mergeCell ref="C63:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F65:F70"/>
+    <mergeCell ref="H68:H70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13892,18 +13913,18 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC7C67B-1E6D-408B-98E4-808E3DC70BD1}">
-  <dimension ref="E3:H17"/>
+  <dimension ref="E3:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="5:8" ht="15.75" thickBot="1">
       <c r="E3" s="7" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="4" spans="5:8" ht="15.75" thickBot="1">
@@ -13914,10 +13935,10 @@
         <v>1495</v>
       </c>
       <c r="G4" s="172" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="H4" s="173" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="5" spans="5:8" ht="30">
@@ -13927,11 +13948,11 @@
       <c r="F5" s="11" t="s">
         <v>1497</v>
       </c>
-      <c r="G5" s="326" t="s">
-        <v>1508</v>
-      </c>
-      <c r="H5" s="328" t="s">
-        <v>1504</v>
+      <c r="G5" s="249" t="s">
+        <v>1506</v>
+      </c>
+      <c r="H5" s="251" t="s">
+        <v>1503</v>
       </c>
     </row>
     <row r="6" spans="5:8" ht="30">
@@ -13939,13 +13960,13 @@
         <v>1498</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="G6" s="166" t="s">
-        <v>1509</v>
-      </c>
-      <c r="H6" s="329" t="s">
-        <v>1503</v>
+        <v>1507</v>
+      </c>
+      <c r="H6" s="252" t="s">
+        <v>1502</v>
       </c>
     </row>
     <row r="7" spans="5:8" ht="30.75" thickBot="1">
@@ -13953,18 +13974,18 @@
         <v>1499</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1500</v>
-      </c>
-      <c r="G7" s="327" t="s">
-        <v>1502</v>
-      </c>
-      <c r="H7" s="330" t="s">
-        <v>1505</v>
+        <v>1523</v>
+      </c>
+      <c r="G7" s="250" t="s">
+        <v>1501</v>
+      </c>
+      <c r="H7" s="253" t="s">
+        <v>1524</v>
       </c>
     </row>
     <row r="11" spans="5:8">
       <c r="E11" s="7" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="12" spans="5:8" ht="15.75" thickBot="1"/>
@@ -13976,70 +13997,147 @@
         <v>1495</v>
       </c>
       <c r="G13" s="223" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="H13" s="224" t="s">
-        <v>1506</v>
-      </c>
-    </row>
-    <row r="14" spans="5:8" ht="45">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="14" spans="5:8" ht="48.75" customHeight="1">
       <c r="E14" s="13" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>1497</v>
       </c>
       <c r="G14" s="166" t="s">
-        <v>1518</v>
-      </c>
-      <c r="H14" s="331" t="s">
-        <v>1522</v>
+        <v>1516</v>
+      </c>
+      <c r="H14" s="252" t="s">
+        <v>1520</v>
       </c>
     </row>
     <row r="15" spans="5:8" ht="45">
       <c r="E15" s="13" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="G15" s="166" t="s">
-        <v>1519</v>
-      </c>
-      <c r="H15" s="329" t="s">
-        <v>1523</v>
+        <v>1517</v>
+      </c>
+      <c r="H15" s="252" t="s">
+        <v>1521</v>
       </c>
     </row>
     <row r="16" spans="5:8" ht="30">
       <c r="E16" s="13" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G16" s="166" t="s">
+        <v>1518</v>
+      </c>
+      <c r="H16" s="252" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" ht="30.75" thickBot="1">
+      <c r="E17" s="21" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G17" s="250" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H17" s="253" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8">
+      <c r="E19" s="331" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" ht="15.75" thickBot="1"/>
+    <row r="21" spans="5:8">
+      <c r="E21" s="222" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F21" s="223" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G21" s="223" t="s">
+        <v>1505</v>
+      </c>
+      <c r="H21" s="224" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" ht="45">
+      <c r="E22" s="13" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G22" s="166" t="s">
+        <v>1531</v>
+      </c>
+      <c r="H22" s="252" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="23" spans="5:8" ht="45">
+      <c r="E23" s="13" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>1514</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>1517</v>
-      </c>
-      <c r="G16" s="166" t="s">
-        <v>1520</v>
-      </c>
-      <c r="H16" s="331" t="s">
-        <v>1524</v>
-      </c>
-    </row>
-    <row r="17" spans="5:8" ht="30.75" thickBot="1">
-      <c r="E17" s="332" t="s">
+      <c r="G23" s="332" t="s">
+        <v>1532</v>
+      </c>
+      <c r="H23" s="252" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="24" spans="5:8" ht="30">
+      <c r="E24" s="13" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>1515</v>
       </c>
-      <c r="F17" s="333" t="s">
-        <v>1500</v>
-      </c>
-      <c r="G17" s="327" t="s">
-        <v>1521</v>
-      </c>
-      <c r="H17" s="330" t="s">
+      <c r="G24" s="166" t="s">
+        <v>1518</v>
+      </c>
+      <c r="H24" s="252" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="25" spans="5:8" ht="30.75" thickBot="1">
+      <c r="E25" s="21" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G25" s="250" t="s">
+        <v>1533</v>
+      </c>
+      <c r="H25" s="253" t="s">
         <v>1525</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14065,11 +14163,11 @@
       <c r="C2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="271" t="s">
+      <c r="D2" s="260" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="272"/>
-      <c r="F2" s="273"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="262"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="3:10" ht="15.75" thickBot="1">
@@ -14209,11 +14307,11 @@
       <c r="F12" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="259" t="s">
+      <c r="H12" s="263" t="s">
         <v>224</v>
       </c>
-      <c r="I12" s="259"/>
-      <c r="J12" s="259"/>
+      <c r="I12" s="263"/>
+      <c r="J12" s="263"/>
     </row>
     <row r="13" spans="3:10">
       <c r="D13" s="36" t="s">
@@ -15888,11 +15986,11 @@
       <c r="C3" s="40" t="s">
         <v>894</v>
       </c>
-      <c r="D3" s="274" t="s">
+      <c r="D3" s="264" t="s">
         <v>948</v>
       </c>
-      <c r="E3" s="275"/>
-      <c r="F3" s="276"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="266"/>
       <c r="I3" s="7" t="s">
         <v>1017</v>
       </c>
@@ -16502,11 +16600,11 @@
       <c r="C2" s="41" t="s">
         <v>746</v>
       </c>
-      <c r="D2" s="259" t="s">
+      <c r="D2" s="263" t="s">
         <v>850</v>
       </c>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
       <c r="I2" s="7" t="s">
         <v>848</v>
       </c>
@@ -17101,7 +17199,7 @@
       </c>
     </row>
     <row r="60" spans="4:6">
-      <c r="D60" s="277" t="s">
+      <c r="D60" s="267" t="s">
         <v>1265</v>
       </c>
       <c r="E60" s="194" t="s">
@@ -17112,7 +17210,7 @@
       </c>
     </row>
     <row r="61" spans="4:6">
-      <c r="D61" s="278"/>
+      <c r="D61" s="268"/>
       <c r="E61" s="13" t="s">
         <v>1277</v>
       </c>
@@ -17121,7 +17219,7 @@
       </c>
     </row>
     <row r="62" spans="4:6">
-      <c r="D62" s="278"/>
+      <c r="D62" s="268"/>
       <c r="E62" s="13" t="s">
         <v>1278</v>
       </c>
@@ -17130,7 +17228,7 @@
       </c>
     </row>
     <row r="63" spans="4:6">
-      <c r="D63" s="278"/>
+      <c r="D63" s="268"/>
       <c r="E63" s="13" t="s">
         <v>1279</v>
       </c>
@@ -17139,7 +17237,7 @@
       </c>
     </row>
     <row r="64" spans="4:6">
-      <c r="D64" s="278"/>
+      <c r="D64" s="268"/>
       <c r="E64" s="13" t="s">
         <v>1280</v>
       </c>
@@ -17148,7 +17246,7 @@
       </c>
     </row>
     <row r="65" spans="4:6">
-      <c r="D65" s="278"/>
+      <c r="D65" s="268"/>
       <c r="E65" s="13" t="s">
         <v>1281</v>
       </c>
@@ -17157,7 +17255,7 @@
       </c>
     </row>
     <row r="66" spans="4:6">
-      <c r="D66" s="278"/>
+      <c r="D66" s="268"/>
       <c r="E66" s="13" t="s">
         <v>111</v>
       </c>
@@ -17166,7 +17264,7 @@
       </c>
     </row>
     <row r="67" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D67" s="279"/>
+      <c r="D67" s="269"/>
       <c r="E67" s="21" t="s">
         <v>114</v>
       </c>
@@ -17201,11 +17299,11 @@
       <c r="B3" s="40" t="s">
         <v>894</v>
       </c>
-      <c r="C3" s="274" t="s">
+      <c r="C3" s="264" t="s">
         <v>948</v>
       </c>
-      <c r="D3" s="275"/>
-      <c r="E3" s="276"/>
+      <c r="D3" s="265"/>
+      <c r="E3" s="266"/>
       <c r="H3" t="s">
         <v>953</v>
       </c>
@@ -17619,11 +17717,11 @@
       <c r="C3" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D3" s="271" t="s">
+      <c r="D3" s="260" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="272"/>
-      <c r="F3" s="273"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="262"/>
       <c r="H3" s="41" t="s">
         <v>456</v>
       </c>
@@ -17651,11 +17749,11 @@
     </row>
     <row r="5" spans="3:9" ht="15.75">
       <c r="C5" s="7"/>
-      <c r="D5" s="283" t="s">
+      <c r="D5" s="273" t="s">
         <v>458</v>
       </c>
-      <c r="E5" s="284"/>
-      <c r="F5" s="285"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="275"/>
       <c r="H5" s="44" t="s">
         <v>460</v>
       </c>
@@ -17759,11 +17857,11 @@
       <c r="F12" s="53"/>
     </row>
     <row r="13" spans="3:9" ht="15.75">
-      <c r="D13" s="283" t="s">
+      <c r="D13" s="273" t="s">
         <v>460</v>
       </c>
-      <c r="E13" s="284"/>
-      <c r="F13" s="285"/>
+      <c r="E13" s="274"/>
+      <c r="F13" s="275"/>
     </row>
     <row r="14" spans="3:9" ht="31.5">
       <c r="D14" s="54" t="s">
@@ -17965,11 +18063,11 @@
       <c r="F28" s="53"/>
     </row>
     <row r="29" spans="4:9" ht="15.75">
-      <c r="D29" s="286" t="s">
+      <c r="D29" s="276" t="s">
         <v>464</v>
       </c>
-      <c r="E29" s="287"/>
-      <c r="F29" s="288"/>
+      <c r="E29" s="277"/>
+      <c r="F29" s="278"/>
     </row>
     <row r="30" spans="4:9" ht="15.75">
       <c r="D30" s="103" t="s">
@@ -18087,11 +18185,11 @@
       <c r="F40" s="53"/>
     </row>
     <row r="41" spans="4:6" ht="15.75">
-      <c r="D41" s="280" t="s">
+      <c r="D41" s="270" t="s">
         <v>472</v>
       </c>
-      <c r="E41" s="281"/>
-      <c r="F41" s="282"/>
+      <c r="E41" s="271"/>
+      <c r="F41" s="272"/>
     </row>
     <row r="42" spans="4:6" ht="15.75">
       <c r="D42" s="46" t="s">
@@ -18225,11 +18323,11 @@
       <c r="F54" s="53"/>
     </row>
     <row r="55" spans="4:6" ht="15.75">
-      <c r="D55" s="280" t="s">
+      <c r="D55" s="270" t="s">
         <v>476</v>
       </c>
-      <c r="E55" s="281"/>
-      <c r="F55" s="282"/>
+      <c r="E55" s="271"/>
+      <c r="F55" s="272"/>
     </row>
     <row r="56" spans="4:6" ht="15.75">
       <c r="D56" s="61" t="s">
@@ -18311,11 +18409,11 @@
       <c r="B2" s="90" t="s">
         <v>894</v>
       </c>
-      <c r="C2" s="289" t="s">
+      <c r="C2" s="279" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="272"/>
-      <c r="E2" s="273"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="262"/>
       <c r="H2" s="59" t="s">
         <v>511</v>
       </c>
@@ -18569,11 +18667,11 @@
       <c r="C2" s="75" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="274" t="s">
+      <c r="D2" s="264" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="275"/>
-      <c r="F2" s="276"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="266"/>
       <c r="I2" t="s">
         <v>569</v>
       </c>
@@ -18967,11 +19065,11 @@
       <c r="C39" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D39" s="271" t="s">
+      <c r="D39" s="260" t="s">
         <v>1</v>
       </c>
-      <c r="E39" s="272"/>
-      <c r="F39" s="273"/>
+      <c r="E39" s="261"/>
+      <c r="F39" s="262"/>
       <c r="H39" t="s">
         <v>635</v>
       </c>
@@ -19369,11 +19467,11 @@
       <c r="C76" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D76" s="271" t="s">
+      <c r="D76" s="260" t="s">
         <v>1</v>
       </c>
-      <c r="E76" s="272"/>
-      <c r="F76" s="273"/>
+      <c r="E76" s="261"/>
+      <c r="F76" s="262"/>
       <c r="H76" t="s">
         <v>688</v>
       </c>
@@ -19786,11 +19884,11 @@
       <c r="C114" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D114" s="271" t="s">
+      <c r="D114" s="260" t="s">
         <v>1</v>
       </c>
-      <c r="E114" s="272"/>
-      <c r="F114" s="273"/>
+      <c r="E114" s="261"/>
+      <c r="F114" s="262"/>
       <c r="H114" s="2" t="s">
         <v>637</v>
       </c>
@@ -20122,11 +20220,11 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="293" t="s">
+      <c r="D3" s="283" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="294"/>
-      <c r="F3" s="295"/>
+      <c r="E3" s="284"/>
+      <c r="F3" s="285"/>
       <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
@@ -20145,11 +20243,11 @@
     </row>
     <row r="5" spans="3:9" ht="15.75" thickBot="1">
       <c r="C5" s="7"/>
-      <c r="D5" s="290" t="s">
+      <c r="D5" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="291"/>
-      <c r="F5" s="292"/>
+      <c r="E5" s="281"/>
+      <c r="F5" s="282"/>
       <c r="H5" s="8" t="s">
         <v>6</v>
       </c>
@@ -20399,11 +20497,11 @@
     </row>
     <row r="24" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="25" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D25" s="296" t="s">
+      <c r="D25" s="286" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="297"/>
-      <c r="F25" s="298"/>
+      <c r="E25" s="287"/>
+      <c r="F25" s="288"/>
     </row>
     <row r="26" spans="4:6">
       <c r="D26" s="110" t="s">
@@ -20638,11 +20736,11 @@
     </row>
     <row r="47" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="48" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D48" s="290" t="s">
+      <c r="D48" s="280" t="s">
         <v>1312</v>
       </c>
-      <c r="E48" s="291"/>
-      <c r="F48" s="292"/>
+      <c r="E48" s="281"/>
+      <c r="F48" s="282"/>
     </row>
     <row r="49" spans="4:6">
       <c r="D49" s="10" t="s">
@@ -20965,11 +21063,11 @@
     </row>
     <row r="78" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="79" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D79" s="299" t="s">
+      <c r="D79" s="289" t="s">
         <v>21</v>
       </c>
-      <c r="E79" s="300"/>
-      <c r="F79" s="301"/>
+      <c r="E79" s="290"/>
+      <c r="F79" s="291"/>
     </row>
     <row r="80" spans="4:6">
       <c r="D80" s="118" t="s">
@@ -21116,11 +21214,11 @@
     </row>
     <row r="93" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="94" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D94" s="299" t="s">
+      <c r="D94" s="289" t="s">
         <v>30</v>
       </c>
-      <c r="E94" s="300"/>
-      <c r="F94" s="301"/>
+      <c r="E94" s="290"/>
+      <c r="F94" s="291"/>
     </row>
     <row r="95" spans="4:6">
       <c r="D95" s="110" t="s">
@@ -21234,11 +21332,11 @@
     </row>
     <row r="105" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="106" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D106" s="290" t="s">
+      <c r="D106" s="280" t="s">
         <v>26</v>
       </c>
-      <c r="E106" s="291"/>
-      <c r="F106" s="292"/>
+      <c r="E106" s="281"/>
+      <c r="F106" s="282"/>
     </row>
     <row r="107" spans="4:6">
       <c r="D107" s="110" t="s">

--- a/Relatorio/APIS_detalhe_Campos_v23_06.xlsx
+++ b/Relatorio/APIS_detalhe_Campos_v23_06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ESTG 25_26\2S\ProjetoInformatico\Prototipo\Versoes\weatherSense\Relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B33971D-2925-49C5-86AE-D2A95760CE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822E9191-E502-4DC6-93AE-18B0118FB428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="14" xr2:uid="{E6E5DD2F-D0B6-44E9-B2EB-37380A5D374B}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3361" uniqueCount="1534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3361" uniqueCount="1538">
   <si>
     <t>Foreca</t>
   </si>
@@ -5649,12 +5649,6 @@
     <t>Registos históricos paginados</t>
   </si>
   <si>
-    <t>/data/observations/history?lat=39.735122&amp;lon=-8.821217&amp;variable=temperature&amp;range=24h</t>
-  </si>
-  <si>
-    <t>/data/observations/current?lat=39.7436&amp;lon=-8.8071</t>
-  </si>
-  <si>
     <t>Exemplo de pedido</t>
   </si>
   <si>
@@ -5703,24 +5697,9 @@
     <t>Registos históricos paginados das previsões terrestres</t>
   </si>
   <si>
-    <t>/data/forecast/terrestrial/current?lat=39.735122&amp;lon=-8.821217</t>
-  </si>
-  <si>
-    <t>/data/forecast/terrestrial/timeline?lat=39.735122&amp;lon=-8.821217&amp;provider=openmeteo&amp;hours=24</t>
-  </si>
-  <si>
-    <t>/data/forecast/terrestrial/history?lat=39.735122&amp;lon=-8.821217&amp;variable=temperature&amp;range=24h</t>
-  </si>
-  <si>
     <t>lat, lon, page, page_size, search,variable</t>
   </si>
   <si>
-    <t>/data/observations/records?lat=39.735122&amp;lon=-8.821217&amp;page=1&amp;page_size=10&amp;variable=temperature</t>
-  </si>
-  <si>
-    <t>/data/forecast/terrestrial/records?lat=39.735122&amp;lon=-8.821217&amp;page=1&amp;page_size=10&amp;variable=temperature</t>
-  </si>
-  <si>
     <t>PREV MARINE</t>
   </si>
   <si>
@@ -5743,6 +5722,39 @@
   </si>
   <si>
     <t>Registos históricos paginados das previsões marítimas</t>
+  </si>
+  <si>
+    <t>/data/observations/current?lat=39.7351&amp;lon=-8.8212</t>
+  </si>
+  <si>
+    <t>/data/observations/history?lat=39.7351&amp;lon=-8.8212&amp;variable=temperature&amp;range=24h</t>
+  </si>
+  <si>
+    <t>/data/observations/records?lat=39.7351&amp;lon=-8.8212&amp;page=1&amp;page_size=10</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/current?lat=39.7351&amp;lon=-8.8212</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/timeline?lat=39.7351&amp;lon=-8.8212&amp;provider=openmeteo&amp;hours=24</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/history?lat=39.7351&amp;lon=-8.8212&amp;variable=temperature&amp;range=24h</t>
+  </si>
+  <si>
+    <t>/data/forecast/terrestrial/records?lat=39.7351&amp;lon=-8.8212&amp;page=1&amp;page_size=10</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/current?lat=39.9300&amp;lon=-9.1200</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/timeline?lat=39.9300&amp;lon=-9.1200&amp;provider=ipma&amp;hours=24</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/history?lat=39.9300&amp;lon=-9.1200&amp;variable=waveHeight&amp;range=24h</t>
+  </si>
+  <si>
+    <t>/data/forecast/marine/records?lat=39.9300&amp;lon=-9.1200&amp;page=1&amp;page_size=10&amp;search=&amp;variable=seaTemperature&amp;variable=seaTemperature</t>
   </si>
 </sst>
 </file>
@@ -7416,24 +7428,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7530,6 +7548,24 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7557,23 +7593,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7587,31 +7632,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7622,36 +7664,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8320,7 +8332,7 @@
       </c>
     </row>
     <row r="5" spans="3:12" ht="15.75">
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="256" t="s">
         <v>746</v>
       </c>
       <c r="D5" s="93" t="s">
@@ -8335,7 +8347,7 @@
       <c r="G5" s="93" t="s">
         <v>1033</v>
       </c>
-      <c r="H5" s="256" t="s">
+      <c r="H5" s="257" t="s">
         <v>1034</v>
       </c>
       <c r="I5" s="258" t="s">
@@ -8344,12 +8356,12 @@
       <c r="J5" s="258" t="s">
         <v>1036</v>
       </c>
-      <c r="K5" s="254" t="s">
+      <c r="K5" s="259" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="6" spans="3:12" ht="15.75">
-      <c r="C6" s="257"/>
+      <c r="C6" s="256"/>
       <c r="D6" s="93" t="s">
         <v>1038</v>
       </c>
@@ -8362,13 +8374,13 @@
       <c r="G6" s="93" t="s">
         <v>1041</v>
       </c>
-      <c r="H6" s="256"/>
+      <c r="H6" s="257"/>
       <c r="I6" s="258"/>
       <c r="J6" s="258"/>
-      <c r="K6" s="259"/>
+      <c r="K6" s="260"/>
     </row>
     <row r="7" spans="3:12" ht="15.75">
-      <c r="C7" s="257"/>
+      <c r="C7" s="256"/>
       <c r="D7" s="93" t="s">
         <v>860</v>
       </c>
@@ -8381,94 +8393,94 @@
       <c r="G7" s="93" t="s">
         <v>1043</v>
       </c>
-      <c r="H7" s="256"/>
+      <c r="H7" s="257"/>
       <c r="I7" s="258"/>
       <c r="J7" s="258"/>
-      <c r="K7" s="255"/>
+      <c r="K7" s="261"/>
     </row>
     <row r="8" spans="3:12" ht="15.75">
-      <c r="C8" s="257" t="s">
+      <c r="C8" s="256" t="s">
         <v>1044</v>
       </c>
       <c r="D8" s="93" t="s">
         <v>1045</v>
       </c>
-      <c r="E8" s="256" t="s">
+      <c r="E8" s="257" t="s">
         <v>1046</v>
       </c>
-      <c r="F8" s="256" t="s">
+      <c r="F8" s="257" t="s">
         <v>1047</v>
       </c>
-      <c r="G8" s="256" t="s">
+      <c r="G8" s="257" t="s">
         <v>1048</v>
       </c>
-      <c r="H8" s="256" t="s">
+      <c r="H8" s="257" t="s">
         <v>1049</v>
       </c>
-      <c r="I8" s="256" t="s">
+      <c r="I8" s="257" t="s">
         <v>1050</v>
       </c>
-      <c r="J8" s="256" t="s">
+      <c r="J8" s="257" t="s">
         <v>1051</v>
       </c>
-      <c r="K8" s="254" t="s">
+      <c r="K8" s="259" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="9" spans="3:12" ht="15.75">
-      <c r="C9" s="257"/>
+      <c r="C9" s="256"/>
       <c r="D9" s="93" t="s">
         <v>1052</v>
       </c>
-      <c r="E9" s="256"/>
-      <c r="F9" s="256"/>
-      <c r="G9" s="256"/>
-      <c r="H9" s="256"/>
-      <c r="I9" s="256"/>
-      <c r="J9" s="256"/>
-      <c r="K9" s="255"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="257"/>
+      <c r="I9" s="257"/>
+      <c r="J9" s="257"/>
+      <c r="K9" s="261"/>
     </row>
     <row r="10" spans="3:12" ht="15.75">
-      <c r="C10" s="257" t="s">
+      <c r="C10" s="256" t="s">
         <v>455</v>
       </c>
       <c r="D10" s="93" t="s">
         <v>1053</v>
       </c>
-      <c r="E10" s="256" t="s">
+      <c r="E10" s="257" t="s">
         <v>1054</v>
       </c>
-      <c r="F10" s="256" t="s">
+      <c r="F10" s="257" t="s">
         <v>1055</v>
       </c>
-      <c r="G10" s="256" t="s">
+      <c r="G10" s="257" t="s">
         <v>1048</v>
       </c>
-      <c r="H10" s="256" t="s">
+      <c r="H10" s="257" t="s">
         <v>1034</v>
       </c>
-      <c r="I10" s="256" t="s">
+      <c r="I10" s="257" t="s">
         <v>1056</v>
       </c>
-      <c r="J10" s="256" t="s">
+      <c r="J10" s="257" t="s">
         <v>1048</v>
       </c>
-      <c r="K10" s="254" t="s">
+      <c r="K10" s="259" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="11" spans="3:12" ht="15.75">
-      <c r="C11" s="257"/>
+      <c r="C11" s="256"/>
       <c r="D11" s="93" t="s">
         <v>1058</v>
       </c>
-      <c r="E11" s="256"/>
-      <c r="F11" s="256"/>
-      <c r="G11" s="256"/>
-      <c r="H11" s="256"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="256"/>
-      <c r="K11" s="255"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="257"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="257"/>
+      <c r="J11" s="257"/>
+      <c r="K11" s="261"/>
     </row>
     <row r="12" spans="3:12" ht="15.75">
       <c r="C12" s="92" t="s">
@@ -8615,11 +8627,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="K5:K7"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="J8:J9"/>
@@ -8636,6 +8643,11 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="H8:H9"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="K5:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8922,7 +8934,7 @@
       <c r="G19" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="268" t="s">
+      <c r="H19" s="270" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -8948,7 +8960,7 @@
       <c r="G20" s="148" t="s">
         <v>87</v>
       </c>
-      <c r="H20" s="268"/>
+      <c r="H20" s="270"/>
     </row>
     <row r="21" spans="1:8" ht="21" customHeight="1">
       <c r="A21" s="133" t="s">
@@ -8972,7 +8984,7 @@
       <c r="G21" s="148" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="268"/>
+      <c r="H21" s="270"/>
     </row>
     <row r="22" spans="1:8" ht="21.75" customHeight="1">
       <c r="A22" s="133" t="s">
@@ -8996,7 +9008,7 @@
       <c r="G22" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="268" t="s">
+      <c r="H22" s="270" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -9022,7 +9034,7 @@
       <c r="G23" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="268"/>
+      <c r="H23" s="270"/>
     </row>
     <row r="24" spans="1:8" ht="21.75" customHeight="1">
       <c r="A24" s="133" t="s">
@@ -9046,7 +9058,7 @@
       <c r="G24" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="268"/>
+      <c r="H24" s="270"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1">
       <c r="A25" s="133" t="s">
@@ -9070,7 +9082,7 @@
       <c r="G25" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="268"/>
+      <c r="H25" s="270"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1">
       <c r="A26" s="133" t="s">
@@ -9094,7 +9106,7 @@
       <c r="G26" s="148" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="268"/>
+      <c r="H26" s="270"/>
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1">
       <c r="A27" s="133" t="s">
@@ -9116,7 +9128,7 @@
         <v>1106</v>
       </c>
       <c r="G27" s="148"/>
-      <c r="H27" s="268"/>
+      <c r="H27" s="270"/>
     </row>
     <row r="28" spans="1:8" ht="20.25" customHeight="1">
       <c r="A28" s="133" t="s">
@@ -9140,7 +9152,7 @@
       <c r="G28" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="268"/>
+      <c r="H28" s="270"/>
     </row>
     <row r="29" spans="1:8" ht="21" customHeight="1">
       <c r="A29" s="133" t="s">
@@ -9164,7 +9176,7 @@
       <c r="G29" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="268"/>
+      <c r="H29" s="270"/>
     </row>
     <row r="30" spans="1:8" ht="20.25" customHeight="1">
       <c r="A30" s="133" t="s">
@@ -9188,7 +9200,7 @@
       <c r="G30" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="268"/>
+      <c r="H30" s="270"/>
     </row>
     <row r="31" spans="1:8" ht="20.25" customHeight="1">
       <c r="A31" s="133" t="s">
@@ -9212,7 +9224,7 @@
       <c r="G31" s="148" t="s">
         <v>63</v>
       </c>
-      <c r="H31" s="268"/>
+      <c r="H31" s="270"/>
     </row>
     <row r="32" spans="1:8" ht="23.25" customHeight="1">
       <c r="A32" s="133" t="s">
@@ -9236,7 +9248,7 @@
       <c r="G32" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="268"/>
+      <c r="H32" s="270"/>
     </row>
     <row r="33" spans="1:8" ht="21" customHeight="1">
       <c r="A33" s="133" t="s">
@@ -9258,7 +9270,7 @@
         <v>1106</v>
       </c>
       <c r="G33" s="148"/>
-      <c r="H33" s="268"/>
+      <c r="H33" s="270"/>
     </row>
     <row r="34" spans="1:8" ht="20.25" customHeight="1">
       <c r="A34" s="133" t="s">
@@ -9282,7 +9294,7 @@
       <c r="G34" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="268"/>
+      <c r="H34" s="270"/>
     </row>
     <row r="35" spans="1:8" ht="21" customHeight="1">
       <c r="A35" s="133" t="s">
@@ -9304,7 +9316,7 @@
         <v>1106</v>
       </c>
       <c r="G35" s="148"/>
-      <c r="H35" s="268"/>
+      <c r="H35" s="270"/>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1">
       <c r="A36" s="133" t="s">
@@ -9326,7 +9338,7 @@
         <v>1106</v>
       </c>
       <c r="G36" s="148"/>
-      <c r="H36" s="268"/>
+      <c r="H36" s="270"/>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1">
       <c r="A37" s="133" t="s">
@@ -9350,7 +9362,7 @@
       <c r="G37" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="268"/>
+      <c r="H37" s="270"/>
     </row>
     <row r="38" spans="1:8" ht="20.25" customHeight="1">
       <c r="A38" s="133" t="s">
@@ -9374,7 +9386,7 @@
       <c r="G38" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="H38" s="268" t="s">
+      <c r="H38" s="270" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -9400,7 +9412,7 @@
       <c r="G39" s="155" t="s">
         <v>114</v>
       </c>
-      <c r="H39" s="268"/>
+      <c r="H39" s="270"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="42" spans="1:8" ht="21" customHeight="1" thickBot="1">
@@ -9821,10 +9833,10 @@
   <sheetData>
     <row r="3" spans="2:14" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:14" ht="15.75" thickBot="1">
-      <c r="K4" s="304" t="s">
+      <c r="K4" s="297" t="s">
         <v>1192</v>
       </c>
-      <c r="L4" s="305"/>
+      <c r="L4" s="298"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
@@ -9838,13 +9850,13 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B6" s="292" t="s">
+      <c r="B6" s="300" t="s">
         <v>1437</v>
       </c>
-      <c r="C6" s="293"/>
-      <c r="D6" s="293"/>
-      <c r="E6" s="293"/>
-      <c r="F6" s="294"/>
+      <c r="C6" s="301"/>
+      <c r="D6" s="301"/>
+      <c r="E6" s="301"/>
+      <c r="F6" s="302"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="K6" s="161" t="s">
@@ -9878,7 +9890,7 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="295"/>
+      <c r="B8" s="303"/>
       <c r="C8" s="14" t="s">
         <v>1335</v>
       </c>
@@ -9899,7 +9911,7 @@
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="296"/>
+      <c r="B9" s="304"/>
       <c r="C9" s="14" t="s">
         <v>1336</v>
       </c>
@@ -9920,12 +9932,12 @@
       </c>
     </row>
     <row r="10" spans="2:14">
-      <c r="B10" s="296"/>
-      <c r="C10" s="298"/>
+      <c r="B10" s="304"/>
+      <c r="C10" s="306"/>
       <c r="D10" s="156" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="306"/>
       <c r="F10" s="15" t="s">
         <v>1339</v>
       </c>
@@ -9937,12 +9949,12 @@
       </c>
     </row>
     <row r="11" spans="2:14">
-      <c r="B11" s="296"/>
-      <c r="C11" s="299"/>
+      <c r="B11" s="304"/>
+      <c r="C11" s="307"/>
       <c r="D11" s="156" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="299"/>
+      <c r="E11" s="307"/>
       <c r="F11" s="15" t="s">
         <v>1340</v>
       </c>
@@ -9954,12 +9966,12 @@
       </c>
     </row>
     <row r="12" spans="2:14">
-      <c r="B12" s="296"/>
-      <c r="C12" s="299"/>
+      <c r="B12" s="304"/>
+      <c r="C12" s="307"/>
       <c r="D12" s="156" t="s">
         <v>1164</v>
       </c>
-      <c r="E12" s="299"/>
+      <c r="E12" s="307"/>
       <c r="F12" s="15" t="s">
         <v>1341</v>
       </c>
@@ -9971,10 +9983,10 @@
       </c>
     </row>
     <row r="13" spans="2:14">
-      <c r="B13" s="296"/>
-      <c r="C13" s="299"/>
-      <c r="D13" s="298"/>
-      <c r="E13" s="299"/>
+      <c r="B13" s="304"/>
+      <c r="C13" s="307"/>
+      <c r="D13" s="306"/>
+      <c r="E13" s="307"/>
       <c r="F13" s="15" t="s">
         <v>1342</v>
       </c>
@@ -9986,10 +9998,10 @@
       </c>
     </row>
     <row r="14" spans="2:14">
-      <c r="B14" s="296"/>
-      <c r="C14" s="299"/>
-      <c r="D14" s="299"/>
-      <c r="E14" s="299"/>
+      <c r="B14" s="304"/>
+      <c r="C14" s="307"/>
+      <c r="D14" s="307"/>
+      <c r="E14" s="307"/>
       <c r="F14" s="15" t="s">
         <v>1343</v>
       </c>
@@ -10001,10 +10013,10 @@
       </c>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="296"/>
-      <c r="C15" s="299"/>
-      <c r="D15" s="299"/>
-      <c r="E15" s="299"/>
+      <c r="B15" s="304"/>
+      <c r="C15" s="307"/>
+      <c r="D15" s="307"/>
+      <c r="E15" s="307"/>
       <c r="F15" s="15" t="s">
         <v>1344</v>
       </c>
@@ -10016,10 +10028,10 @@
       </c>
     </row>
     <row r="16" spans="2:14">
-      <c r="B16" s="296"/>
-      <c r="C16" s="299"/>
-      <c r="D16" s="299"/>
-      <c r="E16" s="299"/>
+      <c r="B16" s="304"/>
+      <c r="C16" s="307"/>
+      <c r="D16" s="307"/>
+      <c r="E16" s="307"/>
       <c r="F16" s="15" t="s">
         <v>1345</v>
       </c>
@@ -10031,10 +10043,10 @@
       </c>
     </row>
     <row r="17" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B17" s="297"/>
-      <c r="C17" s="300"/>
-      <c r="D17" s="300"/>
-      <c r="E17" s="300"/>
+      <c r="B17" s="305"/>
+      <c r="C17" s="308"/>
+      <c r="D17" s="308"/>
+      <c r="E17" s="308"/>
       <c r="F17" s="23" t="s">
         <v>1346</v>
       </c>
@@ -10087,11 +10099,11 @@
       <c r="H24" s="224" t="s">
         <v>1189</v>
       </c>
-      <c r="K24" s="306" t="s">
+      <c r="K24" s="299" t="s">
         <v>1194</v>
       </c>
-      <c r="L24" s="306"/>
-      <c r="M24" s="306"/>
+      <c r="L24" s="299"/>
+      <c r="M24" s="299"/>
       <c r="N24" s="174"/>
     </row>
     <row r="25" spans="2:14" ht="15.75" thickBot="1">
@@ -10132,7 +10144,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="15"/>
-      <c r="K26" s="301" t="s">
+      <c r="K26" s="294" t="s">
         <v>0</v>
       </c>
       <c r="L26" s="167" t="s">
@@ -10156,7 +10168,7 @@
         <v>20</v>
       </c>
       <c r="H27" s="26"/>
-      <c r="K27" s="302"/>
+      <c r="K27" s="295"/>
       <c r="L27" s="166" t="s">
         <v>1186</v>
       </c>
@@ -10178,7 +10190,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="169"/>
-      <c r="K28" s="302"/>
+      <c r="K28" s="295"/>
       <c r="L28" s="166" t="s">
         <v>1183</v>
       </c>
@@ -10202,7 +10214,7 @@
       <c r="H29" s="169" t="s">
         <v>1441</v>
       </c>
-      <c r="K29" s="303"/>
+      <c r="K29" s="296"/>
       <c r="L29" s="22" t="s">
         <v>1184</v>
       </c>
@@ -10224,7 +10236,7 @@
         <v>242</v>
       </c>
       <c r="H30" s="15"/>
-      <c r="K30" s="301" t="s">
+      <c r="K30" s="294" t="s">
         <v>455</v>
       </c>
       <c r="L30" s="167" t="s">
@@ -10248,7 +10260,7 @@
         <v>242</v>
       </c>
       <c r="H31" s="15"/>
-      <c r="K31" s="302"/>
+      <c r="K31" s="295"/>
       <c r="L31" s="14" t="s">
         <v>1182</v>
       </c>
@@ -10273,7 +10285,7 @@
       <c r="I32" s="182" t="s">
         <v>1190</v>
       </c>
-      <c r="K32" s="303"/>
+      <c r="K32" s="296"/>
       <c r="L32" s="22" t="s">
         <v>1184</v>
       </c>
@@ -10335,7 +10347,7 @@
         <v>25</v>
       </c>
       <c r="H35" s="15"/>
-      <c r="K35" s="301" t="s">
+      <c r="K35" s="294" t="s">
         <v>1202</v>
       </c>
       <c r="L35" s="175" t="s">
@@ -10358,7 +10370,7 @@
       <c r="H36" s="15" t="s">
         <v>1445</v>
       </c>
-      <c r="K36" s="302"/>
+      <c r="K36" s="295"/>
       <c r="L36" s="158" t="s">
         <v>1209</v>
       </c>
@@ -10377,7 +10389,7 @@
         <v>242</v>
       </c>
       <c r="H37" s="169"/>
-      <c r="K37" s="302"/>
+      <c r="K37" s="295"/>
       <c r="L37" s="158" t="s">
         <v>1210</v>
       </c>
@@ -10398,7 +10410,7 @@
       <c r="H38" s="169" t="s">
         <v>1447</v>
       </c>
-      <c r="K38" s="302"/>
+      <c r="K38" s="295"/>
       <c r="L38" s="158" t="s">
         <v>1211</v>
       </c>
@@ -10419,7 +10431,7 @@
       <c r="H39" s="169" t="s">
         <v>1191</v>
       </c>
-      <c r="K39" s="303"/>
+      <c r="K39" s="296"/>
       <c r="L39" s="159" t="s">
         <v>1212</v>
       </c>
@@ -10440,7 +10452,7 @@
       <c r="H40" s="169" t="s">
         <v>1446</v>
       </c>
-      <c r="K40" s="301" t="s">
+      <c r="K40" s="294" t="s">
         <v>1203</v>
       </c>
       <c r="L40" s="176" t="s">
@@ -10463,7 +10475,7 @@
       <c r="H41" s="15" t="s">
         <v>1445</v>
       </c>
-      <c r="K41" s="302"/>
+      <c r="K41" s="295"/>
       <c r="L41" s="177" t="s">
         <v>1214</v>
       </c>
@@ -10484,7 +10496,7 @@
       <c r="H42" s="15" t="s">
         <v>1443</v>
       </c>
-      <c r="K42" s="303"/>
+      <c r="K42" s="296"/>
       <c r="L42" s="178" t="s">
         <v>1215</v>
       </c>
@@ -10535,17 +10547,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B8:B17"/>
+    <mergeCell ref="C10:C17"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="E10:E17"/>
     <mergeCell ref="K35:K39"/>
     <mergeCell ref="K40:K42"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="K26:K29"/>
     <mergeCell ref="K30:K32"/>
     <mergeCell ref="K24:M24"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B8:B17"/>
-    <mergeCell ref="C10:C17"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="E10:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" orientation="landscape" r:id="rId1"/>
@@ -10577,24 +10589,24 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:15">
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="265" t="s">
         <v>1016</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
       <c r="F3" t="s">
         <v>1253</v>
       </c>
-      <c r="H3" s="263" t="s">
+      <c r="H3" s="265" t="s">
         <v>949</v>
       </c>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="M3" s="263" t="s">
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="M3" s="265" t="s">
         <v>1236</v>
       </c>
-      <c r="N3" s="263"/>
-      <c r="O3" s="263"/>
+      <c r="N3" s="265"/>
+      <c r="O3" s="265"/>
     </row>
     <row r="4" spans="3:15">
       <c r="C4" s="44"/>
@@ -10614,7 +10626,7 @@
       <c r="J4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="308" t="s">
+      <c r="M4" s="319" t="s">
         <v>1217</v>
       </c>
       <c r="N4" s="40" t="s">
@@ -10625,7 +10637,7 @@
       </c>
     </row>
     <row r="5" spans="3:15">
-      <c r="C5" s="308" t="s">
+      <c r="C5" s="319" t="s">
         <v>1217</v>
       </c>
       <c r="D5" s="14" t="s">
@@ -10634,7 +10646,7 @@
       <c r="E5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="308" t="s">
+      <c r="H5" s="319" t="s">
         <v>1217</v>
       </c>
       <c r="I5" s="14" t="s">
@@ -10643,7 +10655,7 @@
       <c r="J5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="M5" s="308"/>
+      <c r="M5" s="319"/>
       <c r="N5" s="14" t="s">
         <v>871</v>
       </c>
@@ -10652,21 +10664,21 @@
       </c>
     </row>
     <row r="6" spans="3:15">
-      <c r="C6" s="308"/>
+      <c r="C6" s="319"/>
       <c r="D6" s="14" t="s">
         <v>1004</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>1219</v>
       </c>
-      <c r="H6" s="308"/>
+      <c r="H6" s="319"/>
       <c r="I6" s="14" t="s">
         <v>906</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>1227</v>
       </c>
-      <c r="M6" s="308"/>
+      <c r="M6" s="319"/>
       <c r="N6" s="14" t="s">
         <v>873</v>
       </c>
@@ -10675,21 +10687,21 @@
       </c>
     </row>
     <row r="7" spans="3:15">
-      <c r="C7" s="308"/>
+      <c r="C7" s="319"/>
       <c r="D7" s="14" t="s">
         <v>1216</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>1220</v>
       </c>
-      <c r="H7" s="308"/>
+      <c r="H7" s="319"/>
       <c r="I7" s="14" t="s">
         <v>907</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>1228</v>
       </c>
-      <c r="M7" s="308"/>
+      <c r="M7" s="319"/>
       <c r="N7" s="14" t="s">
         <v>875</v>
       </c>
@@ -10698,21 +10710,21 @@
       </c>
     </row>
     <row r="8" spans="3:15">
-      <c r="C8" s="308"/>
+      <c r="C8" s="319"/>
       <c r="D8" s="14" t="s">
         <v>1009</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>1221</v>
       </c>
-      <c r="H8" s="308"/>
+      <c r="H8" s="319"/>
       <c r="I8" s="14" t="s">
         <v>909</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>1229</v>
       </c>
-      <c r="M8" s="308"/>
+      <c r="M8" s="319"/>
       <c r="N8" s="14" t="s">
         <v>877</v>
       </c>
@@ -10721,21 +10733,21 @@
       </c>
     </row>
     <row r="9" spans="3:15">
-      <c r="C9" s="308"/>
+      <c r="C9" s="319"/>
       <c r="D9" s="14" t="s">
         <v>1011</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>1222</v>
       </c>
-      <c r="H9" s="308"/>
+      <c r="H9" s="319"/>
       <c r="I9" s="14" t="s">
         <v>919</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>1230</v>
       </c>
-      <c r="M9" s="308"/>
+      <c r="M9" s="319"/>
       <c r="N9" s="14" t="s">
         <v>879</v>
       </c>
@@ -10744,21 +10756,21 @@
       </c>
     </row>
     <row r="10" spans="3:15">
-      <c r="C10" s="308"/>
+      <c r="C10" s="319"/>
       <c r="D10" s="14" t="s">
         <v>1013</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>1223</v>
       </c>
-      <c r="H10" s="308"/>
+      <c r="H10" s="319"/>
       <c r="I10" s="14" t="s">
         <v>921</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>1231</v>
       </c>
-      <c r="M10" s="308"/>
+      <c r="M10" s="319"/>
       <c r="N10" s="14" t="s">
         <v>881</v>
       </c>
@@ -10767,7 +10779,7 @@
       </c>
     </row>
     <row r="11" spans="3:15">
-      <c r="C11" s="308" t="s">
+      <c r="C11" s="319" t="s">
         <v>1218</v>
       </c>
       <c r="D11" s="14" t="s">
@@ -10776,14 +10788,14 @@
       <c r="E11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="308"/>
+      <c r="H11" s="319"/>
       <c r="I11" s="14" t="s">
         <v>923</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>1232</v>
       </c>
-      <c r="M11" s="308"/>
+      <c r="M11" s="319"/>
       <c r="N11" s="14" t="s">
         <v>883</v>
       </c>
@@ -10792,21 +10804,21 @@
       </c>
     </row>
     <row r="12" spans="3:15">
-      <c r="C12" s="308"/>
+      <c r="C12" s="319"/>
       <c r="D12" s="182" t="s">
         <v>975</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="308"/>
+      <c r="H12" s="319"/>
       <c r="I12" s="14" t="s">
         <v>941</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="M12" s="308"/>
+      <c r="M12" s="319"/>
       <c r="N12" s="14" t="s">
         <v>886</v>
       </c>
@@ -10815,14 +10827,14 @@
       </c>
     </row>
     <row r="13" spans="3:15">
-      <c r="C13" s="308"/>
+      <c r="C13" s="319"/>
       <c r="D13" s="14" t="s">
         <v>976</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>1224</v>
       </c>
-      <c r="H13" s="309" t="s">
+      <c r="H13" s="320" t="s">
         <v>1233</v>
       </c>
       <c r="I13" s="14" t="s">
@@ -10831,7 +10843,7 @@
       <c r="J13" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="M13" s="308"/>
+      <c r="M13" s="319"/>
       <c r="N13" s="14" t="s">
         <v>888</v>
       </c>
@@ -10840,14 +10852,14 @@
       </c>
     </row>
     <row r="14" spans="3:15">
-      <c r="C14" s="308"/>
+      <c r="C14" s="319"/>
       <c r="D14" s="14" t="s">
         <v>1000</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>1225</v>
       </c>
-      <c r="H14" s="310"/>
+      <c r="H14" s="321"/>
       <c r="I14" s="14" t="s">
         <v>945</v>
       </c>
@@ -10865,15 +10877,15 @@
       <c r="D24" s="182"/>
     </row>
     <row r="25" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C25" s="304" t="s">
+      <c r="C25" s="297" t="s">
         <v>1481</v>
       </c>
-      <c r="D25" s="307"/>
-      <c r="E25" s="307"/>
-      <c r="F25" s="307"/>
-      <c r="G25" s="307"/>
-      <c r="H25" s="307"/>
-      <c r="I25" s="305"/>
+      <c r="D25" s="318"/>
+      <c r="E25" s="318"/>
+      <c r="F25" s="318"/>
+      <c r="G25" s="318"/>
+      <c r="H25" s="318"/>
+      <c r="I25" s="298"/>
       <c r="K25" s="244" t="s">
         <v>1484</v>
       </c>
@@ -10933,7 +10945,7 @@
       <c r="P26" s="15"/>
     </row>
     <row r="27" spans="3:16">
-      <c r="C27" s="314"/>
+      <c r="C27" s="312"/>
       <c r="D27" s="14" t="s">
         <v>1256</v>
       </c>
@@ -10970,7 +10982,7 @@
       <c r="P27" s="15"/>
     </row>
     <row r="28" spans="3:16">
-      <c r="C28" s="315"/>
+      <c r="C28" s="313"/>
       <c r="D28" s="14" t="s">
         <v>1358</v>
       </c>
@@ -11007,21 +11019,21 @@
       <c r="P28" s="15"/>
     </row>
     <row r="29" spans="3:16">
-      <c r="C29" s="315"/>
+      <c r="C29" s="313"/>
       <c r="D29" s="14" t="s">
         <v>1359</v>
       </c>
       <c r="E29" s="242" t="s">
         <v>1163</v>
       </c>
-      <c r="F29" s="317"/>
+      <c r="F29" s="315"/>
       <c r="G29" s="14" t="s">
         <v>1363</v>
       </c>
       <c r="H29" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="I29" s="311"/>
+      <c r="I29" s="309"/>
       <c r="K29" s="210" t="s">
         <v>1387</v>
       </c>
@@ -11040,19 +11052,19 @@
       <c r="P29" s="15"/>
     </row>
     <row r="30" spans="3:16">
-      <c r="C30" s="315"/>
+      <c r="C30" s="313"/>
       <c r="D30" s="14" t="s">
         <v>1360</v>
       </c>
-      <c r="E30" s="317"/>
-      <c r="F30" s="318"/>
+      <c r="E30" s="315"/>
+      <c r="F30" s="316"/>
       <c r="G30" s="14" t="s">
         <v>1364</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>1346</v>
       </c>
-      <c r="I30" s="312"/>
+      <c r="I30" s="310"/>
       <c r="K30" s="210" t="s">
         <v>1388</v>
       </c>
@@ -11073,15 +11085,15 @@
       </c>
     </row>
     <row r="31" spans="3:16">
-      <c r="C31" s="315"/>
-      <c r="D31" s="317"/>
-      <c r="E31" s="318"/>
-      <c r="F31" s="318"/>
+      <c r="C31" s="313"/>
+      <c r="D31" s="315"/>
+      <c r="E31" s="316"/>
+      <c r="F31" s="316"/>
       <c r="G31" s="14" t="s">
         <v>1365</v>
       </c>
-      <c r="H31" s="317"/>
-      <c r="I31" s="312"/>
+      <c r="H31" s="315"/>
+      <c r="I31" s="310"/>
       <c r="K31" s="210" t="s">
         <v>1251</v>
       </c>
@@ -11100,15 +11112,15 @@
       <c r="P31" s="15"/>
     </row>
     <row r="32" spans="3:16">
-      <c r="C32" s="315"/>
-      <c r="D32" s="318"/>
-      <c r="E32" s="318"/>
-      <c r="F32" s="318"/>
+      <c r="C32" s="313"/>
+      <c r="D32" s="316"/>
+      <c r="E32" s="316"/>
+      <c r="F32" s="316"/>
       <c r="G32" s="14" t="s">
         <v>1366</v>
       </c>
-      <c r="H32" s="318"/>
-      <c r="I32" s="312"/>
+      <c r="H32" s="316"/>
+      <c r="I32" s="310"/>
       <c r="K32" s="210" t="s">
         <v>1252</v>
       </c>
@@ -11127,15 +11139,15 @@
       <c r="P32" s="15"/>
     </row>
     <row r="33" spans="3:16">
-      <c r="C33" s="315"/>
-      <c r="D33" s="318"/>
-      <c r="E33" s="318"/>
-      <c r="F33" s="318"/>
+      <c r="C33" s="313"/>
+      <c r="D33" s="316"/>
+      <c r="E33" s="316"/>
+      <c r="F33" s="316"/>
       <c r="G33" s="14" t="s">
         <v>1367</v>
       </c>
-      <c r="H33" s="318"/>
-      <c r="I33" s="312"/>
+      <c r="H33" s="316"/>
+      <c r="I33" s="310"/>
       <c r="K33" s="247" t="s">
         <v>1347</v>
       </c>
@@ -11154,15 +11166,15 @@
       <c r="P33" s="15"/>
     </row>
     <row r="34" spans="3:16">
-      <c r="C34" s="315"/>
-      <c r="D34" s="318"/>
-      <c r="E34" s="318"/>
-      <c r="F34" s="318"/>
+      <c r="C34" s="313"/>
+      <c r="D34" s="316"/>
+      <c r="E34" s="316"/>
+      <c r="F34" s="316"/>
       <c r="G34" s="14" t="s">
         <v>1368</v>
       </c>
-      <c r="H34" s="318"/>
-      <c r="I34" s="312"/>
+      <c r="H34" s="316"/>
+      <c r="I34" s="310"/>
       <c r="K34" s="210" t="s">
         <v>1348</v>
       </c>
@@ -11183,15 +11195,15 @@
       </c>
     </row>
     <row r="35" spans="3:16">
-      <c r="C35" s="315"/>
-      <c r="D35" s="318"/>
-      <c r="E35" s="318"/>
-      <c r="F35" s="318"/>
+      <c r="C35" s="313"/>
+      <c r="D35" s="316"/>
+      <c r="E35" s="316"/>
+      <c r="F35" s="316"/>
       <c r="G35" s="14" t="s">
         <v>1369</v>
       </c>
-      <c r="H35" s="318"/>
-      <c r="I35" s="312"/>
+      <c r="H35" s="316"/>
+      <c r="I35" s="310"/>
       <c r="K35" s="247" t="s">
         <v>1389</v>
       </c>
@@ -11210,15 +11222,15 @@
       <c r="P35" s="15"/>
     </row>
     <row r="36" spans="3:16">
-      <c r="C36" s="315"/>
-      <c r="D36" s="318"/>
-      <c r="E36" s="318"/>
-      <c r="F36" s="318"/>
+      <c r="C36" s="313"/>
+      <c r="D36" s="316"/>
+      <c r="E36" s="316"/>
+      <c r="F36" s="316"/>
       <c r="G36" s="14" t="s">
         <v>1370</v>
       </c>
-      <c r="H36" s="318"/>
-      <c r="I36" s="312"/>
+      <c r="H36" s="316"/>
+      <c r="I36" s="310"/>
       <c r="K36" s="247" t="s">
         <v>1390</v>
       </c>
@@ -11237,15 +11249,15 @@
       <c r="P36" s="15"/>
     </row>
     <row r="37" spans="3:16">
-      <c r="C37" s="315"/>
-      <c r="D37" s="318"/>
-      <c r="E37" s="318"/>
-      <c r="F37" s="318"/>
+      <c r="C37" s="313"/>
+      <c r="D37" s="316"/>
+      <c r="E37" s="316"/>
+      <c r="F37" s="316"/>
       <c r="G37" s="14" t="s">
         <v>1371</v>
       </c>
-      <c r="H37" s="318"/>
-      <c r="I37" s="312"/>
+      <c r="H37" s="316"/>
+      <c r="I37" s="310"/>
       <c r="K37" s="247" t="s">
         <v>1391</v>
       </c>
@@ -11264,15 +11276,15 @@
       <c r="P37" s="15"/>
     </row>
     <row r="38" spans="3:16">
-      <c r="C38" s="315"/>
-      <c r="D38" s="318"/>
-      <c r="E38" s="318"/>
-      <c r="F38" s="318"/>
+      <c r="C38" s="313"/>
+      <c r="D38" s="316"/>
+      <c r="E38" s="316"/>
+      <c r="F38" s="316"/>
       <c r="G38" s="14" t="s">
         <v>1372</v>
       </c>
-      <c r="H38" s="318"/>
-      <c r="I38" s="312"/>
+      <c r="H38" s="316"/>
+      <c r="I38" s="310"/>
       <c r="K38" s="247" t="s">
         <v>1392</v>
       </c>
@@ -11291,15 +11303,15 @@
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="3:16">
-      <c r="C39" s="315"/>
-      <c r="D39" s="318"/>
-      <c r="E39" s="318"/>
-      <c r="F39" s="318"/>
+      <c r="C39" s="313"/>
+      <c r="D39" s="316"/>
+      <c r="E39" s="316"/>
+      <c r="F39" s="316"/>
       <c r="G39" s="14" t="s">
         <v>1373</v>
       </c>
-      <c r="H39" s="318"/>
-      <c r="I39" s="312"/>
+      <c r="H39" s="316"/>
+      <c r="I39" s="310"/>
       <c r="K39" s="247" t="s">
         <v>1393</v>
       </c>
@@ -11318,15 +11330,15 @@
       <c r="P39" s="15"/>
     </row>
     <row r="40" spans="3:16">
-      <c r="C40" s="315"/>
-      <c r="D40" s="318"/>
-      <c r="E40" s="318"/>
-      <c r="F40" s="318"/>
+      <c r="C40" s="313"/>
+      <c r="D40" s="316"/>
+      <c r="E40" s="316"/>
+      <c r="F40" s="316"/>
       <c r="G40" s="14" t="s">
         <v>1374</v>
       </c>
-      <c r="H40" s="318"/>
-      <c r="I40" s="312"/>
+      <c r="H40" s="316"/>
+      <c r="I40" s="310"/>
       <c r="K40" s="247" t="s">
         <v>1394</v>
       </c>
@@ -11345,15 +11357,15 @@
       <c r="P40" s="15"/>
     </row>
     <row r="41" spans="3:16">
-      <c r="C41" s="315"/>
-      <c r="D41" s="318"/>
-      <c r="E41" s="318"/>
-      <c r="F41" s="318"/>
+      <c r="C41" s="313"/>
+      <c r="D41" s="316"/>
+      <c r="E41" s="316"/>
+      <c r="F41" s="316"/>
       <c r="G41" s="14" t="s">
         <v>1375</v>
       </c>
-      <c r="H41" s="318"/>
-      <c r="I41" s="312"/>
+      <c r="H41" s="316"/>
+      <c r="I41" s="310"/>
       <c r="K41" s="247" t="s">
         <v>1395</v>
       </c>
@@ -11374,15 +11386,15 @@
       </c>
     </row>
     <row r="42" spans="3:16">
-      <c r="C42" s="315"/>
-      <c r="D42" s="318"/>
-      <c r="E42" s="318"/>
-      <c r="F42" s="318"/>
+      <c r="C42" s="313"/>
+      <c r="D42" s="316"/>
+      <c r="E42" s="316"/>
+      <c r="F42" s="316"/>
       <c r="G42" s="14" t="s">
         <v>1376</v>
       </c>
-      <c r="H42" s="318"/>
-      <c r="I42" s="312"/>
+      <c r="H42" s="316"/>
+      <c r="I42" s="310"/>
       <c r="K42" s="247" t="s">
         <v>1396</v>
       </c>
@@ -11401,15 +11413,15 @@
       <c r="P42" s="15"/>
     </row>
     <row r="43" spans="3:16">
-      <c r="C43" s="315"/>
-      <c r="D43" s="318"/>
-      <c r="E43" s="318"/>
-      <c r="F43" s="318"/>
+      <c r="C43" s="313"/>
+      <c r="D43" s="316"/>
+      <c r="E43" s="316"/>
+      <c r="F43" s="316"/>
       <c r="G43" s="14" t="s">
         <v>1377</v>
       </c>
-      <c r="H43" s="318"/>
-      <c r="I43" s="312"/>
+      <c r="H43" s="316"/>
+      <c r="I43" s="310"/>
       <c r="K43" s="247" t="s">
         <v>1397</v>
       </c>
@@ -11428,15 +11440,15 @@
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C44" s="316"/>
-      <c r="D44" s="319"/>
-      <c r="E44" s="319"/>
-      <c r="F44" s="319"/>
+      <c r="C44" s="314"/>
+      <c r="D44" s="317"/>
+      <c r="E44" s="317"/>
+      <c r="F44" s="317"/>
       <c r="G44" s="22" t="s">
         <v>1378</v>
       </c>
-      <c r="H44" s="319"/>
-      <c r="I44" s="313"/>
+      <c r="H44" s="317"/>
+      <c r="I44" s="311"/>
       <c r="K44" s="247" t="s">
         <v>1398</v>
       </c>
@@ -11723,12 +11735,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="I29:I44"/>
-    <mergeCell ref="C27:C44"/>
-    <mergeCell ref="D31:D44"/>
-    <mergeCell ref="E30:E44"/>
-    <mergeCell ref="F29:F44"/>
-    <mergeCell ref="H31:H44"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="M4:M13"/>
     <mergeCell ref="M3:O3"/>
@@ -11738,6 +11744,12 @@
     <mergeCell ref="H5:H12"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I29:I44"/>
+    <mergeCell ref="C27:C44"/>
+    <mergeCell ref="D31:D44"/>
+    <mergeCell ref="E30:E44"/>
+    <mergeCell ref="F29:F44"/>
+    <mergeCell ref="H31:H44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="41" orientation="landscape" r:id="rId1"/>
@@ -11765,21 +11777,21 @@
   <sheetData>
     <row r="2" spans="3:16" ht="15.75" thickBot="1"/>
     <row r="3" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C3" s="286" t="s">
+      <c r="C3" s="288" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="287"/>
-      <c r="E3" s="288"/>
-      <c r="I3" s="286" t="s">
+      <c r="D3" s="289"/>
+      <c r="E3" s="290"/>
+      <c r="I3" s="288" t="s">
         <v>746</v>
       </c>
-      <c r="J3" s="287"/>
-      <c r="K3" s="330"/>
-      <c r="N3" s="292" t="s">
+      <c r="J3" s="289"/>
+      <c r="K3" s="329"/>
+      <c r="N3" s="300" t="s">
         <v>455</v>
       </c>
-      <c r="O3" s="293"/>
-      <c r="P3" s="323"/>
+      <c r="O3" s="301"/>
+      <c r="P3" s="322"/>
     </row>
     <row r="4" spans="3:16" ht="15.75" thickBot="1">
       <c r="C4" s="192"/>
@@ -11805,7 +11817,7 @@
       </c>
     </row>
     <row r="5" spans="3:16">
-      <c r="C5" s="327" t="s">
+      <c r="C5" s="326" t="s">
         <v>1265</v>
       </c>
       <c r="D5" s="185" t="s">
@@ -11814,7 +11826,7 @@
       <c r="E5" s="185" t="s">
         <v>327</v>
       </c>
-      <c r="I5" s="267" t="s">
+      <c r="I5" s="269" t="s">
         <v>1265</v>
       </c>
       <c r="J5" s="194" t="s">
@@ -11823,7 +11835,7 @@
       <c r="K5" s="12" t="s">
         <v>1282</v>
       </c>
-      <c r="N5" s="327" t="s">
+      <c r="N5" s="326" t="s">
         <v>1265</v>
       </c>
       <c r="O5" s="187" t="s">
@@ -11834,21 +11846,21 @@
       </c>
     </row>
     <row r="6" spans="3:16">
-      <c r="C6" s="328"/>
+      <c r="C6" s="327"/>
       <c r="D6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>239</v>
       </c>
-      <c r="I6" s="268"/>
+      <c r="I6" s="270"/>
       <c r="J6" s="13" t="s">
         <v>1277</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>1283</v>
       </c>
-      <c r="N6" s="328"/>
+      <c r="N6" s="327"/>
       <c r="O6" s="81" t="s">
         <v>503</v>
       </c>
@@ -11857,21 +11869,21 @@
       </c>
     </row>
     <row r="7" spans="3:16">
-      <c r="C7" s="328"/>
+      <c r="C7" s="327"/>
       <c r="D7" s="183" t="s">
         <v>247</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>248</v>
       </c>
-      <c r="I7" s="268"/>
+      <c r="I7" s="270"/>
       <c r="J7" s="13" t="s">
         <v>1278</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="N7" s="328"/>
+      <c r="N7" s="327"/>
       <c r="O7" s="81" t="s">
         <v>502</v>
       </c>
@@ -11880,21 +11892,21 @@
       </c>
     </row>
     <row r="8" spans="3:16">
-      <c r="C8" s="328"/>
+      <c r="C8" s="327"/>
       <c r="D8" s="183" t="s">
         <v>276</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>277</v>
       </c>
-      <c r="I8" s="268"/>
+      <c r="I8" s="270"/>
       <c r="J8" s="13" t="s">
         <v>1279</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="N8" s="328"/>
+      <c r="N8" s="327"/>
       <c r="O8" s="81" t="s">
         <v>1287</v>
       </c>
@@ -11903,21 +11915,21 @@
       </c>
     </row>
     <row r="9" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C9" s="329"/>
+      <c r="C9" s="328"/>
       <c r="D9" s="184" t="s">
         <v>280</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="I9" s="268"/>
+      <c r="I9" s="270"/>
       <c r="J9" s="13" t="s">
         <v>1280</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="N9" s="329"/>
+      <c r="N9" s="328"/>
       <c r="O9" s="188" t="s">
         <v>1288</v>
       </c>
@@ -11926,7 +11938,7 @@
       </c>
     </row>
     <row r="10" spans="3:16">
-      <c r="C10" s="327" t="s">
+      <c r="C10" s="326" t="s">
         <v>1266</v>
       </c>
       <c r="D10" s="190" t="s">
@@ -11935,14 +11947,14 @@
       <c r="E10" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="I10" s="268"/>
+      <c r="I10" s="270"/>
       <c r="J10" s="13" t="s">
         <v>1281</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>1285</v>
       </c>
-      <c r="N10" s="324" t="s">
+      <c r="N10" s="323" t="s">
         <v>1266</v>
       </c>
       <c r="O10" s="187" t="s">
@@ -11953,21 +11965,21 @@
       </c>
     </row>
     <row r="11" spans="3:16">
-      <c r="C11" s="328"/>
+      <c r="C11" s="327"/>
       <c r="D11" s="81" t="s">
         <v>307</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>1110</v>
       </c>
-      <c r="I11" s="268"/>
+      <c r="I11" s="270"/>
       <c r="J11" s="13" t="s">
         <v>111</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="N11" s="325"/>
+      <c r="N11" s="324"/>
       <c r="O11" s="81" t="s">
         <v>1290</v>
       </c>
@@ -11976,21 +11988,21 @@
       </c>
     </row>
     <row r="12" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C12" s="328"/>
+      <c r="C12" s="327"/>
       <c r="D12" s="81" t="s">
         <v>314</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="I12" s="269"/>
+      <c r="I12" s="271"/>
       <c r="J12" s="21" t="s">
         <v>114</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="N12" s="325"/>
+      <c r="N12" s="324"/>
       <c r="O12" s="81" t="s">
         <v>1291</v>
       </c>
@@ -11999,14 +12011,14 @@
       </c>
     </row>
     <row r="13" spans="3:16">
-      <c r="C13" s="328"/>
+      <c r="C13" s="327"/>
       <c r="D13" s="81" t="s">
         <v>336</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>1267</v>
       </c>
-      <c r="I13" s="325" t="s">
+      <c r="I13" s="324" t="s">
         <v>1266</v>
       </c>
       <c r="J13" s="197" t="s">
@@ -12015,7 +12027,7 @@
       <c r="K13" s="168" t="s">
         <v>762</v>
       </c>
-      <c r="N13" s="325"/>
+      <c r="N13" s="324"/>
       <c r="O13" s="81" t="s">
         <v>1292</v>
       </c>
@@ -12024,21 +12036,21 @@
       </c>
     </row>
     <row r="14" spans="3:16">
-      <c r="C14" s="328"/>
+      <c r="C14" s="327"/>
       <c r="D14" s="81" t="s">
         <v>339</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>1268</v>
       </c>
-      <c r="I14" s="325"/>
+      <c r="I14" s="324"/>
       <c r="J14" s="24" t="s">
         <v>800</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>801</v>
       </c>
-      <c r="N14" s="325"/>
+      <c r="N14" s="324"/>
       <c r="O14" s="81" t="s">
         <v>1293</v>
       </c>
@@ -12047,21 +12059,21 @@
       </c>
     </row>
     <row r="15" spans="3:16">
-      <c r="C15" s="328"/>
+      <c r="C15" s="327"/>
       <c r="D15" s="81" t="s">
         <v>340</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>1269</v>
       </c>
-      <c r="I15" s="325"/>
+      <c r="I15" s="324"/>
       <c r="J15" s="24" t="s">
         <v>813</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="N15" s="325"/>
+      <c r="N15" s="324"/>
       <c r="O15" s="81" t="s">
         <v>1294</v>
       </c>
@@ -12070,21 +12082,21 @@
       </c>
     </row>
     <row r="16" spans="3:16">
-      <c r="C16" s="328"/>
+      <c r="C16" s="327"/>
       <c r="D16" s="81" t="s">
         <v>341</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="I16" s="325"/>
+      <c r="I16" s="324"/>
       <c r="J16" s="24" t="s">
         <v>807</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>1274</v>
       </c>
-      <c r="N16" s="325"/>
+      <c r="N16" s="324"/>
       <c r="O16" s="81" t="s">
         <v>1295</v>
       </c>
@@ -12093,21 +12105,21 @@
       </c>
     </row>
     <row r="17" spans="3:16">
-      <c r="C17" s="328"/>
+      <c r="C17" s="327"/>
       <c r="D17" s="81" t="s">
         <v>350</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>983</v>
       </c>
-      <c r="I17" s="325"/>
+      <c r="I17" s="324"/>
       <c r="J17" s="24" t="s">
         <v>769</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="N17" s="325"/>
+      <c r="N17" s="324"/>
       <c r="O17" s="81" t="s">
         <v>1299</v>
       </c>
@@ -12116,21 +12128,21 @@
       </c>
     </row>
     <row r="18" spans="3:16">
-      <c r="C18" s="328"/>
+      <c r="C18" s="327"/>
       <c r="D18" s="81" t="s">
         <v>353</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>1270</v>
       </c>
-      <c r="I18" s="325"/>
+      <c r="I18" s="324"/>
       <c r="J18" s="24" t="s">
         <v>763</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="N18" s="325"/>
+      <c r="N18" s="324"/>
       <c r="O18" s="81" t="s">
         <v>1300</v>
       </c>
@@ -12139,21 +12151,21 @@
       </c>
     </row>
     <row r="19" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C19" s="328"/>
+      <c r="C19" s="327"/>
       <c r="D19" s="81" t="s">
         <v>354</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="I19" s="325"/>
+      <c r="I19" s="324"/>
       <c r="J19" s="24" t="s">
         <v>66</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>779</v>
       </c>
-      <c r="N19" s="326"/>
+      <c r="N19" s="325"/>
       <c r="O19" s="188" t="s">
         <v>492</v>
       </c>
@@ -12162,14 +12174,14 @@
       </c>
     </row>
     <row r="20" spans="3:16">
-      <c r="C20" s="328"/>
+      <c r="C20" s="327"/>
       <c r="D20" s="81" t="s">
         <v>356</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>1273</v>
       </c>
-      <c r="I20" s="325"/>
+      <c r="I20" s="324"/>
       <c r="J20" s="24" t="s">
         <v>784</v>
       </c>
@@ -12178,14 +12190,14 @@
       </c>
     </row>
     <row r="21" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C21" s="328"/>
+      <c r="C21" s="327"/>
       <c r="D21" s="81" t="s">
         <v>359</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>1272</v>
       </c>
-      <c r="I21" s="326"/>
+      <c r="I21" s="325"/>
       <c r="J21" s="27" t="s">
         <v>786</v>
       </c>
@@ -12194,7 +12206,7 @@
       </c>
     </row>
     <row r="22" spans="3:16">
-      <c r="C22" s="328"/>
+      <c r="C22" s="327"/>
       <c r="D22" s="81" t="s">
         <v>370</v>
       </c>
@@ -12203,7 +12215,7 @@
       </c>
     </row>
     <row r="23" spans="3:16">
-      <c r="C23" s="328"/>
+      <c r="C23" s="327"/>
       <c r="D23" s="81" t="s">
         <v>372</v>
       </c>
@@ -12212,7 +12224,7 @@
       </c>
     </row>
     <row r="24" spans="3:16">
-      <c r="C24" s="328"/>
+      <c r="C24" s="327"/>
       <c r="D24" s="81" t="s">
         <v>382</v>
       </c>
@@ -12221,7 +12233,7 @@
       </c>
     </row>
     <row r="25" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C25" s="329"/>
+      <c r="C25" s="328"/>
       <c r="D25" s="188" t="s">
         <v>386</v>
       </c>
@@ -12236,16 +12248,16 @@
     </row>
     <row r="28" spans="3:16" ht="15.75" thickBot="1"/>
     <row r="29" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C29" s="286" t="s">
+      <c r="C29" s="288" t="s">
         <v>1307</v>
       </c>
-      <c r="D29" s="287"/>
-      <c r="E29" s="288"/>
-      <c r="I29" s="286" t="s">
+      <c r="D29" s="289"/>
+      <c r="E29" s="290"/>
+      <c r="I29" s="288" t="s">
         <v>1309</v>
       </c>
-      <c r="J29" s="287"/>
-      <c r="K29" s="288"/>
+      <c r="J29" s="289"/>
+      <c r="K29" s="290"/>
     </row>
     <row r="30" spans="3:16" ht="15.75" thickBot="1">
       <c r="C30" s="87"/>
@@ -12264,7 +12276,7 @@
       </c>
     </row>
     <row r="31" spans="3:16" ht="30">
-      <c r="C31" s="267" t="s">
+      <c r="C31" s="269" t="s">
         <v>1265</v>
       </c>
       <c r="D31" s="200" t="s">
@@ -12274,7 +12286,7 @@
         <v>327</v>
       </c>
       <c r="F31" s="193"/>
-      <c r="I31" s="327" t="s">
+      <c r="I31" s="326" t="s">
         <v>1265</v>
       </c>
       <c r="J31" s="209" t="s">
@@ -12285,7 +12297,7 @@
       </c>
     </row>
     <row r="32" spans="3:16" ht="45">
-      <c r="C32" s="268"/>
+      <c r="C32" s="270"/>
       <c r="D32" s="199" t="s">
         <v>698</v>
       </c>
@@ -12293,7 +12305,7 @@
         <v>248</v>
       </c>
       <c r="F32" s="193"/>
-      <c r="I32" s="328"/>
+      <c r="I32" s="327"/>
       <c r="J32" s="203" t="s">
         <v>87</v>
       </c>
@@ -12302,7 +12314,7 @@
       </c>
     </row>
     <row r="33" spans="3:11" ht="45">
-      <c r="C33" s="268"/>
+      <c r="C33" s="270"/>
       <c r="D33" s="199" t="s">
         <v>699</v>
       </c>
@@ -12310,7 +12322,7 @@
         <v>239</v>
       </c>
       <c r="F33" s="193"/>
-      <c r="I33" s="328"/>
+      <c r="I33" s="327"/>
       <c r="J33" s="203" t="s">
         <v>89</v>
       </c>
@@ -12319,7 +12331,7 @@
       </c>
     </row>
     <row r="34" spans="3:11" ht="45">
-      <c r="C34" s="268"/>
+      <c r="C34" s="270"/>
       <c r="D34" s="199" t="s">
         <v>714</v>
       </c>
@@ -12327,7 +12339,7 @@
         <v>283</v>
       </c>
       <c r="F34" s="193"/>
-      <c r="I34" s="328"/>
+      <c r="I34" s="327"/>
       <c r="J34" s="203" t="s">
         <v>73</v>
       </c>
@@ -12336,7 +12348,7 @@
       </c>
     </row>
     <row r="35" spans="3:11" ht="45">
-      <c r="C35" s="268"/>
+      <c r="C35" s="270"/>
       <c r="D35" s="199" t="s">
         <v>715</v>
       </c>
@@ -12344,7 +12356,7 @@
         <v>271</v>
       </c>
       <c r="F35" s="193"/>
-      <c r="I35" s="328"/>
+      <c r="I35" s="327"/>
       <c r="J35" s="203" t="s">
         <v>105</v>
       </c>
@@ -12353,7 +12365,7 @@
       </c>
     </row>
     <row r="36" spans="3:11" ht="45">
-      <c r="C36" s="268"/>
+      <c r="C36" s="270"/>
       <c r="D36" s="199" t="s">
         <v>659</v>
       </c>
@@ -12361,7 +12373,7 @@
         <v>250</v>
       </c>
       <c r="F36" s="193"/>
-      <c r="I36" s="328"/>
+      <c r="I36" s="327"/>
       <c r="J36" s="203" t="s">
         <v>41</v>
       </c>
@@ -12370,7 +12382,7 @@
       </c>
     </row>
     <row r="37" spans="3:11" ht="45">
-      <c r="C37" s="268"/>
+      <c r="C37" s="270"/>
       <c r="D37" s="199" t="s">
         <v>716</v>
       </c>
@@ -12378,7 +12390,7 @@
         <v>717</v>
       </c>
       <c r="F37" s="193"/>
-      <c r="I37" s="328"/>
+      <c r="I37" s="327"/>
       <c r="J37" s="203" t="s">
         <v>108</v>
       </c>
@@ -12387,7 +12399,7 @@
       </c>
     </row>
     <row r="38" spans="3:11" ht="45">
-      <c r="C38" s="268"/>
+      <c r="C38" s="270"/>
       <c r="D38" s="199" t="s">
         <v>718</v>
       </c>
@@ -12395,7 +12407,7 @@
         <v>719</v>
       </c>
       <c r="F38" s="193"/>
-      <c r="I38" s="328"/>
+      <c r="I38" s="327"/>
       <c r="J38" s="203" t="s">
         <v>51</v>
       </c>
@@ -12404,7 +12416,7 @@
       </c>
     </row>
     <row r="39" spans="3:11" ht="30">
-      <c r="C39" s="268"/>
+      <c r="C39" s="270"/>
       <c r="D39" s="199" t="s">
         <v>720</v>
       </c>
@@ -12412,7 +12424,7 @@
         <v>338</v>
       </c>
       <c r="F39" s="193"/>
-      <c r="I39" s="328"/>
+      <c r="I39" s="327"/>
       <c r="J39" s="203" t="s">
         <v>56</v>
       </c>
@@ -12421,7 +12433,7 @@
       </c>
     </row>
     <row r="40" spans="3:11" ht="30">
-      <c r="C40" s="268"/>
+      <c r="C40" s="270"/>
       <c r="D40" s="199" t="s">
         <v>721</v>
       </c>
@@ -12429,7 +12441,7 @@
         <v>292</v>
       </c>
       <c r="F40" s="193"/>
-      <c r="I40" s="328"/>
+      <c r="I40" s="327"/>
       <c r="J40" s="203" t="s">
         <v>125</v>
       </c>
@@ -12438,7 +12450,7 @@
       </c>
     </row>
     <row r="41" spans="3:11" ht="45">
-      <c r="C41" s="268"/>
+      <c r="C41" s="270"/>
       <c r="D41" s="199" t="s">
         <v>722</v>
       </c>
@@ -12446,7 +12458,7 @@
         <v>723</v>
       </c>
       <c r="F41" s="193"/>
-      <c r="I41" s="328"/>
+      <c r="I41" s="327"/>
       <c r="J41" s="203" t="s">
         <v>63</v>
       </c>
@@ -12455,7 +12467,7 @@
       </c>
     </row>
     <row r="42" spans="3:11" ht="45.75" thickBot="1">
-      <c r="C42" s="269"/>
+      <c r="C42" s="271"/>
       <c r="D42" s="201" t="s">
         <v>674</v>
       </c>
@@ -12463,7 +12475,7 @@
         <v>513</v>
       </c>
       <c r="F42" s="193"/>
-      <c r="I42" s="328"/>
+      <c r="I42" s="327"/>
       <c r="J42" s="203" t="s">
         <v>13</v>
       </c>
@@ -12472,7 +12484,7 @@
       </c>
     </row>
     <row r="43" spans="3:11" ht="30">
-      <c r="C43" s="327" t="s">
+      <c r="C43" s="326" t="s">
         <v>1266</v>
       </c>
       <c r="D43" s="187" t="s">
@@ -12481,7 +12493,7 @@
       <c r="E43" s="168" t="s">
         <v>644</v>
       </c>
-      <c r="I43" s="328"/>
+      <c r="I43" s="327"/>
       <c r="J43" s="203" t="s">
         <v>111</v>
       </c>
@@ -12490,14 +12502,14 @@
       </c>
     </row>
     <row r="44" spans="3:11" ht="30.75" thickBot="1">
-      <c r="C44" s="328"/>
+      <c r="C44" s="327"/>
       <c r="D44" s="81" t="s">
         <v>679</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>680</v>
       </c>
-      <c r="I44" s="329"/>
+      <c r="I44" s="328"/>
       <c r="J44" s="206" t="s">
         <v>114</v>
       </c>
@@ -12506,14 +12518,14 @@
       </c>
     </row>
     <row r="45" spans="3:11" ht="30">
-      <c r="C45" s="328"/>
+      <c r="C45" s="327"/>
       <c r="D45" s="81" t="s">
         <v>645</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="I45" s="328" t="s">
+      <c r="I45" s="327" t="s">
         <v>1266</v>
       </c>
       <c r="J45" s="207" t="s">
@@ -12524,14 +12536,14 @@
       </c>
     </row>
     <row r="46" spans="3:11" ht="30">
-      <c r="C46" s="328"/>
+      <c r="C46" s="327"/>
       <c r="D46" s="81" t="s">
         <v>653</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="I46" s="328"/>
+      <c r="I46" s="327"/>
       <c r="J46" s="203" t="s">
         <v>23</v>
       </c>
@@ -12540,14 +12552,14 @@
       </c>
     </row>
     <row r="47" spans="3:11" ht="30">
-      <c r="C47" s="328"/>
+      <c r="C47" s="327"/>
       <c r="D47" s="81" t="s">
         <v>656</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="I47" s="328"/>
+      <c r="I47" s="327"/>
       <c r="J47" s="203" t="s">
         <v>38</v>
       </c>
@@ -12556,14 +12568,14 @@
       </c>
     </row>
     <row r="48" spans="3:11" ht="30">
-      <c r="C48" s="328"/>
+      <c r="C48" s="327"/>
       <c r="D48" s="81" t="s">
         <v>659</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>577</v>
       </c>
-      <c r="I48" s="328"/>
+      <c r="I48" s="327"/>
       <c r="J48" s="203" t="s">
         <v>48</v>
       </c>
@@ -12572,14 +12584,14 @@
       </c>
     </row>
     <row r="49" spans="3:11" ht="30">
-      <c r="C49" s="328"/>
+      <c r="C49" s="327"/>
       <c r="D49" s="81" t="s">
         <v>664</v>
       </c>
       <c r="E49" s="15" t="s">
         <v>610</v>
       </c>
-      <c r="I49" s="328"/>
+      <c r="I49" s="327"/>
       <c r="J49" s="203" t="s">
         <v>41</v>
       </c>
@@ -12588,14 +12600,14 @@
       </c>
     </row>
     <row r="50" spans="3:11" ht="30">
-      <c r="C50" s="328"/>
+      <c r="C50" s="327"/>
       <c r="D50" s="81" t="s">
         <v>665</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="I50" s="328"/>
+      <c r="I50" s="327"/>
       <c r="J50" s="203" t="s">
         <v>32</v>
       </c>
@@ -12604,14 +12616,14 @@
       </c>
     </row>
     <row r="51" spans="3:11" ht="45">
-      <c r="C51" s="328"/>
+      <c r="C51" s="327"/>
       <c r="D51" s="81" t="s">
         <v>666</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="I51" s="328"/>
+      <c r="I51" s="327"/>
       <c r="J51" s="203" t="s">
         <v>51</v>
       </c>
@@ -12620,14 +12632,14 @@
       </c>
     </row>
     <row r="52" spans="3:11" ht="30">
-      <c r="C52" s="328"/>
+      <c r="C52" s="327"/>
       <c r="D52" s="81" t="s">
         <v>667</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="I52" s="328"/>
+      <c r="I52" s="327"/>
       <c r="J52" s="203" t="s">
         <v>73</v>
       </c>
@@ -12636,14 +12648,14 @@
       </c>
     </row>
     <row r="53" spans="3:11" ht="30">
-      <c r="C53" s="328"/>
+      <c r="C53" s="327"/>
       <c r="D53" s="81" t="s">
         <v>668</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>1308</v>
       </c>
-      <c r="I53" s="328"/>
+      <c r="I53" s="327"/>
       <c r="J53" s="203" t="s">
         <v>56</v>
       </c>
@@ -12652,14 +12664,14 @@
       </c>
     </row>
     <row r="54" spans="3:11" ht="30">
-      <c r="C54" s="328"/>
+      <c r="C54" s="327"/>
       <c r="D54" s="81" t="s">
         <v>672</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="I54" s="328"/>
+      <c r="I54" s="327"/>
       <c r="J54" s="203" t="s">
         <v>63</v>
       </c>
@@ -12668,14 +12680,14 @@
       </c>
     </row>
     <row r="55" spans="3:11" ht="15.75" thickBot="1">
-      <c r="C55" s="329"/>
+      <c r="C55" s="328"/>
       <c r="D55" s="188" t="s">
         <v>674</v>
       </c>
       <c r="E55" s="23" t="s">
         <v>513</v>
       </c>
-      <c r="I55" s="328"/>
+      <c r="I55" s="327"/>
       <c r="J55" s="203" t="s">
         <v>66</v>
       </c>
@@ -12684,7 +12696,7 @@
       </c>
     </row>
     <row r="56" spans="3:11" ht="45.75" thickBot="1">
-      <c r="I56" s="329"/>
+      <c r="I56" s="328"/>
       <c r="J56" s="206" t="s">
         <v>13</v>
       </c>
@@ -12697,16 +12709,16 @@
     </row>
     <row r="60" spans="3:11" ht="15.75" thickBot="1"/>
     <row r="61" spans="3:11" ht="15.75" thickBot="1">
-      <c r="C61" s="292" t="s">
+      <c r="C61" s="300" t="s">
         <v>1449</v>
       </c>
-      <c r="D61" s="293"/>
-      <c r="E61" s="293"/>
-      <c r="F61" s="293"/>
-      <c r="G61" s="293"/>
-      <c r="H61" s="293"/>
-      <c r="I61" s="293"/>
-      <c r="J61" s="294"/>
+      <c r="D61" s="301"/>
+      <c r="E61" s="301"/>
+      <c r="F61" s="301"/>
+      <c r="G61" s="301"/>
+      <c r="H61" s="301"/>
+      <c r="I61" s="301"/>
+      <c r="J61" s="302"/>
       <c r="K61" s="7"/>
     </row>
     <row r="62" spans="3:11">
@@ -12736,7 +12748,7 @@
       </c>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="314"/>
+      <c r="C63" s="312"/>
       <c r="D63" s="25" t="s">
         <v>1256</v>
       </c>
@@ -12760,7 +12772,7 @@
       </c>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="315"/>
+      <c r="C64" s="313"/>
       <c r="D64" s="25" t="s">
         <v>1358</v>
       </c>
@@ -12784,88 +12796,88 @@
       </c>
     </row>
     <row r="65" spans="3:10">
-      <c r="C65" s="315"/>
+      <c r="C65" s="313"/>
       <c r="D65" s="25" t="s">
         <v>1359</v>
       </c>
       <c r="E65" s="25" t="s">
         <v>1163</v>
       </c>
-      <c r="F65" s="317"/>
+      <c r="F65" s="315"/>
       <c r="G65" s="14" t="s">
         <v>1409</v>
       </c>
       <c r="H65" s="14" t="s">
         <v>1346</v>
       </c>
-      <c r="I65" s="317"/>
-      <c r="J65" s="320"/>
+      <c r="I65" s="315"/>
+      <c r="J65" s="330"/>
     </row>
     <row r="66" spans="3:10">
-      <c r="C66" s="315"/>
+      <c r="C66" s="313"/>
       <c r="D66" s="25" t="s">
         <v>1360</v>
       </c>
-      <c r="E66" s="317"/>
-      <c r="F66" s="318"/>
+      <c r="E66" s="315"/>
+      <c r="F66" s="316"/>
       <c r="G66" s="14" t="s">
         <v>1410</v>
       </c>
       <c r="H66" s="14" t="s">
         <v>1339</v>
       </c>
-      <c r="I66" s="318"/>
-      <c r="J66" s="321"/>
+      <c r="I66" s="316"/>
+      <c r="J66" s="331"/>
     </row>
     <row r="67" spans="3:10">
-      <c r="C67" s="315"/>
-      <c r="D67" s="317"/>
-      <c r="E67" s="318"/>
-      <c r="F67" s="318"/>
+      <c r="C67" s="313"/>
+      <c r="D67" s="315"/>
+      <c r="E67" s="316"/>
+      <c r="F67" s="316"/>
       <c r="G67" s="14" t="s">
         <v>1343</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="I67" s="318"/>
-      <c r="J67" s="321"/>
+      <c r="I67" s="316"/>
+      <c r="J67" s="331"/>
     </row>
     <row r="68" spans="3:10">
-      <c r="C68" s="315"/>
-      <c r="D68" s="318"/>
-      <c r="E68" s="318"/>
-      <c r="F68" s="318"/>
+      <c r="C68" s="313"/>
+      <c r="D68" s="316"/>
+      <c r="E68" s="316"/>
+      <c r="F68" s="316"/>
       <c r="G68" s="14" t="s">
         <v>1345</v>
       </c>
-      <c r="H68" s="317"/>
-      <c r="I68" s="318"/>
-      <c r="J68" s="321"/>
+      <c r="H68" s="315"/>
+      <c r="I68" s="316"/>
+      <c r="J68" s="331"/>
     </row>
     <row r="69" spans="3:10">
-      <c r="C69" s="315"/>
-      <c r="D69" s="318"/>
-      <c r="E69" s="318"/>
-      <c r="F69" s="318"/>
+      <c r="C69" s="313"/>
+      <c r="D69" s="316"/>
+      <c r="E69" s="316"/>
+      <c r="F69" s="316"/>
       <c r="G69" s="14" t="s">
         <v>1411</v>
       </c>
-      <c r="H69" s="318"/>
-      <c r="I69" s="318"/>
-      <c r="J69" s="321"/>
+      <c r="H69" s="316"/>
+      <c r="I69" s="316"/>
+      <c r="J69" s="331"/>
     </row>
     <row r="70" spans="3:10" ht="15.75" thickBot="1">
-      <c r="C70" s="316"/>
-      <c r="D70" s="319"/>
-      <c r="E70" s="319"/>
-      <c r="F70" s="319"/>
+      <c r="C70" s="314"/>
+      <c r="D70" s="317"/>
+      <c r="E70" s="317"/>
+      <c r="F70" s="317"/>
       <c r="G70" s="22" t="s">
         <v>1344</v>
       </c>
-      <c r="H70" s="319"/>
-      <c r="I70" s="319"/>
-      <c r="J70" s="322"/>
+      <c r="H70" s="317"/>
+      <c r="I70" s="317"/>
+      <c r="J70" s="332"/>
     </row>
     <row r="71" spans="3:10">
       <c r="E71" s="189"/>
@@ -13426,6 +13438,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="I65:I70"/>
+    <mergeCell ref="J65:J70"/>
+    <mergeCell ref="C63:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F65:F70"/>
+    <mergeCell ref="H68:H70"/>
     <mergeCell ref="C61:J61"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="N10:N19"/>
@@ -13442,13 +13461,6 @@
     <mergeCell ref="I45:I56"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C31:C42"/>
-    <mergeCell ref="I65:I70"/>
-    <mergeCell ref="J65:J70"/>
-    <mergeCell ref="C63:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F65:F70"/>
-    <mergeCell ref="H68:H70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13924,7 +13936,7 @@
   <sheetData>
     <row r="3" spans="5:8" ht="15.75" thickBot="1">
       <c r="E3" s="7" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="4" spans="5:8" ht="15.75" thickBot="1">
@@ -13935,10 +13947,10 @@
         <v>1495</v>
       </c>
       <c r="G4" s="172" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="H4" s="173" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="5" spans="5:8" ht="30">
@@ -13949,10 +13961,10 @@
         <v>1497</v>
       </c>
       <c r="G5" s="249" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="H5" s="251" t="s">
-        <v>1503</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="6" spans="5:8" ht="30">
@@ -13963,10 +13975,10 @@
         <v>1500</v>
       </c>
       <c r="G6" s="166" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="H6" s="252" t="s">
-        <v>1502</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="7" spans="5:8" ht="30.75" thickBot="1">
@@ -13974,18 +13986,18 @@
         <v>1499</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="G7" s="250" t="s">
         <v>1501</v>
       </c>
       <c r="H7" s="253" t="s">
-        <v>1524</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="11" spans="5:8">
       <c r="E11" s="7" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="12" spans="5:8" ht="15.75" thickBot="1"/>
@@ -13997,71 +14009,71 @@
         <v>1495</v>
       </c>
       <c r="G13" s="223" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="H13" s="224" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="14" spans="5:8" ht="48.75" customHeight="1">
       <c r="E14" s="13" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>1497</v>
       </c>
       <c r="G14" s="166" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="H14" s="252" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="15" spans="5:8" ht="45">
       <c r="E15" s="13" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="G15" s="166" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="H15" s="252" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="16" spans="5:8" ht="30">
       <c r="E16" s="13" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="G16" s="166" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H16" s="252" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="17" spans="5:8" ht="30.75" thickBot="1">
       <c r="E17" s="21" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="G17" s="250" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H17" s="253" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8">
+      <c r="E19" s="254" t="s">
         <v>1519</v>
-      </c>
-      <c r="H17" s="253" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="19" spans="5:8">
-      <c r="E19" s="331" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="20" spans="5:8" ht="15.75" thickBot="1"/>
@@ -14073,66 +14085,66 @@
         <v>1495</v>
       </c>
       <c r="G21" s="223" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="H21" s="224" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="22" spans="5:8" ht="45">
       <c r="E22" s="13" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>1497</v>
       </c>
       <c r="G22" s="166" t="s">
-        <v>1531</v>
+        <v>1524</v>
       </c>
       <c r="H22" s="252" t="s">
-        <v>1520</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="23" spans="5:8" ht="45">
       <c r="E23" s="13" t="s">
-        <v>1528</v>
+        <v>1521</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>1514</v>
-      </c>
-      <c r="G23" s="332" t="s">
-        <v>1532</v>
+        <v>1512</v>
+      </c>
+      <c r="G23" s="255" t="s">
+        <v>1525</v>
       </c>
       <c r="H23" s="252" t="s">
-        <v>1521</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="24" spans="5:8" ht="30">
       <c r="E24" s="13" t="s">
-        <v>1529</v>
+        <v>1522</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="G24" s="166" t="s">
+        <v>1516</v>
+      </c>
+      <c r="H24" s="252" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="25" spans="5:8" ht="45.75" thickBot="1">
+      <c r="E25" s="21" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F25" s="22" t="s">
         <v>1518</v>
       </c>
-      <c r="H24" s="252" t="s">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="25" spans="5:8" ht="30.75" thickBot="1">
-      <c r="E25" s="21" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>1523</v>
-      </c>
       <c r="G25" s="250" t="s">
-        <v>1533</v>
+        <v>1526</v>
       </c>
       <c r="H25" s="253" t="s">
-        <v>1525</v>
+        <v>1537</v>
       </c>
     </row>
   </sheetData>
@@ -14163,11 +14175,11 @@
       <c r="C2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="260" t="s">
+      <c r="D2" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="261"/>
-      <c r="F2" s="262"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="264"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="3:10" ht="15.75" thickBot="1">
@@ -14307,11 +14319,11 @@
       <c r="F12" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="263" t="s">
+      <c r="H12" s="265" t="s">
         <v>224</v>
       </c>
-      <c r="I12" s="263"/>
-      <c r="J12" s="263"/>
+      <c r="I12" s="265"/>
+      <c r="J12" s="265"/>
     </row>
     <row r="13" spans="3:10">
       <c r="D13" s="36" t="s">
@@ -15986,11 +15998,11 @@
       <c r="C3" s="40" t="s">
         <v>894</v>
       </c>
-      <c r="D3" s="264" t="s">
+      <c r="D3" s="266" t="s">
         <v>948</v>
       </c>
-      <c r="E3" s="265"/>
-      <c r="F3" s="266"/>
+      <c r="E3" s="267"/>
+      <c r="F3" s="268"/>
       <c r="I3" s="7" t="s">
         <v>1017</v>
       </c>
@@ -16600,11 +16612,11 @@
       <c r="C2" s="41" t="s">
         <v>746</v>
       </c>
-      <c r="D2" s="263" t="s">
+      <c r="D2" s="265" t="s">
         <v>850</v>
       </c>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="265"/>
       <c r="I2" s="7" t="s">
         <v>848</v>
       </c>
@@ -17199,7 +17211,7 @@
       </c>
     </row>
     <row r="60" spans="4:6">
-      <c r="D60" s="267" t="s">
+      <c r="D60" s="269" t="s">
         <v>1265</v>
       </c>
       <c r="E60" s="194" t="s">
@@ -17210,7 +17222,7 @@
       </c>
     </row>
     <row r="61" spans="4:6">
-      <c r="D61" s="268"/>
+      <c r="D61" s="270"/>
       <c r="E61" s="13" t="s">
         <v>1277</v>
       </c>
@@ -17219,7 +17231,7 @@
       </c>
     </row>
     <row r="62" spans="4:6">
-      <c r="D62" s="268"/>
+      <c r="D62" s="270"/>
       <c r="E62" s="13" t="s">
         <v>1278</v>
       </c>
@@ -17228,7 +17240,7 @@
       </c>
     </row>
     <row r="63" spans="4:6">
-      <c r="D63" s="268"/>
+      <c r="D63" s="270"/>
       <c r="E63" s="13" t="s">
         <v>1279</v>
       </c>
@@ -17237,7 +17249,7 @@
       </c>
     </row>
     <row r="64" spans="4:6">
-      <c r="D64" s="268"/>
+      <c r="D64" s="270"/>
       <c r="E64" s="13" t="s">
         <v>1280</v>
       </c>
@@ -17246,7 +17258,7 @@
       </c>
     </row>
     <row r="65" spans="4:6">
-      <c r="D65" s="268"/>
+      <c r="D65" s="270"/>
       <c r="E65" s="13" t="s">
         <v>1281</v>
       </c>
@@ -17255,7 +17267,7 @@
       </c>
     </row>
     <row r="66" spans="4:6">
-      <c r="D66" s="268"/>
+      <c r="D66" s="270"/>
       <c r="E66" s="13" t="s">
         <v>111</v>
       </c>
@@ -17264,7 +17276,7 @@
       </c>
     </row>
     <row r="67" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D67" s="269"/>
+      <c r="D67" s="271"/>
       <c r="E67" s="21" t="s">
         <v>114</v>
       </c>
@@ -17299,11 +17311,11 @@
       <c r="B3" s="40" t="s">
         <v>894</v>
       </c>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="266" t="s">
         <v>948</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="E3" s="266"/>
+      <c r="D3" s="267"/>
+      <c r="E3" s="268"/>
       <c r="H3" t="s">
         <v>953</v>
       </c>
@@ -17717,11 +17729,11 @@
       <c r="C3" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D3" s="260" t="s">
+      <c r="D3" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="261"/>
-      <c r="F3" s="262"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="264"/>
       <c r="H3" s="41" t="s">
         <v>456</v>
       </c>
@@ -17749,11 +17761,11 @@
     </row>
     <row r="5" spans="3:9" ht="15.75">
       <c r="C5" s="7"/>
-      <c r="D5" s="273" t="s">
+      <c r="D5" s="275" t="s">
         <v>458</v>
       </c>
-      <c r="E5" s="274"/>
-      <c r="F5" s="275"/>
+      <c r="E5" s="276"/>
+      <c r="F5" s="277"/>
       <c r="H5" s="44" t="s">
         <v>460</v>
       </c>
@@ -17857,11 +17869,11 @@
       <c r="F12" s="53"/>
     </row>
     <row r="13" spans="3:9" ht="15.75">
-      <c r="D13" s="273" t="s">
+      <c r="D13" s="275" t="s">
         <v>460</v>
       </c>
-      <c r="E13" s="274"/>
-      <c r="F13" s="275"/>
+      <c r="E13" s="276"/>
+      <c r="F13" s="277"/>
     </row>
     <row r="14" spans="3:9" ht="31.5">
       <c r="D14" s="54" t="s">
@@ -18063,11 +18075,11 @@
       <c r="F28" s="53"/>
     </row>
     <row r="29" spans="4:9" ht="15.75">
-      <c r="D29" s="276" t="s">
+      <c r="D29" s="278" t="s">
         <v>464</v>
       </c>
-      <c r="E29" s="277"/>
-      <c r="F29" s="278"/>
+      <c r="E29" s="279"/>
+      <c r="F29" s="280"/>
     </row>
     <row r="30" spans="4:9" ht="15.75">
       <c r="D30" s="103" t="s">
@@ -18185,11 +18197,11 @@
       <c r="F40" s="53"/>
     </row>
     <row r="41" spans="4:6" ht="15.75">
-      <c r="D41" s="270" t="s">
+      <c r="D41" s="272" t="s">
         <v>472</v>
       </c>
-      <c r="E41" s="271"/>
-      <c r="F41" s="272"/>
+      <c r="E41" s="273"/>
+      <c r="F41" s="274"/>
     </row>
     <row r="42" spans="4:6" ht="15.75">
       <c r="D42" s="46" t="s">
@@ -18323,11 +18335,11 @@
       <c r="F54" s="53"/>
     </row>
     <row r="55" spans="4:6" ht="15.75">
-      <c r="D55" s="270" t="s">
+      <c r="D55" s="272" t="s">
         <v>476</v>
       </c>
-      <c r="E55" s="271"/>
-      <c r="F55" s="272"/>
+      <c r="E55" s="273"/>
+      <c r="F55" s="274"/>
     </row>
     <row r="56" spans="4:6" ht="15.75">
       <c r="D56" s="61" t="s">
@@ -18409,11 +18421,11 @@
       <c r="B2" s="90" t="s">
         <v>894</v>
       </c>
-      <c r="C2" s="279" t="s">
+      <c r="C2" s="281" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="262"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="264"/>
       <c r="H2" s="59" t="s">
         <v>511</v>
       </c>
@@ -18667,11 +18679,11 @@
       <c r="C2" s="75" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="264" t="s">
+      <c r="D2" s="266" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="265"/>
-      <c r="F2" s="266"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="268"/>
       <c r="I2" t="s">
         <v>569</v>
       </c>
@@ -19065,11 +19077,11 @@
       <c r="C39" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D39" s="260" t="s">
+      <c r="D39" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="E39" s="261"/>
-      <c r="F39" s="262"/>
+      <c r="E39" s="263"/>
+      <c r="F39" s="264"/>
       <c r="H39" t="s">
         <v>635</v>
       </c>
@@ -19467,11 +19479,11 @@
       <c r="C76" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D76" s="260" t="s">
+      <c r="D76" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="E76" s="261"/>
-      <c r="F76" s="262"/>
+      <c r="E76" s="263"/>
+      <c r="F76" s="264"/>
       <c r="H76" t="s">
         <v>688</v>
       </c>
@@ -19884,11 +19896,11 @@
       <c r="C114" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D114" s="260" t="s">
+      <c r="D114" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="E114" s="261"/>
-      <c r="F114" s="262"/>
+      <c r="E114" s="263"/>
+      <c r="F114" s="264"/>
       <c r="H114" s="2" t="s">
         <v>637</v>
       </c>
@@ -20220,11 +20232,11 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="283" t="s">
+      <c r="D3" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="284"/>
-      <c r="F3" s="285"/>
+      <c r="E3" s="286"/>
+      <c r="F3" s="287"/>
       <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
@@ -20243,11 +20255,11 @@
     </row>
     <row r="5" spans="3:9" ht="15.75" thickBot="1">
       <c r="C5" s="7"/>
-      <c r="D5" s="280" t="s">
+      <c r="D5" s="282" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="281"/>
-      <c r="F5" s="282"/>
+      <c r="E5" s="283"/>
+      <c r="F5" s="284"/>
       <c r="H5" s="8" t="s">
         <v>6</v>
       </c>
@@ -20497,11 +20509,11 @@
     </row>
     <row r="24" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="25" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D25" s="286" t="s">
+      <c r="D25" s="288" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="287"/>
-      <c r="F25" s="288"/>
+      <c r="E25" s="289"/>
+      <c r="F25" s="290"/>
     </row>
     <row r="26" spans="4:6">
       <c r="D26" s="110" t="s">
@@ -20736,11 +20748,11 @@
     </row>
     <row r="47" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="48" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D48" s="280" t="s">
+      <c r="D48" s="282" t="s">
         <v>1312</v>
       </c>
-      <c r="E48" s="281"/>
-      <c r="F48" s="282"/>
+      <c r="E48" s="283"/>
+      <c r="F48" s="284"/>
     </row>
     <row r="49" spans="4:6">
       <c r="D49" s="10" t="s">
@@ -21063,11 +21075,11 @@
     </row>
     <row r="78" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="79" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D79" s="289" t="s">
+      <c r="D79" s="291" t="s">
         <v>21</v>
       </c>
-      <c r="E79" s="290"/>
-      <c r="F79" s="291"/>
+      <c r="E79" s="292"/>
+      <c r="F79" s="293"/>
     </row>
     <row r="80" spans="4:6">
       <c r="D80" s="118" t="s">
@@ -21214,11 +21226,11 @@
     </row>
     <row r="93" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="94" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D94" s="289" t="s">
+      <c r="D94" s="291" t="s">
         <v>30</v>
       </c>
-      <c r="E94" s="290"/>
-      <c r="F94" s="291"/>
+      <c r="E94" s="292"/>
+      <c r="F94" s="293"/>
     </row>
     <row r="95" spans="4:6">
       <c r="D95" s="110" t="s">
@@ -21332,11 +21344,11 @@
     </row>
     <row r="105" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="106" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D106" s="280" t="s">
+      <c r="D106" s="282" t="s">
         <v>26</v>
       </c>
-      <c r="E106" s="281"/>
-      <c r="F106" s="282"/>
+      <c r="E106" s="283"/>
+      <c r="F106" s="284"/>
     </row>
     <row r="107" spans="4:6">
       <c r="D107" s="110" t="s">

--- a/Relatorio/APIS_detalhe_Campos_v23_06.xlsx
+++ b/Relatorio/APIS_detalhe_Campos_v23_06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ESTG 25_26\2S\ProjetoInformatico\Prototipo\Versoes\weatherSense\Relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822E9191-E502-4DC6-93AE-18B0118FB428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07A8ACF-5122-4F2A-B59A-0F6C1D763BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="14" xr2:uid="{E6E5DD2F-D0B6-44E9-B2EB-37380A5D374B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="15" xr2:uid="{E6E5DD2F-D0B6-44E9-B2EB-37380A5D374B}"/>
   </bookViews>
   <sheets>
     <sheet name="GERAL" sheetId="9" r:id="rId1"/>
@@ -27,7 +27,8 @@
     <sheet name="Campos_IMPL_Prev_Mar" sheetId="13" r:id="rId12"/>
     <sheet name="Campos_IMPL_Prev_Terra" sheetId="14" r:id="rId13"/>
     <sheet name="Tab_FonteDimensao" sheetId="15" r:id="rId14"/>
-    <sheet name="Folha1" sheetId="16" r:id="rId15"/>
+    <sheet name="Endpoints Relat" sheetId="16" r:id="rId15"/>
+    <sheet name="Folha1" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3361" uniqueCount="1538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3565" uniqueCount="1660">
   <si>
     <t>Foreca</t>
   </si>
@@ -5756,12 +5757,444 @@
   <si>
     <t>/data/forecast/marine/records?lat=39.9300&amp;lon=-9.1200&amp;page=1&amp;page_size=10&amp;search=&amp;variable=seaTemperature&amp;variable=seaTemperature</t>
   </si>
+  <si>
+    <t xml:space="preserve">Variável </t>
+  </si>
+  <si>
+    <t>Vento</t>
+  </si>
+  <si>
+    <t>Pressão</t>
+  </si>
+  <si>
+    <t>24.1 ºC</t>
+  </si>
+  <si>
+    <t>24.5 ºC</t>
+  </si>
+  <si>
+    <t>70 %</t>
+  </si>
+  <si>
+    <t>68 %</t>
+  </si>
+  <si>
+    <t>Diferença</t>
+  </si>
+  <si>
+    <t>-0.4 ºC</t>
+  </si>
+  <si>
+    <t>-2 %</t>
+  </si>
+  <si>
+    <t>12,0 km/h</t>
+  </si>
+  <si>
+    <t>11,5 km/h</t>
+  </si>
+  <si>
+    <t>1016 hPa</t>
+  </si>
+  <si>
+    <t>1015 hPa</t>
+  </si>
+  <si>
+    <t>10 km</t>
+  </si>
+  <si>
+    <t>0 km</t>
+  </si>
+  <si>
+    <t>+1 hPA</t>
+  </si>
+  <si>
+    <t>+0,5 km/h</t>
+  </si>
+  <si>
+    <t>Indicador</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>↑</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Temperatura (ºc)</t>
+  </si>
+  <si>
+    <t>ICON</t>
+  </si>
+  <si>
+    <t>ARPEGE</t>
+  </si>
+  <si>
+    <t>Maior valor</t>
+  </si>
+  <si>
+    <t>Menor valor</t>
+  </si>
+  <si>
+    <t>Spread (Máx - Mín)</t>
+  </si>
+  <si>
+    <t>Pontuação atribuída</t>
+  </si>
+  <si>
+    <t>23.8</t>
+  </si>
+  <si>
+    <t>24.1</t>
+  </si>
+  <si>
+    <t>24.3</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>24.5</t>
+  </si>
+  <si>
+    <t>0,7 ºC</t>
+  </si>
+  <si>
+    <t>Variável</t>
+  </si>
+  <si>
+    <t>Excelente (100%)</t>
+  </si>
+  <si>
+    <t>Boa (85%)</t>
+  </si>
+  <si>
+    <t>Moderada (65%)</t>
+  </si>
+  <si>
+    <t>Baixa (45%)</t>
+  </si>
+  <si>
+    <t>Muito Baixa (25%)</t>
+  </si>
+  <si>
+    <t>≤ 1 °C</t>
+  </si>
+  <si>
+    <t>≤ 2 °C</t>
+  </si>
+  <si>
+    <t>≤ 4 °C</t>
+  </si>
+  <si>
+    <t>≤ 6 °C</t>
+  </si>
+  <si>
+    <t>&gt; 6 °C</t>
+  </si>
+  <si>
+    <t>≤ 5 %</t>
+  </si>
+  <si>
+    <t>≤ 10 %</t>
+  </si>
+  <si>
+    <t>≤ 20 %</t>
+  </si>
+  <si>
+    <t>≤ 30 %</t>
+  </si>
+  <si>
+    <t>&gt; 30 %</t>
+  </si>
+  <si>
+    <t>≤ 3 km/h</t>
+  </si>
+  <si>
+    <t>≤ 7 km/h</t>
+  </si>
+  <si>
+    <t>≤ 12 km/h</t>
+  </si>
+  <si>
+    <t>≤ 20 km/h</t>
+  </si>
+  <si>
+    <t>&gt; 20 km/h</t>
+  </si>
+  <si>
+    <t>≤ 0,5 mm</t>
+  </si>
+  <si>
+    <t>≤ 2 mm</t>
+  </si>
+  <si>
+    <t>≤ 5 mm</t>
+  </si>
+  <si>
+    <t>≤ 10 mm</t>
+  </si>
+  <si>
+    <t>&gt; 10 mm</t>
+  </si>
+  <si>
+    <t>≤ 1 hPa</t>
+  </si>
+  <si>
+    <t>≤ 3 hPa</t>
+  </si>
+  <si>
+    <t>≤ 6 hPa</t>
+  </si>
+  <si>
+    <t>≤ 10 hPa</t>
+  </si>
+  <si>
+    <t>&gt; 10 hPa</t>
+  </si>
+  <si>
+    <t>≤ 2 km</t>
+  </si>
+  <si>
+    <t>≤ 5 km</t>
+  </si>
+  <si>
+    <t>≤ 10 km</t>
+  </si>
+  <si>
+    <t>≤ 20 km</t>
+  </si>
+  <si>
+    <t>&gt; 20 km</t>
+  </si>
+  <si>
+    <t>Condição</t>
+  </si>
+  <si>
+    <t>Classificação</t>
+  </si>
+  <si>
+    <t>Operacional</t>
+  </si>
+  <si>
+    <t>Atenção</t>
+  </si>
+  <si>
+    <t>Não recomendado</t>
+  </si>
+  <si>
+    <t>&gt; 30 km/h</t>
+  </si>
+  <si>
+    <t>&gt; 1 mm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&gt; 20 km/h e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 30 km/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&gt; 0 mm e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1 mm</t>
+    </r>
+  </si>
+  <si>
+    <t>Penalização (pontos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 3 km </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 3 km </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>e &lt; 5 km</t>
+    </r>
+  </si>
+  <si>
+    <t>80 % - 100 %</t>
+  </si>
+  <si>
+    <t>60 % - 79 %</t>
+  </si>
+  <si>
+    <t>&lt; 60 %</t>
+  </si>
+  <si>
+    <t>+30</t>
+  </si>
+  <si>
+    <t>+20</t>
+  </si>
+  <si>
+    <t>+15</t>
+  </si>
+  <si>
+    <t>+25</t>
+  </si>
+  <si>
+    <t>≥ 30 ºC</t>
+  </si>
+  <si>
+    <t>≥ 25 ºC e &lt; 30 ºC</t>
+  </si>
+  <si>
+    <t>&gt; 30 % e ≤ 45 %</t>
+  </si>
+  <si>
+    <t>≥ 25 km/h</t>
+  </si>
+  <si>
+    <t>≥ 15 km/h e &lt; 25 km/h</t>
+  </si>
+  <si>
+    <t>Baixo</t>
+  </si>
+  <si>
+    <t>Moderado</t>
+  </si>
+  <si>
+    <t>Elevado</t>
+  </si>
+  <si>
+    <t>Muito Elevado</t>
+  </si>
+  <si>
+    <t>Incremento (pontos)</t>
+  </si>
+  <si>
+    <t>= 0 mm</t>
+  </si>
+  <si>
+    <t>Altura da onda</t>
+  </si>
+  <si>
+    <t>Período da onda</t>
+  </si>
+  <si>
+    <t>Condicionado</t>
+  </si>
+  <si>
+    <t>&gt; 20 km/h e ≤ 30 km/h</t>
+  </si>
+  <si>
+    <t>&gt; 45 km/h</t>
+  </si>
+  <si>
+    <t>&gt; 2,5 m</t>
+  </si>
+  <si>
+    <t>&lt; 4 s</t>
+  </si>
+  <si>
+    <t>&gt; 15 km/h e ≤ 20 km/h</t>
+  </si>
+  <si>
+    <t>25 % - 49 %</t>
+  </si>
+  <si>
+    <t>50 % - 74 %</t>
+  </si>
+  <si>
+    <t>75 % - 100 %</t>
+  </si>
+  <si>
+    <t>0 % - 24 %</t>
+  </si>
+  <si>
+    <t>&gt; 1,5 m e ≤ 2,5 m</t>
+  </si>
+  <si>
+    <t>&gt; 1,0 m e ≤ 1,5 m</t>
+  </si>
+  <si>
+    <t>&gt; 25 km/h e ≤ 35 km/h</t>
+  </si>
+  <si>
+    <t>&gt; 35 km/h e ≤ 45 km/h</t>
+  </si>
+  <si>
+    <t>≥ 4 s e &lt; 6 s</t>
+  </si>
+  <si>
+    <t>Altura do swell</t>
+  </si>
+  <si>
+    <t>Estável</t>
+  </si>
+  <si>
+    <t>Instável</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5915,6 +6348,46 @@
       <color rgb="FFFFA657"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -6711,7 +7184,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="333">
+  <cellXfs count="376">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7434,6 +7907,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7664,6 +8240,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8332,7 +8926,7 @@
       </c>
     </row>
     <row r="5" spans="3:12" ht="15.75">
-      <c r="C5" s="256" t="s">
+      <c r="C5" s="293" t="s">
         <v>746</v>
       </c>
       <c r="D5" s="93" t="s">
@@ -8347,21 +8941,21 @@
       <c r="G5" s="93" t="s">
         <v>1033</v>
       </c>
-      <c r="H5" s="257" t="s">
+      <c r="H5" s="294" t="s">
         <v>1034</v>
       </c>
-      <c r="I5" s="258" t="s">
+      <c r="I5" s="295" t="s">
         <v>1035</v>
       </c>
-      <c r="J5" s="258" t="s">
+      <c r="J5" s="295" t="s">
         <v>1036</v>
       </c>
-      <c r="K5" s="259" t="s">
+      <c r="K5" s="296" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="6" spans="3:12" ht="15.75">
-      <c r="C6" s="256"/>
+      <c r="C6" s="293"/>
       <c r="D6" s="93" t="s">
         <v>1038</v>
       </c>
@@ -8374,13 +8968,13 @@
       <c r="G6" s="93" t="s">
         <v>1041</v>
       </c>
-      <c r="H6" s="257"/>
-      <c r="I6" s="258"/>
-      <c r="J6" s="258"/>
-      <c r="K6" s="260"/>
+      <c r="H6" s="294"/>
+      <c r="I6" s="295"/>
+      <c r="J6" s="295"/>
+      <c r="K6" s="297"/>
     </row>
     <row r="7" spans="3:12" ht="15.75">
-      <c r="C7" s="256"/>
+      <c r="C7" s="293"/>
       <c r="D7" s="93" t="s">
         <v>860</v>
       </c>
@@ -8393,94 +8987,94 @@
       <c r="G7" s="93" t="s">
         <v>1043</v>
       </c>
-      <c r="H7" s="257"/>
-      <c r="I7" s="258"/>
-      <c r="J7" s="258"/>
-      <c r="K7" s="261"/>
+      <c r="H7" s="294"/>
+      <c r="I7" s="295"/>
+      <c r="J7" s="295"/>
+      <c r="K7" s="298"/>
     </row>
     <row r="8" spans="3:12" ht="15.75">
-      <c r="C8" s="256" t="s">
+      <c r="C8" s="293" t="s">
         <v>1044</v>
       </c>
       <c r="D8" s="93" t="s">
         <v>1045</v>
       </c>
-      <c r="E8" s="257" t="s">
+      <c r="E8" s="294" t="s">
         <v>1046</v>
       </c>
-      <c r="F8" s="257" t="s">
+      <c r="F8" s="294" t="s">
         <v>1047</v>
       </c>
-      <c r="G8" s="257" t="s">
+      <c r="G8" s="294" t="s">
         <v>1048</v>
       </c>
-      <c r="H8" s="257" t="s">
+      <c r="H8" s="294" t="s">
         <v>1049</v>
       </c>
-      <c r="I8" s="257" t="s">
+      <c r="I8" s="294" t="s">
         <v>1050</v>
       </c>
-      <c r="J8" s="257" t="s">
+      <c r="J8" s="294" t="s">
         <v>1051</v>
       </c>
-      <c r="K8" s="259" t="s">
+      <c r="K8" s="296" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="9" spans="3:12" ht="15.75">
-      <c r="C9" s="256"/>
+      <c r="C9" s="293"/>
       <c r="D9" s="93" t="s">
         <v>1052</v>
       </c>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="261"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
+      <c r="I9" s="294"/>
+      <c r="J9" s="294"/>
+      <c r="K9" s="298"/>
     </row>
     <row r="10" spans="3:12" ht="15.75">
-      <c r="C10" s="256" t="s">
+      <c r="C10" s="293" t="s">
         <v>455</v>
       </c>
       <c r="D10" s="93" t="s">
         <v>1053</v>
       </c>
-      <c r="E10" s="257" t="s">
+      <c r="E10" s="294" t="s">
         <v>1054</v>
       </c>
-      <c r="F10" s="257" t="s">
+      <c r="F10" s="294" t="s">
         <v>1055</v>
       </c>
-      <c r="G10" s="257" t="s">
+      <c r="G10" s="294" t="s">
         <v>1048</v>
       </c>
-      <c r="H10" s="257" t="s">
+      <c r="H10" s="294" t="s">
         <v>1034</v>
       </c>
-      <c r="I10" s="257" t="s">
+      <c r="I10" s="294" t="s">
         <v>1056</v>
       </c>
-      <c r="J10" s="257" t="s">
+      <c r="J10" s="294" t="s">
         <v>1048</v>
       </c>
-      <c r="K10" s="259" t="s">
+      <c r="K10" s="296" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="11" spans="3:12" ht="15.75">
-      <c r="C11" s="256"/>
+      <c r="C11" s="293"/>
       <c r="D11" s="93" t="s">
         <v>1058</v>
       </c>
-      <c r="E11" s="257"/>
-      <c r="F11" s="257"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="261"/>
+      <c r="E11" s="294"/>
+      <c r="F11" s="294"/>
+      <c r="G11" s="294"/>
+      <c r="H11" s="294"/>
+      <c r="I11" s="294"/>
+      <c r="J11" s="294"/>
+      <c r="K11" s="298"/>
     </row>
     <row r="12" spans="3:12" ht="15.75">
       <c r="C12" s="92" t="s">
@@ -8934,7 +9528,7 @@
       <c r="G19" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="270" t="s">
+      <c r="H19" s="307" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -8960,7 +9554,7 @@
       <c r="G20" s="148" t="s">
         <v>87</v>
       </c>
-      <c r="H20" s="270"/>
+      <c r="H20" s="307"/>
     </row>
     <row r="21" spans="1:8" ht="21" customHeight="1">
       <c r="A21" s="133" t="s">
@@ -8984,7 +9578,7 @@
       <c r="G21" s="148" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="270"/>
+      <c r="H21" s="307"/>
     </row>
     <row r="22" spans="1:8" ht="21.75" customHeight="1">
       <c r="A22" s="133" t="s">
@@ -9008,7 +9602,7 @@
       <c r="G22" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="270" t="s">
+      <c r="H22" s="307" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -9034,7 +9628,7 @@
       <c r="G23" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="270"/>
+      <c r="H23" s="307"/>
     </row>
     <row r="24" spans="1:8" ht="21.75" customHeight="1">
       <c r="A24" s="133" t="s">
@@ -9058,7 +9652,7 @@
       <c r="G24" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="270"/>
+      <c r="H24" s="307"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1">
       <c r="A25" s="133" t="s">
@@ -9082,7 +9676,7 @@
       <c r="G25" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="270"/>
+      <c r="H25" s="307"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1">
       <c r="A26" s="133" t="s">
@@ -9106,7 +9700,7 @@
       <c r="G26" s="148" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="270"/>
+      <c r="H26" s="307"/>
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1">
       <c r="A27" s="133" t="s">
@@ -9128,7 +9722,7 @@
         <v>1106</v>
       </c>
       <c r="G27" s="148"/>
-      <c r="H27" s="270"/>
+      <c r="H27" s="307"/>
     </row>
     <row r="28" spans="1:8" ht="20.25" customHeight="1">
       <c r="A28" s="133" t="s">
@@ -9152,7 +9746,7 @@
       <c r="G28" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="270"/>
+      <c r="H28" s="307"/>
     </row>
     <row r="29" spans="1:8" ht="21" customHeight="1">
       <c r="A29" s="133" t="s">
@@ -9176,7 +9770,7 @@
       <c r="G29" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="270"/>
+      <c r="H29" s="307"/>
     </row>
     <row r="30" spans="1:8" ht="20.25" customHeight="1">
       <c r="A30" s="133" t="s">
@@ -9200,7 +9794,7 @@
       <c r="G30" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="270"/>
+      <c r="H30" s="307"/>
     </row>
     <row r="31" spans="1:8" ht="20.25" customHeight="1">
       <c r="A31" s="133" t="s">
@@ -9224,7 +9818,7 @@
       <c r="G31" s="148" t="s">
         <v>63</v>
       </c>
-      <c r="H31" s="270"/>
+      <c r="H31" s="307"/>
     </row>
     <row r="32" spans="1:8" ht="23.25" customHeight="1">
       <c r="A32" s="133" t="s">
@@ -9248,7 +9842,7 @@
       <c r="G32" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="270"/>
+      <c r="H32" s="307"/>
     </row>
     <row r="33" spans="1:8" ht="21" customHeight="1">
       <c r="A33" s="133" t="s">
@@ -9270,7 +9864,7 @@
         <v>1106</v>
       </c>
       <c r="G33" s="148"/>
-      <c r="H33" s="270"/>
+      <c r="H33" s="307"/>
     </row>
     <row r="34" spans="1:8" ht="20.25" customHeight="1">
       <c r="A34" s="133" t="s">
@@ -9294,7 +9888,7 @@
       <c r="G34" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="270"/>
+      <c r="H34" s="307"/>
     </row>
     <row r="35" spans="1:8" ht="21" customHeight="1">
       <c r="A35" s="133" t="s">
@@ -9316,7 +9910,7 @@
         <v>1106</v>
       </c>
       <c r="G35" s="148"/>
-      <c r="H35" s="270"/>
+      <c r="H35" s="307"/>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1">
       <c r="A36" s="133" t="s">
@@ -9338,7 +9932,7 @@
         <v>1106</v>
       </c>
       <c r="G36" s="148"/>
-      <c r="H36" s="270"/>
+      <c r="H36" s="307"/>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1">
       <c r="A37" s="133" t="s">
@@ -9362,7 +9956,7 @@
       <c r="G37" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="270"/>
+      <c r="H37" s="307"/>
     </row>
     <row r="38" spans="1:8" ht="20.25" customHeight="1">
       <c r="A38" s="133" t="s">
@@ -9386,7 +9980,7 @@
       <c r="G38" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="H38" s="270" t="s">
+      <c r="H38" s="307" t="s">
         <v>1104</v>
       </c>
     </row>
@@ -9412,7 +10006,7 @@
       <c r="G39" s="155" t="s">
         <v>114</v>
       </c>
-      <c r="H39" s="270"/>
+      <c r="H39" s="307"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="42" spans="1:8" ht="21" customHeight="1" thickBot="1">
@@ -9833,10 +10427,10 @@
   <sheetData>
     <row r="3" spans="2:14" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:14" ht="15.75" thickBot="1">
-      <c r="K4" s="297" t="s">
+      <c r="K4" s="334" t="s">
         <v>1192</v>
       </c>
-      <c r="L4" s="298"/>
+      <c r="L4" s="335"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
@@ -9850,13 +10444,13 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B6" s="300" t="s">
+      <c r="B6" s="337" t="s">
         <v>1437</v>
       </c>
-      <c r="C6" s="301"/>
-      <c r="D6" s="301"/>
-      <c r="E6" s="301"/>
-      <c r="F6" s="302"/>
+      <c r="C6" s="338"/>
+      <c r="D6" s="338"/>
+      <c r="E6" s="338"/>
+      <c r="F6" s="339"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="K6" s="161" t="s">
@@ -9890,7 +10484,7 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="303"/>
+      <c r="B8" s="340"/>
       <c r="C8" s="14" t="s">
         <v>1335</v>
       </c>
@@ -9911,7 +10505,7 @@
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="304"/>
+      <c r="B9" s="341"/>
       <c r="C9" s="14" t="s">
         <v>1336</v>
       </c>
@@ -9932,12 +10526,12 @@
       </c>
     </row>
     <row r="10" spans="2:14">
-      <c r="B10" s="304"/>
-      <c r="C10" s="306"/>
+      <c r="B10" s="341"/>
+      <c r="C10" s="343"/>
       <c r="D10" s="156" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="306"/>
+      <c r="E10" s="343"/>
       <c r="F10" s="15" t="s">
         <v>1339</v>
       </c>
@@ -9949,12 +10543,12 @@
       </c>
     </row>
     <row r="11" spans="2:14">
-      <c r="B11" s="304"/>
-      <c r="C11" s="307"/>
+      <c r="B11" s="341"/>
+      <c r="C11" s="344"/>
       <c r="D11" s="156" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="307"/>
+      <c r="E11" s="344"/>
       <c r="F11" s="15" t="s">
         <v>1340</v>
       </c>
@@ -9966,12 +10560,12 @@
       </c>
     </row>
     <row r="12" spans="2:14">
-      <c r="B12" s="304"/>
-      <c r="C12" s="307"/>
+      <c r="B12" s="341"/>
+      <c r="C12" s="344"/>
       <c r="D12" s="156" t="s">
         <v>1164</v>
       </c>
-      <c r="E12" s="307"/>
+      <c r="E12" s="344"/>
       <c r="F12" s="15" t="s">
         <v>1341</v>
       </c>
@@ -9983,10 +10577,10 @@
       </c>
     </row>
     <row r="13" spans="2:14">
-      <c r="B13" s="304"/>
-      <c r="C13" s="307"/>
-      <c r="D13" s="306"/>
-      <c r="E13" s="307"/>
+      <c r="B13" s="341"/>
+      <c r="C13" s="344"/>
+      <c r="D13" s="343"/>
+      <c r="E13" s="344"/>
       <c r="F13" s="15" t="s">
         <v>1342</v>
       </c>
@@ -9998,10 +10592,10 @@
       </c>
     </row>
     <row r="14" spans="2:14">
-      <c r="B14" s="304"/>
-      <c r="C14" s="307"/>
-      <c r="D14" s="307"/>
-      <c r="E14" s="307"/>
+      <c r="B14" s="341"/>
+      <c r="C14" s="344"/>
+      <c r="D14" s="344"/>
+      <c r="E14" s="344"/>
       <c r="F14" s="15" t="s">
         <v>1343</v>
       </c>
@@ -10013,10 +10607,10 @@
       </c>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="304"/>
-      <c r="C15" s="307"/>
-      <c r="D15" s="307"/>
-      <c r="E15" s="307"/>
+      <c r="B15" s="341"/>
+      <c r="C15" s="344"/>
+      <c r="D15" s="344"/>
+      <c r="E15" s="344"/>
       <c r="F15" s="15" t="s">
         <v>1344</v>
       </c>
@@ -10028,10 +10622,10 @@
       </c>
     </row>
     <row r="16" spans="2:14">
-      <c r="B16" s="304"/>
-      <c r="C16" s="307"/>
-      <c r="D16" s="307"/>
-      <c r="E16" s="307"/>
+      <c r="B16" s="341"/>
+      <c r="C16" s="344"/>
+      <c r="D16" s="344"/>
+      <c r="E16" s="344"/>
       <c r="F16" s="15" t="s">
         <v>1345</v>
       </c>
@@ -10043,10 +10637,10 @@
       </c>
     </row>
     <row r="17" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B17" s="305"/>
-      <c r="C17" s="308"/>
-      <c r="D17" s="308"/>
-      <c r="E17" s="308"/>
+      <c r="B17" s="342"/>
+      <c r="C17" s="345"/>
+      <c r="D17" s="345"/>
+      <c r="E17" s="345"/>
       <c r="F17" s="23" t="s">
         <v>1346</v>
       </c>
@@ -10099,11 +10693,11 @@
       <c r="H24" s="224" t="s">
         <v>1189</v>
       </c>
-      <c r="K24" s="299" t="s">
+      <c r="K24" s="336" t="s">
         <v>1194</v>
       </c>
-      <c r="L24" s="299"/>
-      <c r="M24" s="299"/>
+      <c r="L24" s="336"/>
+      <c r="M24" s="336"/>
       <c r="N24" s="174"/>
     </row>
     <row r="25" spans="2:14" ht="15.75" thickBot="1">
@@ -10144,7 +10738,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="15"/>
-      <c r="K26" s="294" t="s">
+      <c r="K26" s="331" t="s">
         <v>0</v>
       </c>
       <c r="L26" s="167" t="s">
@@ -10168,7 +10762,7 @@
         <v>20</v>
       </c>
       <c r="H27" s="26"/>
-      <c r="K27" s="295"/>
+      <c r="K27" s="332"/>
       <c r="L27" s="166" t="s">
         <v>1186</v>
       </c>
@@ -10190,7 +10784,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="169"/>
-      <c r="K28" s="295"/>
+      <c r="K28" s="332"/>
       <c r="L28" s="166" t="s">
         <v>1183</v>
       </c>
@@ -10214,7 +10808,7 @@
       <c r="H29" s="169" t="s">
         <v>1441</v>
       </c>
-      <c r="K29" s="296"/>
+      <c r="K29" s="333"/>
       <c r="L29" s="22" t="s">
         <v>1184</v>
       </c>
@@ -10236,7 +10830,7 @@
         <v>242</v>
       </c>
       <c r="H30" s="15"/>
-      <c r="K30" s="294" t="s">
+      <c r="K30" s="331" t="s">
         <v>455</v>
       </c>
       <c r="L30" s="167" t="s">
@@ -10260,7 +10854,7 @@
         <v>242</v>
       </c>
       <c r="H31" s="15"/>
-      <c r="K31" s="295"/>
+      <c r="K31" s="332"/>
       <c r="L31" s="14" t="s">
         <v>1182</v>
       </c>
@@ -10285,7 +10879,7 @@
       <c r="I32" s="182" t="s">
         <v>1190</v>
       </c>
-      <c r="K32" s="296"/>
+      <c r="K32" s="333"/>
       <c r="L32" s="22" t="s">
         <v>1184</v>
       </c>
@@ -10347,7 +10941,7 @@
         <v>25</v>
       </c>
       <c r="H35" s="15"/>
-      <c r="K35" s="294" t="s">
+      <c r="K35" s="331" t="s">
         <v>1202</v>
       </c>
       <c r="L35" s="175" t="s">
@@ -10370,7 +10964,7 @@
       <c r="H36" s="15" t="s">
         <v>1445</v>
       </c>
-      <c r="K36" s="295"/>
+      <c r="K36" s="332"/>
       <c r="L36" s="158" t="s">
         <v>1209</v>
       </c>
@@ -10389,7 +10983,7 @@
         <v>242</v>
       </c>
       <c r="H37" s="169"/>
-      <c r="K37" s="295"/>
+      <c r="K37" s="332"/>
       <c r="L37" s="158" t="s">
         <v>1210</v>
       </c>
@@ -10410,7 +11004,7 @@
       <c r="H38" s="169" t="s">
         <v>1447</v>
       </c>
-      <c r="K38" s="295"/>
+      <c r="K38" s="332"/>
       <c r="L38" s="158" t="s">
         <v>1211</v>
       </c>
@@ -10431,7 +11025,7 @@
       <c r="H39" s="169" t="s">
         <v>1191</v>
       </c>
-      <c r="K39" s="296"/>
+      <c r="K39" s="333"/>
       <c r="L39" s="159" t="s">
         <v>1212</v>
       </c>
@@ -10452,7 +11046,7 @@
       <c r="H40" s="169" t="s">
         <v>1446</v>
       </c>
-      <c r="K40" s="294" t="s">
+      <c r="K40" s="331" t="s">
         <v>1203</v>
       </c>
       <c r="L40" s="176" t="s">
@@ -10475,7 +11069,7 @@
       <c r="H41" s="15" t="s">
         <v>1445</v>
       </c>
-      <c r="K41" s="295"/>
+      <c r="K41" s="332"/>
       <c r="L41" s="177" t="s">
         <v>1214</v>
       </c>
@@ -10496,7 +11090,7 @@
       <c r="H42" s="15" t="s">
         <v>1443</v>
       </c>
-      <c r="K42" s="296"/>
+      <c r="K42" s="333"/>
       <c r="L42" s="178" t="s">
         <v>1215</v>
       </c>
@@ -10589,24 +11183,24 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:15">
-      <c r="C3" s="265" t="s">
+      <c r="C3" s="302" t="s">
         <v>1016</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="E3" s="265"/>
+      <c r="D3" s="302"/>
+      <c r="E3" s="302"/>
       <c r="F3" t="s">
         <v>1253</v>
       </c>
-      <c r="H3" s="265" t="s">
+      <c r="H3" s="302" t="s">
         <v>949</v>
       </c>
-      <c r="I3" s="265"/>
-      <c r="J3" s="265"/>
-      <c r="M3" s="265" t="s">
+      <c r="I3" s="302"/>
+      <c r="J3" s="302"/>
+      <c r="M3" s="302" t="s">
         <v>1236</v>
       </c>
-      <c r="N3" s="265"/>
-      <c r="O3" s="265"/>
+      <c r="N3" s="302"/>
+      <c r="O3" s="302"/>
     </row>
     <row r="4" spans="3:15">
       <c r="C4" s="44"/>
@@ -10626,7 +11220,7 @@
       <c r="J4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="319" t="s">
+      <c r="M4" s="356" t="s">
         <v>1217</v>
       </c>
       <c r="N4" s="40" t="s">
@@ -10637,7 +11231,7 @@
       </c>
     </row>
     <row r="5" spans="3:15">
-      <c r="C5" s="319" t="s">
+      <c r="C5" s="356" t="s">
         <v>1217</v>
       </c>
       <c r="D5" s="14" t="s">
@@ -10646,7 +11240,7 @@
       <c r="E5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="319" t="s">
+      <c r="H5" s="356" t="s">
         <v>1217</v>
       </c>
       <c r="I5" s="14" t="s">
@@ -10655,7 +11249,7 @@
       <c r="J5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="M5" s="319"/>
+      <c r="M5" s="356"/>
       <c r="N5" s="14" t="s">
         <v>871</v>
       </c>
@@ -10664,21 +11258,21 @@
       </c>
     </row>
     <row r="6" spans="3:15">
-      <c r="C6" s="319"/>
+      <c r="C6" s="356"/>
       <c r="D6" s="14" t="s">
         <v>1004</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>1219</v>
       </c>
-      <c r="H6" s="319"/>
+      <c r="H6" s="356"/>
       <c r="I6" s="14" t="s">
         <v>906</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>1227</v>
       </c>
-      <c r="M6" s="319"/>
+      <c r="M6" s="356"/>
       <c r="N6" s="14" t="s">
         <v>873</v>
       </c>
@@ -10687,21 +11281,21 @@
       </c>
     </row>
     <row r="7" spans="3:15">
-      <c r="C7" s="319"/>
+      <c r="C7" s="356"/>
       <c r="D7" s="14" t="s">
         <v>1216</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>1220</v>
       </c>
-      <c r="H7" s="319"/>
+      <c r="H7" s="356"/>
       <c r="I7" s="14" t="s">
         <v>907</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>1228</v>
       </c>
-      <c r="M7" s="319"/>
+      <c r="M7" s="356"/>
       <c r="N7" s="14" t="s">
         <v>875</v>
       </c>
@@ -10710,21 +11304,21 @@
       </c>
     </row>
     <row r="8" spans="3:15">
-      <c r="C8" s="319"/>
+      <c r="C8" s="356"/>
       <c r="D8" s="14" t="s">
         <v>1009</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>1221</v>
       </c>
-      <c r="H8" s="319"/>
+      <c r="H8" s="356"/>
       <c r="I8" s="14" t="s">
         <v>909</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>1229</v>
       </c>
-      <c r="M8" s="319"/>
+      <c r="M8" s="356"/>
       <c r="N8" s="14" t="s">
         <v>877</v>
       </c>
@@ -10733,21 +11327,21 @@
       </c>
     </row>
     <row r="9" spans="3:15">
-      <c r="C9" s="319"/>
+      <c r="C9" s="356"/>
       <c r="D9" s="14" t="s">
         <v>1011</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>1222</v>
       </c>
-      <c r="H9" s="319"/>
+      <c r="H9" s="356"/>
       <c r="I9" s="14" t="s">
         <v>919</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>1230</v>
       </c>
-      <c r="M9" s="319"/>
+      <c r="M9" s="356"/>
       <c r="N9" s="14" t="s">
         <v>879</v>
       </c>
@@ -10756,21 +11350,21 @@
       </c>
     </row>
     <row r="10" spans="3:15">
-      <c r="C10" s="319"/>
+      <c r="C10" s="356"/>
       <c r="D10" s="14" t="s">
         <v>1013</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>1223</v>
       </c>
-      <c r="H10" s="319"/>
+      <c r="H10" s="356"/>
       <c r="I10" s="14" t="s">
         <v>921</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>1231</v>
       </c>
-      <c r="M10" s="319"/>
+      <c r="M10" s="356"/>
       <c r="N10" s="14" t="s">
         <v>881</v>
       </c>
@@ -10779,7 +11373,7 @@
       </c>
     </row>
     <row r="11" spans="3:15">
-      <c r="C11" s="319" t="s">
+      <c r="C11" s="356" t="s">
         <v>1218</v>
       </c>
       <c r="D11" s="14" t="s">
@@ -10788,14 +11382,14 @@
       <c r="E11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="319"/>
+      <c r="H11" s="356"/>
       <c r="I11" s="14" t="s">
         <v>923</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>1232</v>
       </c>
-      <c r="M11" s="319"/>
+      <c r="M11" s="356"/>
       <c r="N11" s="14" t="s">
         <v>883</v>
       </c>
@@ -10804,21 +11398,21 @@
       </c>
     </row>
     <row r="12" spans="3:15">
-      <c r="C12" s="319"/>
+      <c r="C12" s="356"/>
       <c r="D12" s="182" t="s">
         <v>975</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="319"/>
+      <c r="H12" s="356"/>
       <c r="I12" s="14" t="s">
         <v>941</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="M12" s="319"/>
+      <c r="M12" s="356"/>
       <c r="N12" s="14" t="s">
         <v>886</v>
       </c>
@@ -10827,14 +11421,14 @@
       </c>
     </row>
     <row r="13" spans="3:15">
-      <c r="C13" s="319"/>
+      <c r="C13" s="356"/>
       <c r="D13" s="14" t="s">
         <v>976</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>1224</v>
       </c>
-      <c r="H13" s="320" t="s">
+      <c r="H13" s="357" t="s">
         <v>1233</v>
       </c>
       <c r="I13" s="14" t="s">
@@ -10843,7 +11437,7 @@
       <c r="J13" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="M13" s="319"/>
+      <c r="M13" s="356"/>
       <c r="N13" s="14" t="s">
         <v>888</v>
       </c>
@@ -10852,14 +11446,14 @@
       </c>
     </row>
     <row r="14" spans="3:15">
-      <c r="C14" s="319"/>
+      <c r="C14" s="356"/>
       <c r="D14" s="14" t="s">
         <v>1000</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>1225</v>
       </c>
-      <c r="H14" s="321"/>
+      <c r="H14" s="358"/>
       <c r="I14" s="14" t="s">
         <v>945</v>
       </c>
@@ -10877,15 +11471,15 @@
       <c r="D24" s="182"/>
     </row>
     <row r="25" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C25" s="297" t="s">
+      <c r="C25" s="334" t="s">
         <v>1481</v>
       </c>
-      <c r="D25" s="318"/>
-      <c r="E25" s="318"/>
-      <c r="F25" s="318"/>
-      <c r="G25" s="318"/>
-      <c r="H25" s="318"/>
-      <c r="I25" s="298"/>
+      <c r="D25" s="355"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
+      <c r="G25" s="355"/>
+      <c r="H25" s="355"/>
+      <c r="I25" s="335"/>
       <c r="K25" s="244" t="s">
         <v>1484</v>
       </c>
@@ -10945,7 +11539,7 @@
       <c r="P26" s="15"/>
     </row>
     <row r="27" spans="3:16">
-      <c r="C27" s="312"/>
+      <c r="C27" s="349"/>
       <c r="D27" s="14" t="s">
         <v>1256</v>
       </c>
@@ -10982,7 +11576,7 @@
       <c r="P27" s="15"/>
     </row>
     <row r="28" spans="3:16">
-      <c r="C28" s="313"/>
+      <c r="C28" s="350"/>
       <c r="D28" s="14" t="s">
         <v>1358</v>
       </c>
@@ -11019,21 +11613,21 @@
       <c r="P28" s="15"/>
     </row>
     <row r="29" spans="3:16">
-      <c r="C29" s="313"/>
+      <c r="C29" s="350"/>
       <c r="D29" s="14" t="s">
         <v>1359</v>
       </c>
       <c r="E29" s="242" t="s">
         <v>1163</v>
       </c>
-      <c r="F29" s="315"/>
+      <c r="F29" s="352"/>
       <c r="G29" s="14" t="s">
         <v>1363</v>
       </c>
       <c r="H29" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="I29" s="309"/>
+      <c r="I29" s="346"/>
       <c r="K29" s="210" t="s">
         <v>1387</v>
       </c>
@@ -11052,19 +11646,19 @@
       <c r="P29" s="15"/>
     </row>
     <row r="30" spans="3:16">
-      <c r="C30" s="313"/>
+      <c r="C30" s="350"/>
       <c r="D30" s="14" t="s">
         <v>1360</v>
       </c>
-      <c r="E30" s="315"/>
-      <c r="F30" s="316"/>
+      <c r="E30" s="352"/>
+      <c r="F30" s="353"/>
       <c r="G30" s="14" t="s">
         <v>1364</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>1346</v>
       </c>
-      <c r="I30" s="310"/>
+      <c r="I30" s="347"/>
       <c r="K30" s="210" t="s">
         <v>1388</v>
       </c>
@@ -11085,15 +11679,15 @@
       </c>
     </row>
     <row r="31" spans="3:16">
-      <c r="C31" s="313"/>
-      <c r="D31" s="315"/>
-      <c r="E31" s="316"/>
-      <c r="F31" s="316"/>
+      <c r="C31" s="350"/>
+      <c r="D31" s="352"/>
+      <c r="E31" s="353"/>
+      <c r="F31" s="353"/>
       <c r="G31" s="14" t="s">
         <v>1365</v>
       </c>
-      <c r="H31" s="315"/>
-      <c r="I31" s="310"/>
+      <c r="H31" s="352"/>
+      <c r="I31" s="347"/>
       <c r="K31" s="210" t="s">
         <v>1251</v>
       </c>
@@ -11112,15 +11706,15 @@
       <c r="P31" s="15"/>
     </row>
     <row r="32" spans="3:16">
-      <c r="C32" s="313"/>
-      <c r="D32" s="316"/>
-      <c r="E32" s="316"/>
-      <c r="F32" s="316"/>
+      <c r="C32" s="350"/>
+      <c r="D32" s="353"/>
+      <c r="E32" s="353"/>
+      <c r="F32" s="353"/>
       <c r="G32" s="14" t="s">
         <v>1366</v>
       </c>
-      <c r="H32" s="316"/>
-      <c r="I32" s="310"/>
+      <c r="H32" s="353"/>
+      <c r="I32" s="347"/>
       <c r="K32" s="210" t="s">
         <v>1252</v>
       </c>
@@ -11139,15 +11733,15 @@
       <c r="P32" s="15"/>
     </row>
     <row r="33" spans="3:16">
-      <c r="C33" s="313"/>
-      <c r="D33" s="316"/>
-      <c r="E33" s="316"/>
-      <c r="F33" s="316"/>
+      <c r="C33" s="350"/>
+      <c r="D33" s="353"/>
+      <c r="E33" s="353"/>
+      <c r="F33" s="353"/>
       <c r="G33" s="14" t="s">
         <v>1367</v>
       </c>
-      <c r="H33" s="316"/>
-      <c r="I33" s="310"/>
+      <c r="H33" s="353"/>
+      <c r="I33" s="347"/>
       <c r="K33" s="247" t="s">
         <v>1347</v>
       </c>
@@ -11166,15 +11760,15 @@
       <c r="P33" s="15"/>
     </row>
     <row r="34" spans="3:16">
-      <c r="C34" s="313"/>
-      <c r="D34" s="316"/>
-      <c r="E34" s="316"/>
-      <c r="F34" s="316"/>
+      <c r="C34" s="350"/>
+      <c r="D34" s="353"/>
+      <c r="E34" s="353"/>
+      <c r="F34" s="353"/>
       <c r="G34" s="14" t="s">
         <v>1368</v>
       </c>
-      <c r="H34" s="316"/>
-      <c r="I34" s="310"/>
+      <c r="H34" s="353"/>
+      <c r="I34" s="347"/>
       <c r="K34" s="210" t="s">
         <v>1348</v>
       </c>
@@ -11195,15 +11789,15 @@
       </c>
     </row>
     <row r="35" spans="3:16">
-      <c r="C35" s="313"/>
-      <c r="D35" s="316"/>
-      <c r="E35" s="316"/>
-      <c r="F35" s="316"/>
+      <c r="C35" s="350"/>
+      <c r="D35" s="353"/>
+      <c r="E35" s="353"/>
+      <c r="F35" s="353"/>
       <c r="G35" s="14" t="s">
         <v>1369</v>
       </c>
-      <c r="H35" s="316"/>
-      <c r="I35" s="310"/>
+      <c r="H35" s="353"/>
+      <c r="I35" s="347"/>
       <c r="K35" s="247" t="s">
         <v>1389</v>
       </c>
@@ -11222,15 +11816,15 @@
       <c r="P35" s="15"/>
     </row>
     <row r="36" spans="3:16">
-      <c r="C36" s="313"/>
-      <c r="D36" s="316"/>
-      <c r="E36" s="316"/>
-      <c r="F36" s="316"/>
+      <c r="C36" s="350"/>
+      <c r="D36" s="353"/>
+      <c r="E36" s="353"/>
+      <c r="F36" s="353"/>
       <c r="G36" s="14" t="s">
         <v>1370</v>
       </c>
-      <c r="H36" s="316"/>
-      <c r="I36" s="310"/>
+      <c r="H36" s="353"/>
+      <c r="I36" s="347"/>
       <c r="K36" s="247" t="s">
         <v>1390</v>
       </c>
@@ -11249,15 +11843,15 @@
       <c r="P36" s="15"/>
     </row>
     <row r="37" spans="3:16">
-      <c r="C37" s="313"/>
-      <c r="D37" s="316"/>
-      <c r="E37" s="316"/>
-      <c r="F37" s="316"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="353"/>
+      <c r="E37" s="353"/>
+      <c r="F37" s="353"/>
       <c r="G37" s="14" t="s">
         <v>1371</v>
       </c>
-      <c r="H37" s="316"/>
-      <c r="I37" s="310"/>
+      <c r="H37" s="353"/>
+      <c r="I37" s="347"/>
       <c r="K37" s="247" t="s">
         <v>1391</v>
       </c>
@@ -11276,15 +11870,15 @@
       <c r="P37" s="15"/>
     </row>
     <row r="38" spans="3:16">
-      <c r="C38" s="313"/>
-      <c r="D38" s="316"/>
-      <c r="E38" s="316"/>
-      <c r="F38" s="316"/>
+      <c r="C38" s="350"/>
+      <c r="D38" s="353"/>
+      <c r="E38" s="353"/>
+      <c r="F38" s="353"/>
       <c r="G38" s="14" t="s">
         <v>1372</v>
       </c>
-      <c r="H38" s="316"/>
-      <c r="I38" s="310"/>
+      <c r="H38" s="353"/>
+      <c r="I38" s="347"/>
       <c r="K38" s="247" t="s">
         <v>1392</v>
       </c>
@@ -11303,15 +11897,15 @@
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="3:16">
-      <c r="C39" s="313"/>
-      <c r="D39" s="316"/>
-      <c r="E39" s="316"/>
-      <c r="F39" s="316"/>
+      <c r="C39" s="350"/>
+      <c r="D39" s="353"/>
+      <c r="E39" s="353"/>
+      <c r="F39" s="353"/>
       <c r="G39" s="14" t="s">
         <v>1373</v>
       </c>
-      <c r="H39" s="316"/>
-      <c r="I39" s="310"/>
+      <c r="H39" s="353"/>
+      <c r="I39" s="347"/>
       <c r="K39" s="247" t="s">
         <v>1393</v>
       </c>
@@ -11330,15 +11924,15 @@
       <c r="P39" s="15"/>
     </row>
     <row r="40" spans="3:16">
-      <c r="C40" s="313"/>
-      <c r="D40" s="316"/>
-      <c r="E40" s="316"/>
-      <c r="F40" s="316"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
       <c r="G40" s="14" t="s">
         <v>1374</v>
       </c>
-      <c r="H40" s="316"/>
-      <c r="I40" s="310"/>
+      <c r="H40" s="353"/>
+      <c r="I40" s="347"/>
       <c r="K40" s="247" t="s">
         <v>1394</v>
       </c>
@@ -11357,15 +11951,15 @@
       <c r="P40" s="15"/>
     </row>
     <row r="41" spans="3:16">
-      <c r="C41" s="313"/>
-      <c r="D41" s="316"/>
-      <c r="E41" s="316"/>
-      <c r="F41" s="316"/>
+      <c r="C41" s="350"/>
+      <c r="D41" s="353"/>
+      <c r="E41" s="353"/>
+      <c r="F41" s="353"/>
       <c r="G41" s="14" t="s">
         <v>1375</v>
       </c>
-      <c r="H41" s="316"/>
-      <c r="I41" s="310"/>
+      <c r="H41" s="353"/>
+      <c r="I41" s="347"/>
       <c r="K41" s="247" t="s">
         <v>1395</v>
       </c>
@@ -11386,15 +11980,15 @@
       </c>
     </row>
     <row r="42" spans="3:16">
-      <c r="C42" s="313"/>
-      <c r="D42" s="316"/>
-      <c r="E42" s="316"/>
-      <c r="F42" s="316"/>
+      <c r="C42" s="350"/>
+      <c r="D42" s="353"/>
+      <c r="E42" s="353"/>
+      <c r="F42" s="353"/>
       <c r="G42" s="14" t="s">
         <v>1376</v>
       </c>
-      <c r="H42" s="316"/>
-      <c r="I42" s="310"/>
+      <c r="H42" s="353"/>
+      <c r="I42" s="347"/>
       <c r="K42" s="247" t="s">
         <v>1396</v>
       </c>
@@ -11413,15 +12007,15 @@
       <c r="P42" s="15"/>
     </row>
     <row r="43" spans="3:16">
-      <c r="C43" s="313"/>
-      <c r="D43" s="316"/>
-      <c r="E43" s="316"/>
-      <c r="F43" s="316"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
       <c r="G43" s="14" t="s">
         <v>1377</v>
       </c>
-      <c r="H43" s="316"/>
-      <c r="I43" s="310"/>
+      <c r="H43" s="353"/>
+      <c r="I43" s="347"/>
       <c r="K43" s="247" t="s">
         <v>1397</v>
       </c>
@@ -11440,15 +12034,15 @@
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C44" s="314"/>
-      <c r="D44" s="317"/>
-      <c r="E44" s="317"/>
-      <c r="F44" s="317"/>
+      <c r="C44" s="351"/>
+      <c r="D44" s="354"/>
+      <c r="E44" s="354"/>
+      <c r="F44" s="354"/>
       <c r="G44" s="22" t="s">
         <v>1378</v>
       </c>
-      <c r="H44" s="317"/>
-      <c r="I44" s="311"/>
+      <c r="H44" s="354"/>
+      <c r="I44" s="348"/>
       <c r="K44" s="247" t="s">
         <v>1398</v>
       </c>
@@ -11777,21 +12371,21 @@
   <sheetData>
     <row r="2" spans="3:16" ht="15.75" thickBot="1"/>
     <row r="3" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C3" s="288" t="s">
+      <c r="C3" s="325" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="289"/>
-      <c r="E3" s="290"/>
-      <c r="I3" s="288" t="s">
+      <c r="D3" s="326"/>
+      <c r="E3" s="327"/>
+      <c r="I3" s="325" t="s">
         <v>746</v>
       </c>
-      <c r="J3" s="289"/>
-      <c r="K3" s="329"/>
-      <c r="N3" s="300" t="s">
+      <c r="J3" s="326"/>
+      <c r="K3" s="366"/>
+      <c r="N3" s="337" t="s">
         <v>455</v>
       </c>
-      <c r="O3" s="301"/>
-      <c r="P3" s="322"/>
+      <c r="O3" s="338"/>
+      <c r="P3" s="359"/>
     </row>
     <row r="4" spans="3:16" ht="15.75" thickBot="1">
       <c r="C4" s="192"/>
@@ -11817,7 +12411,7 @@
       </c>
     </row>
     <row r="5" spans="3:16">
-      <c r="C5" s="326" t="s">
+      <c r="C5" s="363" t="s">
         <v>1265</v>
       </c>
       <c r="D5" s="185" t="s">
@@ -11826,7 +12420,7 @@
       <c r="E5" s="185" t="s">
         <v>327</v>
       </c>
-      <c r="I5" s="269" t="s">
+      <c r="I5" s="306" t="s">
         <v>1265</v>
       </c>
       <c r="J5" s="194" t="s">
@@ -11835,7 +12429,7 @@
       <c r="K5" s="12" t="s">
         <v>1282</v>
       </c>
-      <c r="N5" s="326" t="s">
+      <c r="N5" s="363" t="s">
         <v>1265</v>
       </c>
       <c r="O5" s="187" t="s">
@@ -11846,21 +12440,21 @@
       </c>
     </row>
     <row r="6" spans="3:16">
-      <c r="C6" s="327"/>
+      <c r="C6" s="364"/>
       <c r="D6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>239</v>
       </c>
-      <c r="I6" s="270"/>
+      <c r="I6" s="307"/>
       <c r="J6" s="13" t="s">
         <v>1277</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>1283</v>
       </c>
-      <c r="N6" s="327"/>
+      <c r="N6" s="364"/>
       <c r="O6" s="81" t="s">
         <v>503</v>
       </c>
@@ -11869,21 +12463,21 @@
       </c>
     </row>
     <row r="7" spans="3:16">
-      <c r="C7" s="327"/>
+      <c r="C7" s="364"/>
       <c r="D7" s="183" t="s">
         <v>247</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>248</v>
       </c>
-      <c r="I7" s="270"/>
+      <c r="I7" s="307"/>
       <c r="J7" s="13" t="s">
         <v>1278</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="N7" s="327"/>
+      <c r="N7" s="364"/>
       <c r="O7" s="81" t="s">
         <v>502</v>
       </c>
@@ -11892,21 +12486,21 @@
       </c>
     </row>
     <row r="8" spans="3:16">
-      <c r="C8" s="327"/>
+      <c r="C8" s="364"/>
       <c r="D8" s="183" t="s">
         <v>276</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>277</v>
       </c>
-      <c r="I8" s="270"/>
+      <c r="I8" s="307"/>
       <c r="J8" s="13" t="s">
         <v>1279</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="N8" s="327"/>
+      <c r="N8" s="364"/>
       <c r="O8" s="81" t="s">
         <v>1287</v>
       </c>
@@ -11915,21 +12509,21 @@
       </c>
     </row>
     <row r="9" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C9" s="328"/>
+      <c r="C9" s="365"/>
       <c r="D9" s="184" t="s">
         <v>280</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="I9" s="270"/>
+      <c r="I9" s="307"/>
       <c r="J9" s="13" t="s">
         <v>1280</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="N9" s="328"/>
+      <c r="N9" s="365"/>
       <c r="O9" s="188" t="s">
         <v>1288</v>
       </c>
@@ -11938,7 +12532,7 @@
       </c>
     </row>
     <row r="10" spans="3:16">
-      <c r="C10" s="326" t="s">
+      <c r="C10" s="363" t="s">
         <v>1266</v>
       </c>
       <c r="D10" s="190" t="s">
@@ -11947,14 +12541,14 @@
       <c r="E10" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="I10" s="270"/>
+      <c r="I10" s="307"/>
       <c r="J10" s="13" t="s">
         <v>1281</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>1285</v>
       </c>
-      <c r="N10" s="323" t="s">
+      <c r="N10" s="360" t="s">
         <v>1266</v>
       </c>
       <c r="O10" s="187" t="s">
@@ -11965,21 +12559,21 @@
       </c>
     </row>
     <row r="11" spans="3:16">
-      <c r="C11" s="327"/>
+      <c r="C11" s="364"/>
       <c r="D11" s="81" t="s">
         <v>307</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>1110</v>
       </c>
-      <c r="I11" s="270"/>
+      <c r="I11" s="307"/>
       <c r="J11" s="13" t="s">
         <v>111</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="N11" s="324"/>
+      <c r="N11" s="361"/>
       <c r="O11" s="81" t="s">
         <v>1290</v>
       </c>
@@ -11988,21 +12582,21 @@
       </c>
     </row>
     <row r="12" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C12" s="327"/>
+      <c r="C12" s="364"/>
       <c r="D12" s="81" t="s">
         <v>314</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="I12" s="271"/>
+      <c r="I12" s="308"/>
       <c r="J12" s="21" t="s">
         <v>114</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="N12" s="324"/>
+      <c r="N12" s="361"/>
       <c r="O12" s="81" t="s">
         <v>1291</v>
       </c>
@@ -12011,14 +12605,14 @@
       </c>
     </row>
     <row r="13" spans="3:16">
-      <c r="C13" s="327"/>
+      <c r="C13" s="364"/>
       <c r="D13" s="81" t="s">
         <v>336</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>1267</v>
       </c>
-      <c r="I13" s="324" t="s">
+      <c r="I13" s="361" t="s">
         <v>1266</v>
       </c>
       <c r="J13" s="197" t="s">
@@ -12027,7 +12621,7 @@
       <c r="K13" s="168" t="s">
         <v>762</v>
       </c>
-      <c r="N13" s="324"/>
+      <c r="N13" s="361"/>
       <c r="O13" s="81" t="s">
         <v>1292</v>
       </c>
@@ -12036,21 +12630,21 @@
       </c>
     </row>
     <row r="14" spans="3:16">
-      <c r="C14" s="327"/>
+      <c r="C14" s="364"/>
       <c r="D14" s="81" t="s">
         <v>339</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>1268</v>
       </c>
-      <c r="I14" s="324"/>
+      <c r="I14" s="361"/>
       <c r="J14" s="24" t="s">
         <v>800</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>801</v>
       </c>
-      <c r="N14" s="324"/>
+      <c r="N14" s="361"/>
       <c r="O14" s="81" t="s">
         <v>1293</v>
       </c>
@@ -12059,21 +12653,21 @@
       </c>
     </row>
     <row r="15" spans="3:16">
-      <c r="C15" s="327"/>
+      <c r="C15" s="364"/>
       <c r="D15" s="81" t="s">
         <v>340</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>1269</v>
       </c>
-      <c r="I15" s="324"/>
+      <c r="I15" s="361"/>
       <c r="J15" s="24" t="s">
         <v>813</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="N15" s="324"/>
+      <c r="N15" s="361"/>
       <c r="O15" s="81" t="s">
         <v>1294</v>
       </c>
@@ -12082,21 +12676,21 @@
       </c>
     </row>
     <row r="16" spans="3:16">
-      <c r="C16" s="327"/>
+      <c r="C16" s="364"/>
       <c r="D16" s="81" t="s">
         <v>341</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="I16" s="324"/>
+      <c r="I16" s="361"/>
       <c r="J16" s="24" t="s">
         <v>807</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>1274</v>
       </c>
-      <c r="N16" s="324"/>
+      <c r="N16" s="361"/>
       <c r="O16" s="81" t="s">
         <v>1295</v>
       </c>
@@ -12105,21 +12699,21 @@
       </c>
     </row>
     <row r="17" spans="3:16">
-      <c r="C17" s="327"/>
+      <c r="C17" s="364"/>
       <c r="D17" s="81" t="s">
         <v>350</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>983</v>
       </c>
-      <c r="I17" s="324"/>
+      <c r="I17" s="361"/>
       <c r="J17" s="24" t="s">
         <v>769</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="N17" s="324"/>
+      <c r="N17" s="361"/>
       <c r="O17" s="81" t="s">
         <v>1299</v>
       </c>
@@ -12128,21 +12722,21 @@
       </c>
     </row>
     <row r="18" spans="3:16">
-      <c r="C18" s="327"/>
+      <c r="C18" s="364"/>
       <c r="D18" s="81" t="s">
         <v>353</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>1270</v>
       </c>
-      <c r="I18" s="324"/>
+      <c r="I18" s="361"/>
       <c r="J18" s="24" t="s">
         <v>763</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="N18" s="324"/>
+      <c r="N18" s="361"/>
       <c r="O18" s="81" t="s">
         <v>1300</v>
       </c>
@@ -12151,21 +12745,21 @@
       </c>
     </row>
     <row r="19" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C19" s="327"/>
+      <c r="C19" s="364"/>
       <c r="D19" s="81" t="s">
         <v>354</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="I19" s="324"/>
+      <c r="I19" s="361"/>
       <c r="J19" s="24" t="s">
         <v>66</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>779</v>
       </c>
-      <c r="N19" s="325"/>
+      <c r="N19" s="362"/>
       <c r="O19" s="188" t="s">
         <v>492</v>
       </c>
@@ -12174,14 +12768,14 @@
       </c>
     </row>
     <row r="20" spans="3:16">
-      <c r="C20" s="327"/>
+      <c r="C20" s="364"/>
       <c r="D20" s="81" t="s">
         <v>356</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>1273</v>
       </c>
-      <c r="I20" s="324"/>
+      <c r="I20" s="361"/>
       <c r="J20" s="24" t="s">
         <v>784</v>
       </c>
@@ -12190,14 +12784,14 @@
       </c>
     </row>
     <row r="21" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C21" s="327"/>
+      <c r="C21" s="364"/>
       <c r="D21" s="81" t="s">
         <v>359</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>1272</v>
       </c>
-      <c r="I21" s="325"/>
+      <c r="I21" s="362"/>
       <c r="J21" s="27" t="s">
         <v>786</v>
       </c>
@@ -12206,7 +12800,7 @@
       </c>
     </row>
     <row r="22" spans="3:16">
-      <c r="C22" s="327"/>
+      <c r="C22" s="364"/>
       <c r="D22" s="81" t="s">
         <v>370</v>
       </c>
@@ -12215,7 +12809,7 @@
       </c>
     </row>
     <row r="23" spans="3:16">
-      <c r="C23" s="327"/>
+      <c r="C23" s="364"/>
       <c r="D23" s="81" t="s">
         <v>372</v>
       </c>
@@ -12224,7 +12818,7 @@
       </c>
     </row>
     <row r="24" spans="3:16">
-      <c r="C24" s="327"/>
+      <c r="C24" s="364"/>
       <c r="D24" s="81" t="s">
         <v>382</v>
       </c>
@@ -12233,7 +12827,7 @@
       </c>
     </row>
     <row r="25" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C25" s="328"/>
+      <c r="C25" s="365"/>
       <c r="D25" s="188" t="s">
         <v>386</v>
       </c>
@@ -12248,16 +12842,16 @@
     </row>
     <row r="28" spans="3:16" ht="15.75" thickBot="1"/>
     <row r="29" spans="3:16" ht="15.75" thickBot="1">
-      <c r="C29" s="288" t="s">
+      <c r="C29" s="325" t="s">
         <v>1307</v>
       </c>
-      <c r="D29" s="289"/>
-      <c r="E29" s="290"/>
-      <c r="I29" s="288" t="s">
+      <c r="D29" s="326"/>
+      <c r="E29" s="327"/>
+      <c r="I29" s="325" t="s">
         <v>1309</v>
       </c>
-      <c r="J29" s="289"/>
-      <c r="K29" s="290"/>
+      <c r="J29" s="326"/>
+      <c r="K29" s="327"/>
     </row>
     <row r="30" spans="3:16" ht="15.75" thickBot="1">
       <c r="C30" s="87"/>
@@ -12276,7 +12870,7 @@
       </c>
     </row>
     <row r="31" spans="3:16" ht="30">
-      <c r="C31" s="269" t="s">
+      <c r="C31" s="306" t="s">
         <v>1265</v>
       </c>
       <c r="D31" s="200" t="s">
@@ -12286,7 +12880,7 @@
         <v>327</v>
       </c>
       <c r="F31" s="193"/>
-      <c r="I31" s="326" t="s">
+      <c r="I31" s="363" t="s">
         <v>1265</v>
       </c>
       <c r="J31" s="209" t="s">
@@ -12297,7 +12891,7 @@
       </c>
     </row>
     <row r="32" spans="3:16" ht="45">
-      <c r="C32" s="270"/>
+      <c r="C32" s="307"/>
       <c r="D32" s="199" t="s">
         <v>698</v>
       </c>
@@ -12305,7 +12899,7 @@
         <v>248</v>
       </c>
       <c r="F32" s="193"/>
-      <c r="I32" s="327"/>
+      <c r="I32" s="364"/>
       <c r="J32" s="203" t="s">
         <v>87</v>
       </c>
@@ -12314,7 +12908,7 @@
       </c>
     </row>
     <row r="33" spans="3:11" ht="45">
-      <c r="C33" s="270"/>
+      <c r="C33" s="307"/>
       <c r="D33" s="199" t="s">
         <v>699</v>
       </c>
@@ -12322,7 +12916,7 @@
         <v>239</v>
       </c>
       <c r="F33" s="193"/>
-      <c r="I33" s="327"/>
+      <c r="I33" s="364"/>
       <c r="J33" s="203" t="s">
         <v>89</v>
       </c>
@@ -12331,7 +12925,7 @@
       </c>
     </row>
     <row r="34" spans="3:11" ht="45">
-      <c r="C34" s="270"/>
+      <c r="C34" s="307"/>
       <c r="D34" s="199" t="s">
         <v>714</v>
       </c>
@@ -12339,7 +12933,7 @@
         <v>283</v>
       </c>
       <c r="F34" s="193"/>
-      <c r="I34" s="327"/>
+      <c r="I34" s="364"/>
       <c r="J34" s="203" t="s">
         <v>73</v>
       </c>
@@ -12348,7 +12942,7 @@
       </c>
     </row>
     <row r="35" spans="3:11" ht="45">
-      <c r="C35" s="270"/>
+      <c r="C35" s="307"/>
       <c r="D35" s="199" t="s">
         <v>715</v>
       </c>
@@ -12356,7 +12950,7 @@
         <v>271</v>
       </c>
       <c r="F35" s="193"/>
-      <c r="I35" s="327"/>
+      <c r="I35" s="364"/>
       <c r="J35" s="203" t="s">
         <v>105</v>
       </c>
@@ -12365,7 +12959,7 @@
       </c>
     </row>
     <row r="36" spans="3:11" ht="45">
-      <c r="C36" s="270"/>
+      <c r="C36" s="307"/>
       <c r="D36" s="199" t="s">
         <v>659</v>
       </c>
@@ -12373,7 +12967,7 @@
         <v>250</v>
       </c>
       <c r="F36" s="193"/>
-      <c r="I36" s="327"/>
+      <c r="I36" s="364"/>
       <c r="J36" s="203" t="s">
         <v>41</v>
       </c>
@@ -12382,7 +12976,7 @@
       </c>
     </row>
     <row r="37" spans="3:11" ht="45">
-      <c r="C37" s="270"/>
+      <c r="C37" s="307"/>
       <c r="D37" s="199" t="s">
         <v>716</v>
       </c>
@@ -12390,7 +12984,7 @@
         <v>717</v>
       </c>
       <c r="F37" s="193"/>
-      <c r="I37" s="327"/>
+      <c r="I37" s="364"/>
       <c r="J37" s="203" t="s">
         <v>108</v>
       </c>
@@ -12399,7 +12993,7 @@
       </c>
     </row>
     <row r="38" spans="3:11" ht="45">
-      <c r="C38" s="270"/>
+      <c r="C38" s="307"/>
       <c r="D38" s="199" t="s">
         <v>718</v>
       </c>
@@ -12407,7 +13001,7 @@
         <v>719</v>
       </c>
       <c r="F38" s="193"/>
-      <c r="I38" s="327"/>
+      <c r="I38" s="364"/>
       <c r="J38" s="203" t="s">
         <v>51</v>
       </c>
@@ -12416,7 +13010,7 @@
       </c>
     </row>
     <row r="39" spans="3:11" ht="30">
-      <c r="C39" s="270"/>
+      <c r="C39" s="307"/>
       <c r="D39" s="199" t="s">
         <v>720</v>
       </c>
@@ -12424,7 +13018,7 @@
         <v>338</v>
       </c>
       <c r="F39" s="193"/>
-      <c r="I39" s="327"/>
+      <c r="I39" s="364"/>
       <c r="J39" s="203" t="s">
         <v>56</v>
       </c>
@@ -12433,7 +13027,7 @@
       </c>
     </row>
     <row r="40" spans="3:11" ht="30">
-      <c r="C40" s="270"/>
+      <c r="C40" s="307"/>
       <c r="D40" s="199" t="s">
         <v>721</v>
       </c>
@@ -12441,7 +13035,7 @@
         <v>292</v>
       </c>
       <c r="F40" s="193"/>
-      <c r="I40" s="327"/>
+      <c r="I40" s="364"/>
       <c r="J40" s="203" t="s">
         <v>125</v>
       </c>
@@ -12450,7 +13044,7 @@
       </c>
     </row>
     <row r="41" spans="3:11" ht="45">
-      <c r="C41" s="270"/>
+      <c r="C41" s="307"/>
       <c r="D41" s="199" t="s">
         <v>722</v>
       </c>
@@ -12458,7 +13052,7 @@
         <v>723</v>
       </c>
       <c r="F41" s="193"/>
-      <c r="I41" s="327"/>
+      <c r="I41" s="364"/>
       <c r="J41" s="203" t="s">
         <v>63</v>
       </c>
@@ -12467,7 +13061,7 @@
       </c>
     </row>
     <row r="42" spans="3:11" ht="45.75" thickBot="1">
-      <c r="C42" s="271"/>
+      <c r="C42" s="308"/>
       <c r="D42" s="201" t="s">
         <v>674</v>
       </c>
@@ -12475,7 +13069,7 @@
         <v>513</v>
       </c>
       <c r="F42" s="193"/>
-      <c r="I42" s="327"/>
+      <c r="I42" s="364"/>
       <c r="J42" s="203" t="s">
         <v>13</v>
       </c>
@@ -12484,7 +13078,7 @@
       </c>
     </row>
     <row r="43" spans="3:11" ht="30">
-      <c r="C43" s="326" t="s">
+      <c r="C43" s="363" t="s">
         <v>1266</v>
       </c>
       <c r="D43" s="187" t="s">
@@ -12493,7 +13087,7 @@
       <c r="E43" s="168" t="s">
         <v>644</v>
       </c>
-      <c r="I43" s="327"/>
+      <c r="I43" s="364"/>
       <c r="J43" s="203" t="s">
         <v>111</v>
       </c>
@@ -12502,14 +13096,14 @@
       </c>
     </row>
     <row r="44" spans="3:11" ht="30.75" thickBot="1">
-      <c r="C44" s="327"/>
+      <c r="C44" s="364"/>
       <c r="D44" s="81" t="s">
         <v>679</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>680</v>
       </c>
-      <c r="I44" s="328"/>
+      <c r="I44" s="365"/>
       <c r="J44" s="206" t="s">
         <v>114</v>
       </c>
@@ -12518,14 +13112,14 @@
       </c>
     </row>
     <row r="45" spans="3:11" ht="30">
-      <c r="C45" s="327"/>
+      <c r="C45" s="364"/>
       <c r="D45" s="81" t="s">
         <v>645</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="I45" s="327" t="s">
+      <c r="I45" s="364" t="s">
         <v>1266</v>
       </c>
       <c r="J45" s="207" t="s">
@@ -12536,14 +13130,14 @@
       </c>
     </row>
     <row r="46" spans="3:11" ht="30">
-      <c r="C46" s="327"/>
+      <c r="C46" s="364"/>
       <c r="D46" s="81" t="s">
         <v>653</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="I46" s="327"/>
+      <c r="I46" s="364"/>
       <c r="J46" s="203" t="s">
         <v>23</v>
       </c>
@@ -12552,14 +13146,14 @@
       </c>
     </row>
     <row r="47" spans="3:11" ht="30">
-      <c r="C47" s="327"/>
+      <c r="C47" s="364"/>
       <c r="D47" s="81" t="s">
         <v>656</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="I47" s="327"/>
+      <c r="I47" s="364"/>
       <c r="J47" s="203" t="s">
         <v>38</v>
       </c>
@@ -12568,14 +13162,14 @@
       </c>
     </row>
     <row r="48" spans="3:11" ht="30">
-      <c r="C48" s="327"/>
+      <c r="C48" s="364"/>
       <c r="D48" s="81" t="s">
         <v>659</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>577</v>
       </c>
-      <c r="I48" s="327"/>
+      <c r="I48" s="364"/>
       <c r="J48" s="203" t="s">
         <v>48</v>
       </c>
@@ -12584,14 +13178,14 @@
       </c>
     </row>
     <row r="49" spans="3:11" ht="30">
-      <c r="C49" s="327"/>
+      <c r="C49" s="364"/>
       <c r="D49" s="81" t="s">
         <v>664</v>
       </c>
       <c r="E49" s="15" t="s">
         <v>610</v>
       </c>
-      <c r="I49" s="327"/>
+      <c r="I49" s="364"/>
       <c r="J49" s="203" t="s">
         <v>41</v>
       </c>
@@ -12600,14 +13194,14 @@
       </c>
     </row>
     <row r="50" spans="3:11" ht="30">
-      <c r="C50" s="327"/>
+      <c r="C50" s="364"/>
       <c r="D50" s="81" t="s">
         <v>665</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="I50" s="327"/>
+      <c r="I50" s="364"/>
       <c r="J50" s="203" t="s">
         <v>32</v>
       </c>
@@ -12616,14 +13210,14 @@
       </c>
     </row>
     <row r="51" spans="3:11" ht="45">
-      <c r="C51" s="327"/>
+      <c r="C51" s="364"/>
       <c r="D51" s="81" t="s">
         <v>666</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="I51" s="327"/>
+      <c r="I51" s="364"/>
       <c r="J51" s="203" t="s">
         <v>51</v>
       </c>
@@ -12632,14 +13226,14 @@
       </c>
     </row>
     <row r="52" spans="3:11" ht="30">
-      <c r="C52" s="327"/>
+      <c r="C52" s="364"/>
       <c r="D52" s="81" t="s">
         <v>667</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="I52" s="327"/>
+      <c r="I52" s="364"/>
       <c r="J52" s="203" t="s">
         <v>73</v>
       </c>
@@ -12648,14 +13242,14 @@
       </c>
     </row>
     <row r="53" spans="3:11" ht="30">
-      <c r="C53" s="327"/>
+      <c r="C53" s="364"/>
       <c r="D53" s="81" t="s">
         <v>668</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>1308</v>
       </c>
-      <c r="I53" s="327"/>
+      <c r="I53" s="364"/>
       <c r="J53" s="203" t="s">
         <v>56</v>
       </c>
@@ -12664,14 +13258,14 @@
       </c>
     </row>
     <row r="54" spans="3:11" ht="30">
-      <c r="C54" s="327"/>
+      <c r="C54" s="364"/>
       <c r="D54" s="81" t="s">
         <v>672</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="I54" s="327"/>
+      <c r="I54" s="364"/>
       <c r="J54" s="203" t="s">
         <v>63</v>
       </c>
@@ -12680,14 +13274,14 @@
       </c>
     </row>
     <row r="55" spans="3:11" ht="15.75" thickBot="1">
-      <c r="C55" s="328"/>
+      <c r="C55" s="365"/>
       <c r="D55" s="188" t="s">
         <v>674</v>
       </c>
       <c r="E55" s="23" t="s">
         <v>513</v>
       </c>
-      <c r="I55" s="327"/>
+      <c r="I55" s="364"/>
       <c r="J55" s="203" t="s">
         <v>66</v>
       </c>
@@ -12696,7 +13290,7 @@
       </c>
     </row>
     <row r="56" spans="3:11" ht="45.75" thickBot="1">
-      <c r="I56" s="328"/>
+      <c r="I56" s="365"/>
       <c r="J56" s="206" t="s">
         <v>13</v>
       </c>
@@ -12709,16 +13303,16 @@
     </row>
     <row r="60" spans="3:11" ht="15.75" thickBot="1"/>
     <row r="61" spans="3:11" ht="15.75" thickBot="1">
-      <c r="C61" s="300" t="s">
+      <c r="C61" s="337" t="s">
         <v>1449</v>
       </c>
-      <c r="D61" s="301"/>
-      <c r="E61" s="301"/>
-      <c r="F61" s="301"/>
-      <c r="G61" s="301"/>
-      <c r="H61" s="301"/>
-      <c r="I61" s="301"/>
-      <c r="J61" s="302"/>
+      <c r="D61" s="338"/>
+      <c r="E61" s="338"/>
+      <c r="F61" s="338"/>
+      <c r="G61" s="338"/>
+      <c r="H61" s="338"/>
+      <c r="I61" s="338"/>
+      <c r="J61" s="339"/>
       <c r="K61" s="7"/>
     </row>
     <row r="62" spans="3:11">
@@ -12748,7 +13342,7 @@
       </c>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="312"/>
+      <c r="C63" s="349"/>
       <c r="D63" s="25" t="s">
         <v>1256</v>
       </c>
@@ -12772,7 +13366,7 @@
       </c>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="313"/>
+      <c r="C64" s="350"/>
       <c r="D64" s="25" t="s">
         <v>1358</v>
       </c>
@@ -12796,88 +13390,88 @@
       </c>
     </row>
     <row r="65" spans="3:10">
-      <c r="C65" s="313"/>
+      <c r="C65" s="350"/>
       <c r="D65" s="25" t="s">
         <v>1359</v>
       </c>
       <c r="E65" s="25" t="s">
         <v>1163</v>
       </c>
-      <c r="F65" s="315"/>
+      <c r="F65" s="352"/>
       <c r="G65" s="14" t="s">
         <v>1409</v>
       </c>
       <c r="H65" s="14" t="s">
         <v>1346</v>
       </c>
-      <c r="I65" s="315"/>
-      <c r="J65" s="330"/>
+      <c r="I65" s="352"/>
+      <c r="J65" s="367"/>
     </row>
     <row r="66" spans="3:10">
-      <c r="C66" s="313"/>
+      <c r="C66" s="350"/>
       <c r="D66" s="25" t="s">
         <v>1360</v>
       </c>
-      <c r="E66" s="315"/>
-      <c r="F66" s="316"/>
+      <c r="E66" s="352"/>
+      <c r="F66" s="353"/>
       <c r="G66" s="14" t="s">
         <v>1410</v>
       </c>
       <c r="H66" s="14" t="s">
         <v>1339</v>
       </c>
-      <c r="I66" s="316"/>
-      <c r="J66" s="331"/>
+      <c r="I66" s="353"/>
+      <c r="J66" s="368"/>
     </row>
     <row r="67" spans="3:10">
-      <c r="C67" s="313"/>
-      <c r="D67" s="315"/>
-      <c r="E67" s="316"/>
-      <c r="F67" s="316"/>
+      <c r="C67" s="350"/>
+      <c r="D67" s="352"/>
+      <c r="E67" s="353"/>
+      <c r="F67" s="353"/>
       <c r="G67" s="14" t="s">
         <v>1343</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="I67" s="316"/>
-      <c r="J67" s="331"/>
+      <c r="I67" s="353"/>
+      <c r="J67" s="368"/>
     </row>
     <row r="68" spans="3:10">
-      <c r="C68" s="313"/>
-      <c r="D68" s="316"/>
-      <c r="E68" s="316"/>
-      <c r="F68" s="316"/>
+      <c r="C68" s="350"/>
+      <c r="D68" s="353"/>
+      <c r="E68" s="353"/>
+      <c r="F68" s="353"/>
       <c r="G68" s="14" t="s">
         <v>1345</v>
       </c>
-      <c r="H68" s="315"/>
-      <c r="I68" s="316"/>
-      <c r="J68" s="331"/>
+      <c r="H68" s="352"/>
+      <c r="I68" s="353"/>
+      <c r="J68" s="368"/>
     </row>
     <row r="69" spans="3:10">
-      <c r="C69" s="313"/>
-      <c r="D69" s="316"/>
-      <c r="E69" s="316"/>
-      <c r="F69" s="316"/>
+      <c r="C69" s="350"/>
+      <c r="D69" s="353"/>
+      <c r="E69" s="353"/>
+      <c r="F69" s="353"/>
       <c r="G69" s="14" t="s">
         <v>1411</v>
       </c>
-      <c r="H69" s="316"/>
-      <c r="I69" s="316"/>
-      <c r="J69" s="331"/>
+      <c r="H69" s="353"/>
+      <c r="I69" s="353"/>
+      <c r="J69" s="368"/>
     </row>
     <row r="70" spans="3:10" ht="15.75" thickBot="1">
-      <c r="C70" s="314"/>
-      <c r="D70" s="317"/>
-      <c r="E70" s="317"/>
-      <c r="F70" s="317"/>
+      <c r="C70" s="351"/>
+      <c r="D70" s="354"/>
+      <c r="E70" s="354"/>
+      <c r="F70" s="354"/>
       <c r="G70" s="22" t="s">
         <v>1344</v>
       </c>
-      <c r="H70" s="317"/>
-      <c r="I70" s="317"/>
-      <c r="J70" s="332"/>
+      <c r="H70" s="354"/>
+      <c r="I70" s="354"/>
+      <c r="J70" s="369"/>
     </row>
     <row r="71" spans="3:10">
       <c r="E71" s="189"/>
@@ -14153,6 +14747,827 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B63580-C196-4136-BD8B-AD44553E2078}">
+  <dimension ref="D3:U49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:21" ht="15.75" thickBot="1"/>
+    <row r="4" spans="4:21" ht="18.75">
+      <c r="D4" s="256" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E4" s="257" t="s">
+        <v>455</v>
+      </c>
+      <c r="F4" s="257" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="257" t="s">
+        <v>1545</v>
+      </c>
+      <c r="H4" s="258" t="s">
+        <v>1556</v>
+      </c>
+      <c r="L4" s="222" t="s">
+        <v>1560</v>
+      </c>
+      <c r="M4" s="224" t="s">
+        <v>1561</v>
+      </c>
+      <c r="P4" s="268" t="s">
+        <v>1574</v>
+      </c>
+      <c r="Q4" s="269" t="s">
+        <v>1575</v>
+      </c>
+      <c r="R4" s="269" t="s">
+        <v>1576</v>
+      </c>
+      <c r="S4" s="269" t="s">
+        <v>1577</v>
+      </c>
+      <c r="T4" s="269" t="s">
+        <v>1578</v>
+      </c>
+      <c r="U4" s="270" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="5" spans="4:21" ht="18.75">
+      <c r="D5" s="264" t="s">
+        <v>308</v>
+      </c>
+      <c r="E5" s="259" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F5" s="259" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G5" s="261" t="s">
+        <v>1546</v>
+      </c>
+      <c r="H5" s="260" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>1562</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>1568</v>
+      </c>
+      <c r="P5" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>1580</v>
+      </c>
+      <c r="R5" s="25" t="s">
+        <v>1581</v>
+      </c>
+      <c r="S5" s="25" t="s">
+        <v>1582</v>
+      </c>
+      <c r="T5" s="25" t="s">
+        <v>1583</v>
+      </c>
+      <c r="U5" s="26" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="6" spans="4:21" ht="18.75">
+      <c r="D6" s="264" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E6" s="261" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F6" s="261" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G6" s="261" t="s">
+        <v>1547</v>
+      </c>
+      <c r="H6" s="262" t="s">
+        <v>1559</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>1569</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>1585</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>1586</v>
+      </c>
+      <c r="S6" s="25" t="s">
+        <v>1587</v>
+      </c>
+      <c r="T6" s="25" t="s">
+        <v>1588</v>
+      </c>
+      <c r="U6" s="26" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="7" spans="4:21" ht="18.75">
+      <c r="D7" s="264" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E7" s="261" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F7" s="261" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G7" s="261" t="s">
+        <v>1555</v>
+      </c>
+      <c r="H7" s="260" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>1563</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>1570</v>
+      </c>
+      <c r="P7" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>1590</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>1591</v>
+      </c>
+      <c r="S7" s="25" t="s">
+        <v>1592</v>
+      </c>
+      <c r="T7" s="25" t="s">
+        <v>1593</v>
+      </c>
+      <c r="U7" s="26" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="8" spans="4:21" ht="18.75">
+      <c r="D8" s="264" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E8" s="261" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F8" s="261" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G8" s="261" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H8" s="262" t="s">
+        <v>1558</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>1571</v>
+      </c>
+      <c r="P8" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>1595</v>
+      </c>
+      <c r="R8" s="25" t="s">
+        <v>1596</v>
+      </c>
+      <c r="S8" s="25" t="s">
+        <v>1597</v>
+      </c>
+      <c r="T8" s="25" t="s">
+        <v>1598</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="9" spans="4:21" ht="19.5" thickBot="1">
+      <c r="D9" s="265" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" s="266" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F9" s="266" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G9" s="266" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H9" s="263" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>1307</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>1572</v>
+      </c>
+      <c r="P9" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>1600</v>
+      </c>
+      <c r="R9" s="25" t="s">
+        <v>1601</v>
+      </c>
+      <c r="S9" s="25" t="s">
+        <v>1602</v>
+      </c>
+      <c r="T9" s="25" t="s">
+        <v>1603</v>
+      </c>
+      <c r="U9" s="26" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="10" spans="4:21" ht="15.75" thickBot="1">
+      <c r="L10" s="13" t="s">
+        <v>1564</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>1572</v>
+      </c>
+      <c r="P10" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>1605</v>
+      </c>
+      <c r="R10" s="28" t="s">
+        <v>1606</v>
+      </c>
+      <c r="S10" s="28" t="s">
+        <v>1607</v>
+      </c>
+      <c r="T10" s="28" t="s">
+        <v>1608</v>
+      </c>
+      <c r="U10" s="29" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="11" spans="4:21">
+      <c r="L11" s="13" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="12" spans="4:21">
+      <c r="L12" s="210" t="s">
+        <v>1566</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="13" spans="4:21" ht="15.75" thickBot="1">
+      <c r="L13" s="21" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M13" s="267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="4:10" ht="15.75" thickBot="1"/>
+    <row r="19" spans="4:10" ht="18.75">
+      <c r="D19" s="272" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E19" s="273" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F19" s="274" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H19" s="272" t="s">
+        <v>1574</v>
+      </c>
+      <c r="I19" s="273" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J19" s="274" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="20" spans="4:10" ht="18.75">
+      <c r="D20" s="275" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" s="271" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F20" s="276">
+        <v>-35</v>
+      </c>
+      <c r="H20" s="275" t="s">
+        <v>308</v>
+      </c>
+      <c r="I20" s="271" t="s">
+        <v>1629</v>
+      </c>
+      <c r="J20" s="283" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="21" spans="4:10" ht="18.75">
+      <c r="D21" s="275" t="s">
+        <v>232</v>
+      </c>
+      <c r="E21" s="271" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F21" s="276">
+        <v>-20</v>
+      </c>
+      <c r="H21" s="275" t="s">
+        <v>308</v>
+      </c>
+      <c r="I21" s="271" t="s">
+        <v>1630</v>
+      </c>
+      <c r="J21" s="283" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="22" spans="4:10" ht="18.75">
+      <c r="D22" s="275" t="s">
+        <v>262</v>
+      </c>
+      <c r="E22" s="271" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F22" s="282">
+        <v>-35</v>
+      </c>
+      <c r="H22" s="275" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I22" s="271" t="s">
+        <v>1588</v>
+      </c>
+      <c r="J22" s="285" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="23" spans="4:10" ht="18.75">
+      <c r="D23" s="275" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" s="271" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F23" s="276">
+        <v>-15</v>
+      </c>
+      <c r="H23" s="275" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I23" s="271" t="s">
+        <v>1631</v>
+      </c>
+      <c r="J23" s="283" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="24" spans="4:10" ht="18.75">
+      <c r="D24" s="275" t="s">
+        <v>275</v>
+      </c>
+      <c r="E24" s="271" t="s">
+        <v>1620</v>
+      </c>
+      <c r="F24" s="276">
+        <v>-30</v>
+      </c>
+      <c r="H24" s="275" t="s">
+        <v>232</v>
+      </c>
+      <c r="I24" s="271" t="s">
+        <v>1632</v>
+      </c>
+      <c r="J24" s="283" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="25" spans="4:10" ht="18.75">
+      <c r="D25" s="279" t="s">
+        <v>275</v>
+      </c>
+      <c r="E25" s="278" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F25" s="276">
+        <v>-15</v>
+      </c>
+      <c r="H25" s="275" t="s">
+        <v>232</v>
+      </c>
+      <c r="I25" s="284" t="s">
+        <v>1633</v>
+      </c>
+      <c r="J25" s="283" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="26" spans="4:10" ht="18.75">
+      <c r="D26" s="279" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E26" s="271" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F26" s="276" t="s">
+        <v>1612</v>
+      </c>
+      <c r="H26" s="275" t="s">
+        <v>262</v>
+      </c>
+      <c r="I26" s="261" t="s">
+        <v>1639</v>
+      </c>
+      <c r="J26" s="285" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="27" spans="4:10" ht="18.75">
+      <c r="D27" s="370"/>
+      <c r="E27" s="271" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F27" s="280" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H27" s="279" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I27" s="271" t="s">
+        <v>1651</v>
+      </c>
+      <c r="J27" s="276" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="28" spans="4:10" ht="19.5" thickBot="1">
+      <c r="D28" s="371"/>
+      <c r="E28" s="277" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F28" s="281" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H28" s="370"/>
+      <c r="I28" s="271" t="s">
+        <v>1648</v>
+      </c>
+      <c r="J28" s="276" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="29" spans="4:10" ht="18.75">
+      <c r="H29" s="375"/>
+      <c r="I29" s="271" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J29" s="276" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="30" spans="4:10" ht="19.5" thickBot="1">
+      <c r="H30" s="371"/>
+      <c r="I30" s="286" t="s">
+        <v>1650</v>
+      </c>
+      <c r="J30" s="287" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="34" spans="4:10" ht="15.75" thickBot="1"/>
+    <row r="35" spans="4:10" ht="18.75">
+      <c r="D35" s="272" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E35" s="273" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F35" s="274" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H35" s="272" t="s">
+        <v>1574</v>
+      </c>
+      <c r="I35" s="273" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J35" s="274" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="36" spans="4:10" ht="18.75">
+      <c r="D36" s="275" t="s">
+        <v>232</v>
+      </c>
+      <c r="E36" s="271" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F36" s="276">
+        <v>-35</v>
+      </c>
+      <c r="H36" s="275" t="s">
+        <v>1640</v>
+      </c>
+      <c r="I36" s="271" t="s">
+        <v>1645</v>
+      </c>
+      <c r="J36" s="276">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="37" spans="4:10" ht="18.75">
+      <c r="D37" s="275" t="s">
+        <v>232</v>
+      </c>
+      <c r="E37" s="271" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F37" s="276">
+        <v>-20</v>
+      </c>
+      <c r="H37" s="275" t="s">
+        <v>1640</v>
+      </c>
+      <c r="I37" s="271" t="s">
+        <v>1652</v>
+      </c>
+      <c r="J37" s="276">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="38" spans="4:10" ht="18.75">
+      <c r="D38" s="275" t="s">
+        <v>232</v>
+      </c>
+      <c r="E38" s="271" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F38" s="288">
+        <v>-10</v>
+      </c>
+      <c r="H38" s="275" t="s">
+        <v>1640</v>
+      </c>
+      <c r="I38" s="271" t="s">
+        <v>1653</v>
+      </c>
+      <c r="J38" s="288">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="39" spans="4:10" ht="18.75">
+      <c r="D39" s="275" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E39" s="271" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F39" s="276">
+        <v>-35</v>
+      </c>
+      <c r="H39" s="275" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I39" s="271" t="s">
+        <v>1645</v>
+      </c>
+      <c r="J39" s="276">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="40" spans="4:10" ht="18.75">
+      <c r="D40" s="275" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E40" s="271" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F40" s="276">
+        <v>-20</v>
+      </c>
+      <c r="H40" s="275" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I40" s="271" t="s">
+        <v>1652</v>
+      </c>
+      <c r="J40" s="276">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="41" spans="4:10" ht="18.75">
+      <c r="D41" s="275" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E41" s="278" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F41" s="276">
+        <v>-10</v>
+      </c>
+      <c r="H41" s="275" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I41" s="271" t="s">
+        <v>1653</v>
+      </c>
+      <c r="J41" s="276">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="42" spans="4:10" ht="18.75">
+      <c r="D42" s="279" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E42" s="271" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F42" s="276">
+        <v>-30</v>
+      </c>
+      <c r="H42" s="279" t="s">
+        <v>1641</v>
+      </c>
+      <c r="I42" s="271" t="s">
+        <v>1646</v>
+      </c>
+      <c r="J42" s="276">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="43" spans="4:10" ht="18.75">
+      <c r="D43" s="279" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E43" s="271" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F43" s="280">
+        <v>-18</v>
+      </c>
+      <c r="H43" s="279" t="s">
+        <v>1641</v>
+      </c>
+      <c r="I43" s="259" t="s">
+        <v>1656</v>
+      </c>
+      <c r="J43" s="280">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="44" spans="4:10" ht="18.75">
+      <c r="D44" s="279" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E44" s="271" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F44" s="280">
+        <v>-8</v>
+      </c>
+      <c r="H44" s="279" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I44" s="271" t="s">
+        <v>1622</v>
+      </c>
+      <c r="J44" s="280" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="45" spans="4:10" ht="18.75">
+      <c r="D45" s="279" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E45" s="259" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F45" s="288">
+        <v>-20</v>
+      </c>
+      <c r="H45" s="373"/>
+      <c r="I45" s="271" t="s">
+        <v>1623</v>
+      </c>
+      <c r="J45" s="289" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="46" spans="4:10" ht="19.5" thickBot="1">
+      <c r="D46" s="279" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E46" s="259" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F46" s="288">
+        <v>-10</v>
+      </c>
+      <c r="H46" s="374"/>
+      <c r="I46" s="277" t="s">
+        <v>1624</v>
+      </c>
+      <c r="J46" s="287" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="47" spans="4:10" ht="18.75">
+      <c r="D47" s="279" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E47" s="271" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F47" s="289" t="s">
+        <v>1612</v>
+      </c>
+      <c r="H47" s="290"/>
+      <c r="I47" s="291"/>
+      <c r="J47" s="292"/>
+    </row>
+    <row r="48" spans="4:10" ht="18.75">
+      <c r="D48" s="370"/>
+      <c r="E48" s="271" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F48" s="289" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H48" s="372"/>
+      <c r="I48" s="291"/>
+      <c r="J48" s="292"/>
+    </row>
+    <row r="49" spans="4:10" ht="19.5" thickBot="1">
+      <c r="D49" s="371"/>
+      <c r="E49" s="277" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F49" s="287" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H49" s="372"/>
+      <c r="I49" s="291"/>
+      <c r="J49" s="292"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="H28:H30"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="E6:G6 J20:J26" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1A1574-31BD-4B45-9034-01DD5ECC30D1}">
   <sheetPr>
@@ -14175,11 +15590,11 @@
       <c r="C2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="262" t="s">
+      <c r="D2" s="299" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="263"/>
-      <c r="F2" s="264"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="301"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="3:10" ht="15.75" thickBot="1">
@@ -14319,11 +15734,11 @@
       <c r="F12" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="265" t="s">
+      <c r="H12" s="302" t="s">
         <v>224</v>
       </c>
-      <c r="I12" s="265"/>
-      <c r="J12" s="265"/>
+      <c r="I12" s="302"/>
+      <c r="J12" s="302"/>
     </row>
     <row r="13" spans="3:10">
       <c r="D13" s="36" t="s">
@@ -15998,11 +17413,11 @@
       <c r="C3" s="40" t="s">
         <v>894</v>
       </c>
-      <c r="D3" s="266" t="s">
+      <c r="D3" s="303" t="s">
         <v>948</v>
       </c>
-      <c r="E3" s="267"/>
-      <c r="F3" s="268"/>
+      <c r="E3" s="304"/>
+      <c r="F3" s="305"/>
       <c r="I3" s="7" t="s">
         <v>1017</v>
       </c>
@@ -16612,11 +18027,11 @@
       <c r="C2" s="41" t="s">
         <v>746</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="302" t="s">
         <v>850</v>
       </c>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
+      <c r="E2" s="302"/>
+      <c r="F2" s="302"/>
       <c r="I2" s="7" t="s">
         <v>848</v>
       </c>
@@ -17211,7 +18626,7 @@
       </c>
     </row>
     <row r="60" spans="4:6">
-      <c r="D60" s="269" t="s">
+      <c r="D60" s="306" t="s">
         <v>1265</v>
       </c>
       <c r="E60" s="194" t="s">
@@ -17222,7 +18637,7 @@
       </c>
     </row>
     <row r="61" spans="4:6">
-      <c r="D61" s="270"/>
+      <c r="D61" s="307"/>
       <c r="E61" s="13" t="s">
         <v>1277</v>
       </c>
@@ -17231,7 +18646,7 @@
       </c>
     </row>
     <row r="62" spans="4:6">
-      <c r="D62" s="270"/>
+      <c r="D62" s="307"/>
       <c r="E62" s="13" t="s">
         <v>1278</v>
       </c>
@@ -17240,7 +18655,7 @@
       </c>
     </row>
     <row r="63" spans="4:6">
-      <c r="D63" s="270"/>
+      <c r="D63" s="307"/>
       <c r="E63" s="13" t="s">
         <v>1279</v>
       </c>
@@ -17249,7 +18664,7 @@
       </c>
     </row>
     <row r="64" spans="4:6">
-      <c r="D64" s="270"/>
+      <c r="D64" s="307"/>
       <c r="E64" s="13" t="s">
         <v>1280</v>
       </c>
@@ -17258,7 +18673,7 @@
       </c>
     </row>
     <row r="65" spans="4:6">
-      <c r="D65" s="270"/>
+      <c r="D65" s="307"/>
       <c r="E65" s="13" t="s">
         <v>1281</v>
       </c>
@@ -17267,7 +18682,7 @@
       </c>
     </row>
     <row r="66" spans="4:6">
-      <c r="D66" s="270"/>
+      <c r="D66" s="307"/>
       <c r="E66" s="13" t="s">
         <v>111</v>
       </c>
@@ -17276,7 +18691,7 @@
       </c>
     </row>
     <row r="67" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D67" s="271"/>
+      <c r="D67" s="308"/>
       <c r="E67" s="21" t="s">
         <v>114</v>
       </c>
@@ -17311,11 +18726,11 @@
       <c r="B3" s="40" t="s">
         <v>894</v>
       </c>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="303" t="s">
         <v>948</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="E3" s="268"/>
+      <c r="D3" s="304"/>
+      <c r="E3" s="305"/>
       <c r="H3" t="s">
         <v>953</v>
       </c>
@@ -17729,11 +19144,11 @@
       <c r="C3" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D3" s="262" t="s">
+      <c r="D3" s="299" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="263"/>
-      <c r="F3" s="264"/>
+      <c r="E3" s="300"/>
+      <c r="F3" s="301"/>
       <c r="H3" s="41" t="s">
         <v>456</v>
       </c>
@@ -17761,11 +19176,11 @@
     </row>
     <row r="5" spans="3:9" ht="15.75">
       <c r="C5" s="7"/>
-      <c r="D5" s="275" t="s">
+      <c r="D5" s="312" t="s">
         <v>458</v>
       </c>
-      <c r="E5" s="276"/>
-      <c r="F5" s="277"/>
+      <c r="E5" s="313"/>
+      <c r="F5" s="314"/>
       <c r="H5" s="44" t="s">
         <v>460</v>
       </c>
@@ -17869,11 +19284,11 @@
       <c r="F12" s="53"/>
     </row>
     <row r="13" spans="3:9" ht="15.75">
-      <c r="D13" s="275" t="s">
+      <c r="D13" s="312" t="s">
         <v>460</v>
       </c>
-      <c r="E13" s="276"/>
-      <c r="F13" s="277"/>
+      <c r="E13" s="313"/>
+      <c r="F13" s="314"/>
     </row>
     <row r="14" spans="3:9" ht="31.5">
       <c r="D14" s="54" t="s">
@@ -18075,11 +19490,11 @@
       <c r="F28" s="53"/>
     </row>
     <row r="29" spans="4:9" ht="15.75">
-      <c r="D29" s="278" t="s">
+      <c r="D29" s="315" t="s">
         <v>464</v>
       </c>
-      <c r="E29" s="279"/>
-      <c r="F29" s="280"/>
+      <c r="E29" s="316"/>
+      <c r="F29" s="317"/>
     </row>
     <row r="30" spans="4:9" ht="15.75">
       <c r="D30" s="103" t="s">
@@ -18197,11 +19612,11 @@
       <c r="F40" s="53"/>
     </row>
     <row r="41" spans="4:6" ht="15.75">
-      <c r="D41" s="272" t="s">
+      <c r="D41" s="309" t="s">
         <v>472</v>
       </c>
-      <c r="E41" s="273"/>
-      <c r="F41" s="274"/>
+      <c r="E41" s="310"/>
+      <c r="F41" s="311"/>
     </row>
     <row r="42" spans="4:6" ht="15.75">
       <c r="D42" s="46" t="s">
@@ -18335,11 +19750,11 @@
       <c r="F54" s="53"/>
     </row>
     <row r="55" spans="4:6" ht="15.75">
-      <c r="D55" s="272" t="s">
+      <c r="D55" s="309" t="s">
         <v>476</v>
       </c>
-      <c r="E55" s="273"/>
-      <c r="F55" s="274"/>
+      <c r="E55" s="310"/>
+      <c r="F55" s="311"/>
     </row>
     <row r="56" spans="4:6" ht="15.75">
       <c r="D56" s="61" t="s">
@@ -18421,11 +19836,11 @@
       <c r="B2" s="90" t="s">
         <v>894</v>
       </c>
-      <c r="C2" s="281" t="s">
+      <c r="C2" s="318" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="264"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="301"/>
       <c r="H2" s="59" t="s">
         <v>511</v>
       </c>
@@ -18679,11 +20094,11 @@
       <c r="C2" s="75" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="266" t="s">
+      <c r="D2" s="303" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="267"/>
-      <c r="F2" s="268"/>
+      <c r="E2" s="304"/>
+      <c r="F2" s="305"/>
       <c r="I2" t="s">
         <v>569</v>
       </c>
@@ -19077,11 +20492,11 @@
       <c r="C39" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D39" s="262" t="s">
+      <c r="D39" s="299" t="s">
         <v>1</v>
       </c>
-      <c r="E39" s="263"/>
-      <c r="F39" s="264"/>
+      <c r="E39" s="300"/>
+      <c r="F39" s="301"/>
       <c r="H39" t="s">
         <v>635</v>
       </c>
@@ -19479,11 +20894,11 @@
       <c r="C76" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D76" s="262" t="s">
+      <c r="D76" s="299" t="s">
         <v>1</v>
       </c>
-      <c r="E76" s="263"/>
-      <c r="F76" s="264"/>
+      <c r="E76" s="300"/>
+      <c r="F76" s="301"/>
       <c r="H76" t="s">
         <v>688</v>
       </c>
@@ -19896,11 +21311,11 @@
       <c r="C114" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D114" s="262" t="s">
+      <c r="D114" s="299" t="s">
         <v>1</v>
       </c>
-      <c r="E114" s="263"/>
-      <c r="F114" s="264"/>
+      <c r="E114" s="300"/>
+      <c r="F114" s="301"/>
       <c r="H114" s="2" t="s">
         <v>637</v>
       </c>
@@ -20232,11 +21647,11 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="285" t="s">
+      <c r="D3" s="322" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="286"/>
-      <c r="F3" s="287"/>
+      <c r="E3" s="323"/>
+      <c r="F3" s="324"/>
       <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
@@ -20255,11 +21670,11 @@
     </row>
     <row r="5" spans="3:9" ht="15.75" thickBot="1">
       <c r="C5" s="7"/>
-      <c r="D5" s="282" t="s">
+      <c r="D5" s="319" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="283"/>
-      <c r="F5" s="284"/>
+      <c r="E5" s="320"/>
+      <c r="F5" s="321"/>
       <c r="H5" s="8" t="s">
         <v>6</v>
       </c>
@@ -20509,11 +21924,11 @@
     </row>
     <row r="24" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="25" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D25" s="288" t="s">
+      <c r="D25" s="325" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="289"/>
-      <c r="F25" s="290"/>
+      <c r="E25" s="326"/>
+      <c r="F25" s="327"/>
     </row>
     <row r="26" spans="4:6">
       <c r="D26" s="110" t="s">
@@ -20748,11 +22163,11 @@
     </row>
     <row r="47" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="48" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D48" s="282" t="s">
+      <c r="D48" s="319" t="s">
         <v>1312</v>
       </c>
-      <c r="E48" s="283"/>
-      <c r="F48" s="284"/>
+      <c r="E48" s="320"/>
+      <c r="F48" s="321"/>
     </row>
     <row r="49" spans="4:6">
       <c r="D49" s="10" t="s">
@@ -21075,11 +22490,11 @@
     </row>
     <row r="78" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="79" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D79" s="291" t="s">
+      <c r="D79" s="328" t="s">
         <v>21</v>
       </c>
-      <c r="E79" s="292"/>
-      <c r="F79" s="293"/>
+      <c r="E79" s="329"/>
+      <c r="F79" s="330"/>
     </row>
     <row r="80" spans="4:6">
       <c r="D80" s="118" t="s">
@@ -21226,11 +22641,11 @@
     </row>
     <row r="93" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="94" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D94" s="291" t="s">
+      <c r="D94" s="328" t="s">
         <v>30</v>
       </c>
-      <c r="E94" s="292"/>
-      <c r="F94" s="293"/>
+      <c r="E94" s="329"/>
+      <c r="F94" s="330"/>
     </row>
     <row r="95" spans="4:6">
       <c r="D95" s="110" t="s">
@@ -21344,11 +22759,11 @@
     </row>
     <row r="105" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="106" spans="4:6" ht="15.75" thickBot="1">
-      <c r="D106" s="282" t="s">
+      <c r="D106" s="319" t="s">
         <v>26</v>
       </c>
-      <c r="E106" s="283"/>
-      <c r="F106" s="284"/>
+      <c r="E106" s="320"/>
+      <c r="F106" s="321"/>
     </row>
     <row r="107" spans="4:6">
       <c r="D107" s="110" t="s">
